--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Schema" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Extra" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +41,9 @@
     <font>
       <b val="1"/>
       <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <sz val="11"/>
     </font>
   </fonts>
@@ -103,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -151,6 +155,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4858,6 +4864,238 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="74" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Include this info (yes/no) Test becomes root object, not cell</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Example dataset title</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>What the dataset contains, and anything needed to read it correctly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>Keywords</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>electrolysis</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>electrochemistry</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>Publisher</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Date issued</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>Date published</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Publication DOI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1234/example.2026.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>Dataset URL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.1234567</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Dataset API URL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/api/records/1234567</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Citation</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>F. Lastname et al., Example Journal 1, 100 (2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Figures</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fig. 1a</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Fig. 2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Authors</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Affiliations</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Firstname Lastname</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Corsin Battaglia</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4966,7 +5204,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5222,13 +5460,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C167"/>
+  <dimension ref="A1:C169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6355,360 +6593,384 @@
         </is>
       </c>
     </row>
-    <row r="143"/>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q262760</t>
+        </is>
+      </c>
+    </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>AGC</t>
+          <t>ETH Zurich</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q367032</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>AGC Inc. (formerly Asahi Glass); manufacturer of Selemion AEM/CEM series and Flemion CEM series. https://www.agc.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Agfa</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q310172</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Agfa-Gevaert; manufacturer of Zirfon Perl UTP 500 porous composite diaphragm for alkaline water electrolysis. https://www.agfa.com</t>
-        </is>
-      </c>
-    </row>
+          <t>https://www.wikidata.org/wiki/Q11942</t>
+        </is>
+      </c>
+    </row>
+    <row r="145"/>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Astom</t>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q367032</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Astom Corporation (formerly Tokuyama); manufacturer of Neosepta ion exchange membrane series (AMX, CMX, AHA, BP-1). https://www.astom-corp.jp. to be requested</t>
+          <t>AGC Inc. (formerly Asahi Glass); manufacturer of Selemion AEM/CEM series and Flemion CEM series. https://www.agc.com</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AvCarb</t>
+          <t>Agfa</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q310172</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AvCarb Material Solutions; manufacturer of carbon GDL series (P75, MGL190, 1071HCB) and MPLs. https://www.avcarb.com. to be requested</t>
+          <t>Agfa-Gevaert; manufacturer of Zirfon Perl UTP 500 porous composite diaphragm for alkaline water electrolysis. https://www.agfa.com</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Celgard</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q122199856</t>
+          <t>Astom</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Celgard LLC (Polypore subsidiary); manufacturer of microporous polyolefin separators and membranes for batteries and filtration. https://www.celgard.com</t>
+          <t>Astom Corporation (formerly Tokuyama); manufacturer of Neosepta ion exchange membrane series (AMX, CMX, AHA, BP-1). https://www.astom-corp.jp. to be requested</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Chemours</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q15829006</t>
+          <t>AvCarb</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>The Chemours Company; manufacturer of Nafion perfluorosulfonic acid CEM series (N117, N115, N212, N211). https://www.chemours.com</t>
+          <t>AvCarb Material Solutions; manufacturer of carbon GDL series (P75, MGL190, 1071HCB) and MPLs. https://www.avcarb.com. to be requested</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Customcells</t>
+          <t>Celgard</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q120784603</t>
+          <t>https://www.wikidata.org/wiki/Q122199856</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Customcells Group; manufacturer of custom lithium-ion battery cells for R&amp;D and prototyping. https://www.customcells.org</t>
+          <t>Celgard LLC (Polypore subsidiary); manufacturer of microporous polyolefin separators and membranes for batteries and filtration. https://www.celgard.com</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Dioxide Materials</t>
+          <t>Chemours</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q15829006</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Dioxide Materials; manufacturer of Sustainion X37-50 anion exchange membrane (PolyArylPiperidinium backbone, 50 µm). https://www.dioxidematerials.com. to be requested</t>
+          <t>The Chemours Company; manufacturer of Nafion perfluorosulfonic acid CEM series (N117, N115, N212, N211). https://www.chemours.com</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>El-Cell</t>
+          <t>Customcells</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q120784603</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>EL-CELL GmbH; developer of high-precision electrochemical testing equipment and battery research solutions. https://el-cell.com, to be requested</t>
+          <t>Customcells Group; manufacturer of custom lithium-ion battery cells for R&amp;D and prototyping. https://www.customcells.org</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Freudenberg</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q879878</t>
+          <t>Dioxide Materials</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Freudenberg Performance Materials; manufacturer of gas diffusion layer series (H23C6, H14C9, H23C2) for fuel cells and electrolyzers. https://www.freudenberg-pm.com</t>
+          <t>Dioxide Materials; manufacturer of Sustainion X37-50 anion exchange membrane (PolyArylPiperidinium backbone, 50 µm). https://www.dioxidematerials.com. to be requested</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Fuel Cell Store</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q27868725</t>
+          <t>El-Cell</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Fuel Cell Store; US-based distributor of membrane electrode assemblies, GDLs and ion exchange membranes including Sustainion, PiperION and Nafion. https://www.fuelcellstore.com. to be requested</t>
+          <t>EL-CELL GmbH; developer of high-precision electrochemical testing equipment and battery research solutions. https://el-cell.com, to be requested</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Fumatech</t>
+          <t>Freudenberg</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q879878</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FuMA-Tech GmbH; manufacturer of FAA-3-50 and FAP-375-PP AEM series, Fumapem F/SF CEM series, and FBM bipolar membrane. https://www.fumatech.com. to be requested</t>
+          <t>Freudenberg Performance Materials; manufacturer of gas diffusion layer series (H23C6, H14C9, H23C2) for fuel cells and electrolyzers. https://www.freudenberg-pm.com</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Goodfellow</t>
+          <t>Fuel Cell Store</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q21449964</t>
+          <t>https://www.wikidata.org/wiki/Q27868725</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Goodfellow Group; supplier of metals, alloys, polymers, ceramics and other materials in small quantities for research and development. https://www.goodfellow.com</t>
+          <t>Fuel Cell Store; US-based distributor of membrane electrode assemblies, GDLs and ion exchange membranes including Sustainion, PiperION and Nafion. https://www.fuelcellstore.com. to be requested</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Hohsen</t>
+          <t>Fumatech</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Hohsen Corp.; Japanese manufacturer of specialty separators and ion exchange membranes for electrochemical applications. to be requested</t>
+          <t>FuMA-Tech GmbH; manufacturer of FAA-3-50 and FAP-375-PP AEM series, Fumapem F/SF CEM series, and FBM bipolar membrane. https://www.fumatech.com. to be requested</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ionomr</t>
+          <t>Goodfellow</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q21449964</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ionomr Innovations; manufacturer of Aemion+ AEM series (AF1-HNN5-50-X, AF1-HWW8-25-X) based on poly(arylene imidazolium) backbone. https://www.ionomr.com. to be requested</t>
+          <t>Goodfellow Group; supplier of metals, alloys, polymers, ceramics and other materials in small quantities for research and development. https://www.goodfellow.com</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Millipore Sigma</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q1669719</t>
+          <t>Hohsen</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MilliporeSigma (Merck KGaA subsidiary, US operations); supplier of high-purity electrolyte chemicals and reagents for research. https://www.sigmaaldrich.com. to be requested</t>
+          <t>Hohsen Corp.; Japanese manufacturer of specialty separators and ion exchange membranes for electrochemical applications. to be requested</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SGLCarbon</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q2361947</t>
+          <t>Ionomr</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SGL Carbon SE; manufacturer of Sigracet GDL series (22BB, 28BC, 29BC, 39BB, 39BC) for fuel cells and electrolyzers. https://www.sglcarbon.com</t>
+          <t>Ionomr Innovations; manufacturer of Aemion+ AEM series (AF1-HNN5-50-X, AF1-HWW8-25-X) based on poly(arylene imidazolium) backbone. https://www.ionomr.com. to be requested</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Sigracet</t>
+          <t>Millipore Sigma</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1669719</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SIGRACET Fuel Cell Components</t>
+          <t>MilliporeSigma (Merck KGaA subsidiary, US operations); supplier of high-purity electrolyte chemicals and reagents for research. https://www.sigmaaldrich.com. to be requested</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sterlitech</t>
+          <t>SGLCarbon</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q2361947</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Sterlitech Corporation; provider of PTFE membranes (0.05 μm to 10.0 μm) for chemical venting, gas diffusion, and aggressive solvent filtration. https://www.sterlitech.com, to be requested</t>
+          <t>SGL Carbon SE; manufacturer of Sigracet GDL series (22BB, 28BC, 29BC, 39BB, 39BC) for fuel cells and electrolyzers. https://www.sglcarbon.com</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Solvay</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q487209</t>
+          <t>Sigracet</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Solvay S.A.; manufacturer of Aquivion short-side-chain PFSA CEM series (E87-05S, E87-12S, E98-05S) for PEM electrolyzers. https://www.solvay.com</t>
+          <t>SIGRACET Fuel Cell Components</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Solvionic</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q30285492</t>
+          <t>Sterlitech</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Solvionic; French manufacturer and supplier of ionic liquids and specialty electrolyte solutions for electrochemical research. https://www.solvionic.com</t>
+          <t>Sterlitech Corporation; provider of PTFE membranes (0.05 μm to 10.0 μm) for chemical venting, gas diffusion, and aggressive solvent filtration. https://www.sterlitech.com, to be requested</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Solvay</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q306455</t>
+          <t>https://www.wikidata.org/wiki/Q487209</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific; global supplier of laboratory chemicals, reagents and analytical instruments. https://www.thermofisher.com</t>
+          <t>Solvay S.A.; manufacturer of Aquivion short-side-chain PFSA CEM series (E87-05S, E87-12S, E98-05S) for PEM electrolyzers. https://www.solvay.com</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Toray</t>
+          <t>Solvionic</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q908461</t>
+          <t>https://www.wikidata.org/wiki/Q30285492</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Toray Industries; manufacturer of Toray carbon paper GDL series (TGP-H-060, TGP-H-090, TGP-H-120) for fuel cells and electrolyzers. https://www.toray.com</t>
+          <t>Solvionic; French manufacturer and supplier of ionic liquids and specialty electrolyte solutions for electrochemical research. https://www.solvionic.com</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q306455</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific; global supplier of laboratory chemicals, reagents and analytical instruments. https://www.thermofisher.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Toray</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q908461</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Toray Industries; manufacturer of Toray carbon paper GDL series (TGP-H-060, TGP-H-090, TGP-H-120) for fuel cells and electrolyzers. https://www.toray.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
           <t>Versogen</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>Versogen Inc.; manufacturer of PiperION AEM series based on poly(aryl piperidinium) backbone for CO2 electrolysis and fuel cells. https://www.versogen.com. to be requested</t>
         </is>
@@ -6719,7 +6981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Schema" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Extra" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +41,9 @@
     <font>
       <b val="1"/>
       <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <sz val="11"/>
     </font>
   </fonts>
@@ -103,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -151,6 +155,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4858,6 +4864,238 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="74" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Include this info (yes/no) Test becomes root object</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Example dataset title</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>What the dataset contains, and anything needed to read it correctly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>Keywords</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>electrolysis</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>electrochemistry</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>Publisher</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Date issued</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>Date published</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Publication DOI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1234/example.2026.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>Dataset URL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.1234567</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Dataset API URL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/api/records/1234567</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Citation</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>F. Lastname et al., Example Journal 1, 100 (2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Figures</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fig. 1a</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Fig. 2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Authors</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Affiliations</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Firstname Lastname</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Corsin Battaglia</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4966,7 +5204,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5222,13 +5460,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C167"/>
+  <dimension ref="A1:C169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6355,360 +6593,384 @@
         </is>
       </c>
     </row>
-    <row r="143"/>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q262760</t>
+        </is>
+      </c>
+    </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>AGC</t>
+          <t>ETH Zurich</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q367032</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>AGC Inc. (formerly Asahi Glass); manufacturer of Selemion AEM/CEM series and Flemion CEM series. https://www.agc.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Agfa</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q310172</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Agfa-Gevaert; manufacturer of Zirfon Perl UTP 500 porous composite diaphragm for alkaline water electrolysis. https://www.agfa.com</t>
-        </is>
-      </c>
-    </row>
+          <t>https://www.wikidata.org/wiki/Q11942</t>
+        </is>
+      </c>
+    </row>
+    <row r="145"/>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Astom</t>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q367032</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Astom Corporation (formerly Tokuyama); manufacturer of Neosepta ion exchange membrane series (AMX, CMX, AHA, BP-1). https://www.astom-corp.jp. to be requested</t>
+          <t>AGC Inc. (formerly Asahi Glass); manufacturer of Selemion AEM/CEM series and Flemion CEM series. https://www.agc.com</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AvCarb</t>
+          <t>Agfa</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q310172</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AvCarb Material Solutions; manufacturer of carbon GDL series (P75, MGL190, 1071HCB) and MPLs. https://www.avcarb.com. to be requested</t>
+          <t>Agfa-Gevaert; manufacturer of Zirfon Perl UTP 500 porous composite diaphragm for alkaline water electrolysis. https://www.agfa.com</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Celgard</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q122199856</t>
+          <t>Astom</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Celgard LLC (Polypore subsidiary); manufacturer of microporous polyolefin separators and membranes for batteries and filtration. https://www.celgard.com</t>
+          <t>Astom Corporation (formerly Tokuyama); manufacturer of Neosepta ion exchange membrane series (AMX, CMX, AHA, BP-1). https://www.astom-corp.jp. to be requested</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Chemours</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q15829006</t>
+          <t>AvCarb</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>The Chemours Company; manufacturer of Nafion perfluorosulfonic acid CEM series (N117, N115, N212, N211). https://www.chemours.com</t>
+          <t>AvCarb Material Solutions; manufacturer of carbon GDL series (P75, MGL190, 1071HCB) and MPLs. https://www.avcarb.com. to be requested</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Customcells</t>
+          <t>Celgard</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q120784603</t>
+          <t>https://www.wikidata.org/wiki/Q122199856</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Customcells Group; manufacturer of custom lithium-ion battery cells for R&amp;D and prototyping. https://www.customcells.org</t>
+          <t>Celgard LLC (Polypore subsidiary); manufacturer of microporous polyolefin separators and membranes for batteries and filtration. https://www.celgard.com</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Dioxide Materials</t>
+          <t>Chemours</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q15829006</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Dioxide Materials; manufacturer of Sustainion X37-50 anion exchange membrane (PolyArylPiperidinium backbone, 50 µm). https://www.dioxidematerials.com. to be requested</t>
+          <t>The Chemours Company; manufacturer of Nafion perfluorosulfonic acid CEM series (N117, N115, N212, N211). https://www.chemours.com</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>El-Cell</t>
+          <t>Customcells</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q120784603</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>EL-CELL GmbH; developer of high-precision electrochemical testing equipment and battery research solutions. https://el-cell.com, to be requested</t>
+          <t>Customcells Group; manufacturer of custom lithium-ion battery cells for R&amp;D and prototyping. https://www.customcells.org</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Freudenberg</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q879878</t>
+          <t>Dioxide Materials</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Freudenberg Performance Materials; manufacturer of gas diffusion layer series (H23C6, H14C9, H23C2) for fuel cells and electrolyzers. https://www.freudenberg-pm.com</t>
+          <t>Dioxide Materials; manufacturer of Sustainion X37-50 anion exchange membrane (PolyArylPiperidinium backbone, 50 µm). https://www.dioxidematerials.com. to be requested</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Fuel Cell Store</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q27868725</t>
+          <t>El-Cell</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Fuel Cell Store; US-based distributor of membrane electrode assemblies, GDLs and ion exchange membranes including Sustainion, PiperION and Nafion. https://www.fuelcellstore.com. to be requested</t>
+          <t>EL-CELL GmbH; developer of high-precision electrochemical testing equipment and battery research solutions. https://el-cell.com, to be requested</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Fumatech</t>
+          <t>Freudenberg</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q879878</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FuMA-Tech GmbH; manufacturer of FAA-3-50 and FAP-375-PP AEM series, Fumapem F/SF CEM series, and FBM bipolar membrane. https://www.fumatech.com. to be requested</t>
+          <t>Freudenberg Performance Materials; manufacturer of gas diffusion layer series (H23C6, H14C9, H23C2) for fuel cells and electrolyzers. https://www.freudenberg-pm.com</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Goodfellow</t>
+          <t>Fuel Cell Store</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q21449964</t>
+          <t>https://www.wikidata.org/wiki/Q27868725</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Goodfellow Group; supplier of metals, alloys, polymers, ceramics and other materials in small quantities for research and development. https://www.goodfellow.com</t>
+          <t>Fuel Cell Store; US-based distributor of membrane electrode assemblies, GDLs and ion exchange membranes including Sustainion, PiperION and Nafion. https://www.fuelcellstore.com. to be requested</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Hohsen</t>
+          <t>Fumatech</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Hohsen Corp.; Japanese manufacturer of specialty separators and ion exchange membranes for electrochemical applications. to be requested</t>
+          <t>FuMA-Tech GmbH; manufacturer of FAA-3-50 and FAP-375-PP AEM series, Fumapem F/SF CEM series, and FBM bipolar membrane. https://www.fumatech.com. to be requested</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ionomr</t>
+          <t>Goodfellow</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q21449964</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ionomr Innovations; manufacturer of Aemion+ AEM series (AF1-HNN5-50-X, AF1-HWW8-25-X) based on poly(arylene imidazolium) backbone. https://www.ionomr.com. to be requested</t>
+          <t>Goodfellow Group; supplier of metals, alloys, polymers, ceramics and other materials in small quantities for research and development. https://www.goodfellow.com</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Millipore Sigma</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q1669719</t>
+          <t>Hohsen</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MilliporeSigma (Merck KGaA subsidiary, US operations); supplier of high-purity electrolyte chemicals and reagents for research. https://www.sigmaaldrich.com. to be requested</t>
+          <t>Hohsen Corp.; Japanese manufacturer of specialty separators and ion exchange membranes for electrochemical applications. to be requested</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SGLCarbon</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q2361947</t>
+          <t>Ionomr</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SGL Carbon SE; manufacturer of Sigracet GDL series (22BB, 28BC, 29BC, 39BB, 39BC) for fuel cells and electrolyzers. https://www.sglcarbon.com</t>
+          <t>Ionomr Innovations; manufacturer of Aemion+ AEM series (AF1-HNN5-50-X, AF1-HWW8-25-X) based on poly(arylene imidazolium) backbone. https://www.ionomr.com. to be requested</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Sigracet</t>
+          <t>Millipore Sigma</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1669719</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SIGRACET Fuel Cell Components</t>
+          <t>MilliporeSigma (Merck KGaA subsidiary, US operations); supplier of high-purity electrolyte chemicals and reagents for research. https://www.sigmaaldrich.com. to be requested</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sterlitech</t>
+          <t>SGLCarbon</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q2361947</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Sterlitech Corporation; provider of PTFE membranes (0.05 μm to 10.0 μm) for chemical venting, gas diffusion, and aggressive solvent filtration. https://www.sterlitech.com, to be requested</t>
+          <t>SGL Carbon SE; manufacturer of Sigracet GDL series (22BB, 28BC, 29BC, 39BB, 39BC) for fuel cells and electrolyzers. https://www.sglcarbon.com</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Solvay</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q487209</t>
+          <t>Sigracet</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Solvay S.A.; manufacturer of Aquivion short-side-chain PFSA CEM series (E87-05S, E87-12S, E98-05S) for PEM electrolyzers. https://www.solvay.com</t>
+          <t>SIGRACET Fuel Cell Components</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Solvionic</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q30285492</t>
+          <t>Sterlitech</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Solvionic; French manufacturer and supplier of ionic liquids and specialty electrolyte solutions for electrochemical research. https://www.solvionic.com</t>
+          <t>Sterlitech Corporation; provider of PTFE membranes (0.05 μm to 10.0 μm) for chemical venting, gas diffusion, and aggressive solvent filtration. https://www.sterlitech.com, to be requested</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Solvay</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q306455</t>
+          <t>https://www.wikidata.org/wiki/Q487209</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific; global supplier of laboratory chemicals, reagents and analytical instruments. https://www.thermofisher.com</t>
+          <t>Solvay S.A.; manufacturer of Aquivion short-side-chain PFSA CEM series (E87-05S, E87-12S, E98-05S) for PEM electrolyzers. https://www.solvay.com</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Toray</t>
+          <t>Solvionic</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q908461</t>
+          <t>https://www.wikidata.org/wiki/Q30285492</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Toray Industries; manufacturer of Toray carbon paper GDL series (TGP-H-060, TGP-H-090, TGP-H-120) for fuel cells and electrolyzers. https://www.toray.com</t>
+          <t>Solvionic; French manufacturer and supplier of ionic liquids and specialty electrolyte solutions for electrochemical research. https://www.solvionic.com</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q306455</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific; global supplier of laboratory chemicals, reagents and analytical instruments. https://www.thermofisher.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Toray</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q908461</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Toray Industries; manufacturer of Toray carbon paper GDL series (TGP-H-060, TGP-H-090, TGP-H-120) for fuel cells and electrolyzers. https://www.toray.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
           <t>Versogen</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>Versogen Inc.; manufacturer of PiperION AEM series based on poly(aryl piperidinium) backbone for CO2 electrolysis and fuel cells. https://www.versogen.com. to be requested</t>
         </is>
@@ -6719,7 +6981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -859,7 +859,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>0.1.2</t>
+          <t>0.1.3</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Negative electrode coating active material particle size (leave blanc for films)</t>
+          <t>Negative electrode coating active material particle size (leave blank for films)</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
@@ -1926,7 +1926,7 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material mean particle size (leave blanc for films)</t>
+          <t>Positive electrode coating active material mean particle size (leave blank for films)</t>
         </is>
       </c>
       <c r="B54" s="12" t="n">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="C120" s="16" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>unitless</t>
         </is>
       </c>
       <c r="D120" s="16" t="inlineStr">
@@ -3914,7 +3914,7 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Membrane type  (BilayerMembrane or leave blanc)</t>
+          <t>Membrane type  (BilayerMembrane or leave blank)</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -4356,7 +4356,7 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Cell case type (FlowCell or leave blanc)</t>
+          <t>Cell case type (FlowCell or leave blank)</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -4384,7 +4384,7 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Negative electrode gas compartment (FlowField or leave blanc)</t>
+          <t>Negative electrode gas compartment (FlowField or leave blank)</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
@@ -4570,7 +4570,7 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>Anolyte compartement volume</t>
+          <t>Anolyte compartment volume</t>
         </is>
       </c>
       <c r="B162" s="4" t="n">
@@ -4702,7 +4702,7 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>Positive electrode gas compartment (FlowField or leave blanc)</t>
+          <t>Positive electrode gas compartment (FlowField or leave blank)</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fumasep FAA by Fumtech (AEM)</t>
+          <t>Fumasep FAA by Fumatech (AEM)</t>
         </is>
       </c>
     </row>

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -2498,7 +2498,7 @@
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catholyte solute A molarity </t>
+          <t>Catholyte solute A molarity</t>
         </is>
       </c>
       <c r="B77" s="16" t="n">
@@ -2572,7 +2572,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catholyte volume  </t>
+          <t>Catholyte volume</t>
         </is>
       </c>
       <c r="B80" s="4" t="n">
@@ -3340,7 +3340,7 @@
     <row r="112">
       <c r="A112" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anolyte solute A molarity </t>
+          <t>Anolyte solute A molarity</t>
         </is>
       </c>
       <c r="B112" s="16" t="n">
@@ -3414,7 +3414,7 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anolyte volume  </t>
+          <t>Anolyte volume</t>
         </is>
       </c>
       <c r="B115" s="4" t="n">
@@ -5256,7 +5256,7 @@
     <row r="2">
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">If the item is listed here without unique ID (e.g. R2032), this means the item is already ontologized in BattInFo ontology. No additional ID is required. </t>
+          <t>If the item is listed here without unique ID (e.g. R2032), this means the item is already ontologized in BattInFo ontology. No additional ID is required.</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teflon by Chemours (PTFE), Polyflon by Daikin (PTFE), </t>
+          <t>Teflon by Chemours (PTFE), Polyflon by Daikin (PTFE),</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gas </t>
+          <t>Gas</t>
         </is>
       </c>
     </row>

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -859,7 +859,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>0.1.2</t>
+          <t>0.1.3</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Negative electrode coating active material particle size (leave blanc for films)</t>
+          <t>Negative electrode coating active material particle size (leave blank for films)</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
@@ -1926,7 +1926,7 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material mean particle size (leave blanc for films)</t>
+          <t>Positive electrode coating active material mean particle size (leave blank for films)</t>
         </is>
       </c>
       <c r="B54" s="12" t="n">
@@ -2498,7 +2498,7 @@
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catholyte solute A molarity </t>
+          <t>Catholyte solute A molarity</t>
         </is>
       </c>
       <c r="B77" s="16" t="n">
@@ -2572,7 +2572,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catholyte volume  </t>
+          <t>Catholyte volume</t>
         </is>
       </c>
       <c r="B80" s="4" t="n">
@@ -3340,7 +3340,7 @@
     <row r="112">
       <c r="A112" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anolyte solute A molarity </t>
+          <t>Anolyte solute A molarity</t>
         </is>
       </c>
       <c r="B112" s="16" t="n">
@@ -3414,7 +3414,7 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anolyte volume  </t>
+          <t>Anolyte volume</t>
         </is>
       </c>
       <c r="B115" s="4" t="n">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="C120" s="16" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>unitless</t>
         </is>
       </c>
       <c r="D120" s="16" t="inlineStr">
@@ -3914,7 +3914,7 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Membrane type  (BilayerMembrane or leave blanc)</t>
+          <t>Membrane type  (BilayerMembrane or leave blank)</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -4356,7 +4356,7 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Cell case type (FlowCell or leave blanc)</t>
+          <t>Cell case type (FlowCell or leave blank)</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -4384,7 +4384,7 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Negative electrode gas compartment (FlowField or leave blanc)</t>
+          <t>Negative electrode gas compartment (FlowField or leave blank)</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
@@ -4570,7 +4570,7 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>Anolyte compartement volume</t>
+          <t>Anolyte compartment volume</t>
         </is>
       </c>
       <c r="B162" s="4" t="n">
@@ -4702,7 +4702,7 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>Positive electrode gas compartment (FlowField or leave blanc)</t>
+          <t>Positive electrode gas compartment (FlowField or leave blank)</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
@@ -5256,7 +5256,7 @@
     <row r="2">
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">If the item is listed here without unique ID (e.g. R2032), this means the item is already ontologized in BattInFo ontology. No additional ID is required. </t>
+          <t>If the item is listed here without unique ID (e.g. R2032), this means the item is already ontologized in BattInFo ontology. No additional ID is required.</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fumasep FAA by Fumtech (AEM)</t>
+          <t>Fumasep FAA by Fumatech (AEM)</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teflon by Chemours (PTFE), Polyflon by Daikin (PTFE), </t>
+          <t>Teflon by Chemours (PTFE), Polyflon by Daikin (PTFE),</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gas </t>
+          <t>Gas</t>
         </is>
       </c>
     </row>

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Schema" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Extra" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@References" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="5" state="visible" r:id="rId5"/>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,9 +41,6 @@
     <font>
       <b val="1"/>
       <i val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <sz val="11"/>
     </font>
   </fonts>
@@ -107,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -155,8 +152,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -865,7 +860,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>0.1.3</t>
+          <t>0.2.0</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -4864,224 +4859,357 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="74" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>Include this info (yes/no) Test becomes root object</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>No</t>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>References</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Example dataset title</t>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Include references in metadata file (yes/no)</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>What the dataset contains, and anything needed to read it correctly.</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>References for dataset</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>Keywords</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>electrolysis</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>electrochemistry</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Dataset name</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Dataset for the publication 'Balancing selectivity retention and catalyst restructuring in pulsed CO2 electroreduction on silver'</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>Publisher</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Dataset description</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Dataset for the publication containing raw and processed data used to compose the various figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Dataset publisher</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Empa</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>License</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Dataset license</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>Date issued</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>Date published</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Dataset date issued</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>Publication DOI</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1234/example.2026.001</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Dataset date published</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Dataset URL</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.5281/zenodo.1234567</t>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.22092428</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Dataset API URL</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://zenodo.org/api/records/1234567</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/api/records/22092428</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>Citation</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>F. Lastname et al., Example Journal 1, 100 (2026).</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorA</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Claudia Bissattini</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>EPFL</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>Figures</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorB</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Richa Rajadhyax</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorC</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Alessandro Senocrate</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorD</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Corsin Battaglia</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>References for associated publications</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication DOI</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1039/D6EY00140H</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication title</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Balancing selectivity retention and catalyst restructuring in pulsed CO2 electroreduction on silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication figures</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Fig. 1a</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Fig. 2b</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>Authors</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>Affiliations</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>Firstname Lastname</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorA</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Claudia Bissattini</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Empa</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorB</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Richa Rajadhyax</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorC</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Alessandro Senocrate</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorD</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Corsin Battaglia</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Empa</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>EPFL</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ETH Zurich</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6658,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Claudia Bissattini Alessi</t>
+          <t>Claudia Bissattini</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6542,36 +6670,36 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Claudia Bissattini</t>
+          <t>Finn Beiglboeck</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://orcid.org/0000-0002-3971-0398</t>
+          <t>https://orcid.org/0000-0001-9158-1338</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Finn Beiglboeck</t>
+          <t>Francesco Bernasconi</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://orcid.org/0000-0001-9158-1338</t>
+          <t>https://orcid.org/0000-0002-6563-0578</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Francesco Bernasconi</t>
+          <t>Richa Rajadhyax</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://orcid.org/0000-0002-6563-0578</t>
+          <t>https://orcid.org/0009-0004-2257-1610</t>
         </is>
       </c>
     </row>

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -4859,7 +4859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="74" customWidth="1" min="1" max="1"/>
@@ -5210,6 +5210,92 @@
       <c r="E23" s="4" t="inlineStr">
         <is>
           <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>References for data files</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Data zip file</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Data.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Tabular data schema</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>https://w3id.org/catalysis-data-format/schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Data fileA</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>empa__ecid000001/empa__ecid000001.cdf.parquet</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Time series electrochemical data as parquet with Catalysis Data Format columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Data fileB</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>empa__ecid000001/empa__ecid000001.cdf.csv</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Time series electrochemical data as csv with Catalysis Data Format columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Raw data fileA</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>empa__ecid000001/empa__ecid000001_CA_C01.mpr</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Raw electrochemical data, Biologic EC-Lab mpr binary format</t>
         </is>
       </c>
     </row>

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Individuals" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5424,11 +5425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5442,6 +5444,11 @@
           <t>Key</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5449,223 +5456,264 @@
           <t>hasActiveMaterial</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ActiveMaterial</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hasBinder</t>
+          <t>hasAnolyte</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Binder</t>
+          <t>Anolyte</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hasCase</t>
+          <t>hasBinder</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Binder</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hasCoating</t>
+          <t>hasCatholyte</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Coating</t>
+          <t>Catholyte</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hasConductiveAdditive</t>
+          <t>hasCoating</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ConductiveAdditive</t>
+          <t>Coating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hasCurrentCollector</t>
+          <t>hasConductiveAdditive</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CurrentCollector</t>
+          <t>ConductiveAdditive</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hasElectrolyte</t>
+          <t>hasCounterElectrode</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CounterElectrode</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode</t>
+          <t>hasCurrentCollector</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Electrode</t>
+          <t>CurrentCollector</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode</t>
+          <t>hasElectrolyte</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Electrode</t>
+          <t>Electrolyte</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hasSeparator</t>
+          <t>hasNegativeElectrode</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Separator</t>
+          <t>NegativeElectrode</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hasSolute</t>
+          <t>hasPositiveElectrode</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Solute</t>
+          <t>PositiveElectrode</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hasSolvent</t>
+          <t>hasReferenceElectrode</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Solvent</t>
+          <t>ReferenceElectrode</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hasConstituent</t>
+          <t>hasSeparator</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Separator</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hasInput</t>
+          <t>hasSolute</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Solute</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hasProperty</t>
+          <t>hasSolvent</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Solvent</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hasWaveSpring</t>
+          <t>hasSubstrate</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Substrate</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hasSpacer</t>
+          <t>hasWorkingElectrode</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>WorkingElectrode</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hasMeasuredProperty</t>
+          <t>hasCase</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>hasOutput</t>
+          <t>hasComponent</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hasReferenceElectrode</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ReferenceElectrode</t>
+          <t>hasConstituent</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hasSubstrate</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Substrate</t>
+          <t>hasDatum</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hasWorkingElectrode</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>WorkingElectrode</t>
+          <t>hasInput</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hasCounterElectrode</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CounterElectrode</t>
+          <t>hasMeasuredProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>hasOutput</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>hasProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>hasStringValue</t>
         </is>
       </c>
     </row>
@@ -5680,941 +5728,929 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C169"/>
+  <dimension ref="A1:B127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Class</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>If the item is listed here without unique ID (e.g. R2032), this means the item is already ontologized in BattInFo ontology. No additional ID is required.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ElectrochemicalCell</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Classes available to the @Schema sheet Value column. Classes must already exist in the ontology. You can declare your own custom classes in the @Context sheet. This column is a reference list, a value already known to the ontology works even if it is not listed.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ElectrochemicalCell</t>
+          <t>ElectrochemicalHalfCell</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ElectrochemicalHalfCell</t>
+          <t>BatteryCell</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BatteryCell</t>
+          <t>ElectrolyticCell</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ElectrolyticCell</t>
+          <t>FlowCell</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FlowCell</t>
+          <t>R2032</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R2032</t>
+          <t>CoinCell</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CoinCell</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ThreeElectrodeCell</t>
-        </is>
-      </c>
-    </row>
+          <t>ThreeElectrodeCellDevice</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ZeroGapCell</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>Component</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AnolyteCompartment</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>AnolyteTank</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AnolyteCompartment</t>
+          <t>CatholyteCompartment</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AnolyteTank</t>
+          <t>CatholyteTank</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CatholyteCompartment</t>
+          <t>FlowField</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CatholyteTank</t>
+          <t>GasCompartment</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FlowField</t>
+          <t>NegativeElectrodeGasCompartment</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>requested</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GasCompartment</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>NegativeElectrodeGasCompartment</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+          <t>PositiveElectrodeGasCompartment</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>requested</t>
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PositiveElectrodeGasCompartment</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
+          <t>Electrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GasDiffusionElectrode</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Electrode</t>
+          <t>ImmersionElectrode</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GasDiffusionElectrode</t>
+          <t>ReferenceElectrode</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ImmersionElectrode</t>
+          <t>GlassyCarbonElectrode</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ReferenceElectrode</t>
+          <t>LithiumElectrode</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GlassyCarbonElectrode</t>
+          <t>SilverChlorideElectrode</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LithiumElectrode</t>
+          <t>MercuryOxideElectrode</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>requested</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SilverChlorideElectrode</t>
+          <t>NormalHydrogenElectrode</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MercuryOxideElectrode</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>NormalHydrogenElectrode</t>
-        </is>
-      </c>
-    </row>
+          <t>ReversibleHydrogenElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ReversibleHydrogenElectrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
+          <t>Substrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CarbonPaper</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Substrate</t>
+          <t>ElectrospunMesh</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CarbonPaper</t>
+          <t>ExpandedMesh</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ElectrospunMesh</t>
+          <t>WovenMesh</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ExpandedMesh</t>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>requested</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WovenMesh</t>
+          <t>PerforatedFoil</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>requested</t>
+          <t>Foil</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PerforatedFoil</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Foil</t>
-        </is>
-      </c>
-    </row>
+          <t>Coating</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Coating</t>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
+          <t>Solid</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+    </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Solid</t>
+          <t>Carbon</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>CarbonBlack</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Carbon</t>
+          <t>Copper</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CarbonBlack</t>
+          <t>CopperOxideCompound</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Electrocatalyst</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CopperOxideCompound</t>
+          <t>Graphite</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Electrocatalyst</t>
+          <t>IridiumOxideCompound</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>IridiumIIIOxide</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IridiumOxideCompound</t>
+          <t>IridiumDioxide</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IridiumIIIOxide</t>
+          <t>Lithium</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IridiumDioxide</t>
+          <t>LithiumIronPhosphate</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://pubchem.ncbi.nlm.nih.gov/substance/485083898</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>LithiumNickelManganeseCobaltOxide</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://pubchem.ncbi.nlm.nih.gov/substance/485083898</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LithiumIronPhosphate</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>https://pubchem.ncbi.nlm.nih.gov/substance/485083898</t>
+          <t>LithiumTitanate</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LithiumNickleCobaltManganeseOxide</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>https://pubchem.ncbi.nlm.nih.gov/substance/485083898</t>
+          <t>Nickel</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LithiumTitanate</t>
+          <t>Platinum</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Silver</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>StainlessSteel</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Tantalum</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>StainlessSteel</t>
+          <t>TantalumOxideCompound</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tantalum</t>
+          <t>Titanium</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TantalumOxideCompound</t>
+          <t>TitaniumOxideCompound</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>TitaniumIIOxide</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TitaniumOxideCompound</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>TitaniumIOxide</t>
-        </is>
-      </c>
-    </row>
+          <t>TitaniumIIIOxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TitaniumIIOxide</t>
+          <t>Separator</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TitaniumIIOxide</t>
-        </is>
-      </c>
-    </row>
-    <row r="70"/>
+          <t>GlassFibreSeparator</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>IonExchangeMembrane</t>
+        </is>
+      </c>
+    </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Separator</t>
+          <t>AnionExchangeMembrane</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GlassFiberSeparator</t>
+          <t>CationExchangeMembrane</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IonExchangeMembrane</t>
+          <t>BilayerMembrane</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AnionExchangeMembrane</t>
+          <t>IonomerCompound</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CationExchangeMembrane</t>
+          <t>PerfluorocarboxylicAcid</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Flemion by AGC (CEM), Aciplex by Asahi Kasei (CEM), requested</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BilayerMembrane</t>
+          <t>PerfluorosulfonicAcid</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Nafion by Chemours (long side-chain CEM), Aquivion by Solvay (short side-chain CEM), Fumapem SF by Fumatech (short side-chain CEM), Fumasep F by Fumatech)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IonomerCompound</t>
+          <t>PolyAryleneImidazolium</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Aemion+ by Ionomr (AEM). AF1 by Ionomr (AEM), requested</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PerfluorocarboxylicAcid</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Flemion by AGC (CEM), Aciplex by Asahi Kasei (CEM), requested</t>
+          <t>PolyArylPiperidinium</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Piperion by Versogen (AEM), requested</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PerfluorosulfonicAcid</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Nafion by Chemours (long side-chain CEM), Aquivion by Solvay (short side-chain CEM), Fumapem SF by Fumatech (short side-chain CEM), Fumasep F by Fumatech)</t>
+          <t>PolyArylAmmonium</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Fumasep FAA by Fumatech (AEM)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PolyAryleneImidazolium</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Aemion+ by Ionomr (AEM). AF1 by Ionomr (AEM), requested</t>
+          <t>PolyetherEtherKetone</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Victrex by Solvay (PEEK), Ketaspire by Evonik (PEEK), Radel by Solvay (PEEK), requested</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PolyArylPiperidinium</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Piperion by Versogen (AEM), requested</t>
+          <t>Polyolefin</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PolyArylAmmonium</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Fumasep FAA by Fumatech (AEM)</t>
+          <t>Polypropylene</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Celgard by Polypore International now part of Asahi Kasei (PP)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PolyetherEtherKetone</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Victrex by Solvay (PEEK), Ketaspire by Evonik (PEEK), Radel by Solvay (PEEK), requested</t>
+          <t>Polytetrafluoroethylene</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Teflon by Chemours (PTFE), Polyflon by Daikin (PTFE),</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Polyolefin</t>
+          <t>PolyvinylideneFluoride</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Kynar by Arkema (PVDF), Solef by Solvay (PVDF)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Polypropylene</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Celgard by Polypore International now part of Asahi Kasei (PP)</t>
+          <t>QuaternaryAmmoniumPolySulfone</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Sustainion by Dioxide Materials (AEM), requested</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Polytetrafluoroethylene</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Teflon by Chemours (PTFE), Polyflon by Daikin (PTFE),</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>PolyvinylideneFluoride</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Kynar by Arkema (PVDF), Solef by Solvay (PVDF)</t>
-        </is>
-      </c>
-    </row>
+          <t>SulfonatedPolyEtherEtherKetone</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Speek by Gore (CEM), requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>QuaternaryAmmoniumPolySulfone</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Sustainion by Dioxide Materials (AEM), requested</t>
+          <t>Electrolyte</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SulfonatedPolyEtherEtherKetone</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Speek by Gore (CEM), requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="90"/>
+          <t>LiquidElectrolyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SolidElectrolyte</t>
+        </is>
+      </c>
+    </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Electrolyte</t>
+          <t>EthyleneCarbonate</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LiquidElectrolyte</t>
+          <t>EthylMethylCarbonate</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SolidElectrolyte</t>
+          <t>LithiumBisfluorosulfonylimide</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EthyleneCarbonate</t>
+          <t>LithiumHexafluorophosphate</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EthylMethylCarbonate</t>
+          <t>SodiumChloride</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LithiumBisfluorosulfonylimide</t>
+          <t>SodiumHydroxide</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LithiumHexafluorophosphate</t>
+          <t>PhosphoricAcid</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SodiumChloride</t>
+          <t>PotassiumCarbonate</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SodiumHydroxide</t>
+          <t>SulfuricAcid</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PhosphoricAcid</t>
+          <t>TrisTrimethylsilyPhosphite</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PotassiumCarbonate</t>
+          <t>VinyleneCarbonate</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PotassiumBiCarbonate</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>requested</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SulfuricAcid</t>
+          <t>HydrochloricAcidSolution</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TrisTrimethylsilyPhosphite</t>
+          <t>PotassiumChloride</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>VinyleneCarbonate</t>
+          <t>PotassiumHydroxide</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Methanol</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>HydrochloricAcid</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>PotassiumChloride</t>
-        </is>
-      </c>
-    </row>
+          <t>Ethanol</t>
+        </is>
+      </c>
+    </row>
+    <row r="108"/>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PotassiumHydroxide</t>
+          <t>Gas</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>GasMixture</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Ethanol</t>
-        </is>
-      </c>
-    </row>
-    <row r="112"/>
+          <t>Argon</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+    </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>CarbonDioxide</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GasMixture</t>
+          <t>Nitrogen</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Argon</t>
+          <t>Ammonia</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>CarbonMonoxide</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>requested</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CarbonDioxide</t>
+          <t>Oxygen</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Nitrogen</t>
+          <t>Ethylene</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>requested</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ammonia</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>CarbonMonoxide</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
+          <t>Air</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
         <is>
           <t>requested</t>
         </is>
       </c>
     </row>
+    <row r="120"/>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Oxygen</t>
+          <t>Area</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ethylene</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
         <is>
           <t>requested</t>
         </is>
@@ -6623,570 +6659,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Air</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
+          <t>Purity</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
         <is>
           <t>requested</t>
         </is>
       </c>
     </row>
-    <row r="124"/>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Porosity</t>
+        </is>
+      </c>
+    </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Tortuosity</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>requested</t>
+          <t>Thickness</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Purity</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Porosity</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Tortuosity</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Thickness</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
           <t>Width</t>
-        </is>
-      </c>
-    </row>
-    <row r="132"/>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Corsin Battaglia</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0002-5003-1134</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Graham Kimbell</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0001-9610-3589</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Nukorn Plainpan</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0009-0002-6447-8057</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Alessandro Senocrate</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0002-0952-0948</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Claudia Bissattini</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0002-3971-0398</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Finn Beiglboeck</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0001-9158-1338</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Francesco Bernasconi</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0002-6563-0578</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Richa Rajadhyax</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0009-0004-2257-1610</t>
-        </is>
-      </c>
-    </row>
-    <row r="141"/>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Empa</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q683116</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Swiss Federal Laboratories for Materials Science and Technology; research institution</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>EPFL</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q262760</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>ETH Zurich</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q11942</t>
-        </is>
-      </c>
-    </row>
-    <row r="145"/>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>AGC</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q367032</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>AGC Inc. (formerly Asahi Glass); manufacturer of Selemion AEM/CEM series and Flemion CEM series. https://www.agc.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Agfa</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q310172</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Agfa-Gevaert; manufacturer of Zirfon Perl UTP 500 porous composite diaphragm for alkaline water electrolysis. https://www.agfa.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Astom</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Astom Corporation (formerly Tokuyama); manufacturer of Neosepta ion exchange membrane series (AMX, CMX, AHA, BP-1). https://www.astom-corp.jp. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>AvCarb</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>AvCarb Material Solutions; manufacturer of carbon GDL series (P75, MGL190, 1071HCB) and MPLs. https://www.avcarb.com. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Celgard</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q122199856</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Celgard LLC (Polypore subsidiary); manufacturer of microporous polyolefin separators and membranes for batteries and filtration. https://www.celgard.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Chemours</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q15829006</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>The Chemours Company; manufacturer of Nafion perfluorosulfonic acid CEM series (N117, N115, N212, N211). https://www.chemours.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Customcells</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q120784603</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Customcells Group; manufacturer of custom lithium-ion battery cells for R&amp;D and prototyping. https://www.customcells.org</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Dioxide Materials</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Dioxide Materials; manufacturer of Sustainion X37-50 anion exchange membrane (PolyArylPiperidinium backbone, 50 µm). https://www.dioxidematerials.com. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>El-Cell</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>EL-CELL GmbH; developer of high-precision electrochemical testing equipment and battery research solutions. https://el-cell.com, to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Freudenberg</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q879878</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Freudenberg Performance Materials; manufacturer of gas diffusion layer series (H23C6, H14C9, H23C2) for fuel cells and electrolyzers. https://www.freudenberg-pm.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Fuel Cell Store</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q27868725</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Fuel Cell Store; US-based distributor of membrane electrode assemblies, GDLs and ion exchange membranes including Sustainion, PiperION and Nafion. https://www.fuelcellstore.com. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Fumatech</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>FuMA-Tech GmbH; manufacturer of FAA-3-50 and FAP-375-PP AEM series, Fumapem F/SF CEM series, and FBM bipolar membrane. https://www.fumatech.com. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Goodfellow</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q21449964</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Goodfellow Group; supplier of metals, alloys, polymers, ceramics and other materials in small quantities for research and development. https://www.goodfellow.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Hohsen</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Hohsen Corp.; Japanese manufacturer of specialty separators and ion exchange membranes for electrochemical applications. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Ionomr</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Ionomr Innovations; manufacturer of Aemion+ AEM series (AF1-HNN5-50-X, AF1-HWW8-25-X) based on poly(arylene imidazolium) backbone. https://www.ionomr.com. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Millipore Sigma</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q1669719</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>MilliporeSigma (Merck KGaA subsidiary, US operations); supplier of high-purity electrolyte chemicals and reagents for research. https://www.sigmaaldrich.com. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>SGLCarbon</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q2361947</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>SGL Carbon SE; manufacturer of Sigracet GDL series (22BB, 28BC, 29BC, 39BB, 39BC) for fuel cells and electrolyzers. https://www.sglcarbon.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Sigracet</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>SIGRACET Fuel Cell Components</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Sterlitech</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Sterlitech Corporation; provider of PTFE membranes (0.05 μm to 10.0 μm) for chemical venting, gas diffusion, and aggressive solvent filtration. https://www.sterlitech.com, to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Solvay</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q487209</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Solvay S.A.; manufacturer of Aquivion short-side-chain PFSA CEM series (E87-05S, E87-12S, E98-05S) for PEM electrolyzers. https://www.solvay.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Solvionic</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q30285492</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Solvionic; French manufacturer and supplier of ionic liquids and specialty electrolyte solutions for electrochemical research. https://www.solvionic.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Thermo Fisher Scientific</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q306455</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Thermo Fisher Scientific; global supplier of laboratory chemicals, reagents and analytical instruments. https://www.thermofisher.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Toray</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q908461</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Toray Industries; manufacturer of Toray carbon paper GDL series (TGP-H-060, TGP-H-090, TGP-H-120) for fuel cells and electrolyzers. https://www.toray.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Versogen</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Versogen Inc.; manufacturer of PiperION AEM series based on poly(aryl piperidinium) backbone for CO2 electrolysis and fuel cells. https://www.versogen.com. to be requested</t>
         </is>
       </c>
     </row>
@@ -7196,6 +6702,728 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>IRI</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Corsin Battaglia</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-5003-1134</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Graham Kimbell</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0001-9610-3589</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nukorn Plainpan</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0002-6447-8057</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Alessandro Senocrate</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-0952-0948</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Claudia Bissattini</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-3971-0398</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Finn Beiglboeck</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0001-9158-1338</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Francesco Bernasconi</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-6563-0578</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Richa Rajadhyax</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0004-2257-1610</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q683116</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Swiss Federal Laboratories for Materials Science and Technology; research institution</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q262760</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q11942</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q367032</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AGC Inc. (formerly Asahi Glass); manufacturer of Selemion AEM/CEM series and Flemion CEM series. https://www.agc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Agfa</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q310172</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Agfa-Gevaert; manufacturer of Zirfon Perl UTP 500 porous composite diaphragm for alkaline water electrolysis. https://www.agfa.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Celgard</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q122199856</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Celgard LLC (Polypore subsidiary); manufacturer of microporous polyolefin separators and membranes for batteries and filtration. https://www.celgard.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chemours</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q15829006</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>The Chemours Company; manufacturer of Nafion perfluorosulfonic acid CEM series (N117, N115, N212, N211). https://www.chemours.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Customcells</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q120784603</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Customcells Group; manufacturer of custom lithium-ion battery cells for R&amp;D and prototyping. https://www.customcells.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Freudenberg</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q879878</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Freudenberg Performance Materials; manufacturer of gas diffusion layer series (H23C6, H14C9, H23C2) for fuel cells and electrolyzers. https://www.freudenberg-pm.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuel Cell Store</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q27868725</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fuel Cell Store; US-based distributor of membrane electrode assemblies, GDLs and ion exchange membranes including Sustainion, PiperION and Nafion. https://www.fuelcellstore.com. to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Goodfellow</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q21449964</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Goodfellow Group; supplier of metals, alloys, polymers, ceramics and other materials in small quantities for research and development. https://www.goodfellow.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Millipore Sigma</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1669719</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MilliporeSigma (Merck KGaA subsidiary, US operations); supplier of high-purity electrolyte chemicals and reagents for research. https://www.sigmaaldrich.com. to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SGLCarbon</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q2361947</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SGL Carbon SE; manufacturer of Sigracet GDL series (22BB, 28BC, 29BC, 39BB, 39BC) for fuel cells and electrolyzers. https://www.sglcarbon.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Solvay</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q487209</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Solvay S.A.; manufacturer of Aquivion short-side-chain PFSA CEM series (E87-05S, E87-12S, E98-05S) for PEM electrolyzers. https://www.solvay.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Solvionic</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q30285492</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Solvionic; French manufacturer and supplier of ionic liquids and specialty electrolyte solutions for electrochemical research. https://www.solvionic.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q306455</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific; global supplier of laboratory chemicals, reagents and analytical instruments. https://www.thermofisher.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Toray</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q908461</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Toray Industries; manufacturer of Toray carbon paper GDL series (TGP-H-060, TGP-H-090, TGP-H-120) for fuel cells and electrolyzers. https://www.toray.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Fumatech</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q30254565</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FuMA-Tech GmbH; manufacturer of FAA-3-50 and FAP-375-PP AEM series, Fumapem F/SF CEM series, and FBM bipolar membrane. https://www.fumatech.com. to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Hohsen</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q138027768</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Hohsen Corp.; Japanese manufacturer of specialty separators and ion exchange membranes for electrochemical applications. to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Astom</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Astom Corporation (formerly Tokuyama); manufacturer of Neosepta ion exchange membrane series (AMX, CMX, AHA, BP-1). https://www.astom-corp.jp. to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AvCarb</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AvCarb Material Solutions; manufacturer of carbon GDL series (P75, MGL190, 1071HCB) and MPLs. https://www.avcarb.com. to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Dioxide Materials</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Dioxide Materials; manufacturer of Sustainion X37-50 anion exchange membrane (PolyArylPiperidinium backbone, 50 µm). https://www.dioxidematerials.com. to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>El-Cell</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EL-CELL GmbH; developer of high-precision electrochemical testing equipment and battery research solutions. https://el-cell.com, to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ionomr</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ionomr Innovations; manufacturer of Aemion+ AEM series (AF1-HNN5-50-X, AF1-HWW8-25-X) based on poly(arylene imidazolium) backbone. https://www.ionomr.com. to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sigracet</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SIGRACET Fuel Cell Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sterlitech</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sterlitech Corporation; provider of PTFE membranes (0.05 μm to 10.0 μm) for chemical venting, gas diffusion, and aggressive solvent filtration. https://www.sterlitech.com, to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Versogen</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Versogen Inc.; manufacturer of PiperION AEM series based on poly(aryl piperidinium) backbone for CO2 electrolysis and fuel cells. https://www.versogen.com. to be requested</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -525,8 +525,8 @@
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="160" customWidth="1" min="5" max="5"/>
-    <col width="74" customWidth="1" min="6" max="6"/>
+    <col width="74" customWidth="1" min="5" max="5"/>
+    <col width="160" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -552,12 +552,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Ontology link</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
         </is>
       </c>
     </row>
@@ -584,11 +584,7 @@
           <t>ElectrolyticCell</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C3" s="4" t="n"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -596,12 +592,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
+          <t>Required, do not change</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>type|</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Required, do not change</t>
         </is>
       </c>
     </row>
@@ -616,11 +612,7 @@
           <t>empa__ecid_000001</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -628,12 +620,12 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>Unique ID for cell</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>schema:productID</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Unique ID for cell</t>
         </is>
       </c>
     </row>
@@ -648,11 +640,7 @@
           <t>240616_bco_gr-NMC_01</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -660,12 +648,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>Human-friendly name for the cell</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>schema:name</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Human-friendly name for the cell</t>
         </is>
       </c>
     </row>
@@ -680,11 +668,7 @@
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -692,12 +676,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>Assembly date in ISO8601 format (YYYY-MM-DD)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>schema:dateCreated</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Assembly date in ISO8601 format (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -712,11 +696,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -724,12 +704,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
+          <t>Organisation that made the cell, value should be in @classes with ID</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>schema:manufacturer</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Organisation that made the cell, value should be in @classes with ID</t>
         </is>
       </c>
     </row>
@@ -744,11 +724,7 @@
           <t>Corsin Battaglia</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -756,12 +732,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>Person that made the cell, value should be in @classes with ID</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>schema:creator</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Person that made the cell, value should be in @classes with ID</t>
         </is>
       </c>
     </row>
@@ -776,22 +752,18 @@
           <t>ETHB PREMISE/NCCR Catalysis</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>rdfs:comment</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -804,22 +776,18 @@
           <t>manually</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>rdfs:comment</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -832,11 +800,7 @@
           <t>ElectrolysisCellSchema</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -844,12 +808,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
+          <t>Name of this schema, do not change</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
           <t>rdfs:comment</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Name of this schema, do not change</t>
         </is>
       </c>
     </row>
@@ -864,11 +828,7 @@
           <t>0.2.0</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -876,12 +836,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>Version of this schema, do not change</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>rdfs:comment</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Version of this schema, do not change</t>
         </is>
       </c>
     </row>
@@ -908,22 +868,18 @@
           <t>GasDiffusionElectrode</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -936,22 +892,18 @@
           <t>CarbonPaper</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C15" s="8" t="n"/>
       <c r="D15" s="8" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -964,22 +916,18 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -992,22 +940,18 @@
           <t>Polytetrafluoroethylene</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C17" s="8" t="n"/>
       <c r="D17" s="8" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-hasCoating</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1028,12 +972,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -1046,22 +990,18 @@
           <t>Electrocatalyst</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial</t>
         </is>
       </c>
-      <c r="F19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1074,22 +1014,18 @@
           <t>Copper</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -1110,12 +1046,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassLoading</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1136,12 +1072,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassFraction</t>
         </is>
       </c>
-      <c r="F22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -1154,22 +1090,18 @@
           <t>IonomerCompound</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasBinder</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1182,22 +1114,18 @@
           <t>PerfluorosulfonicAcid</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasBinder</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -1218,12 +1146,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasBinder-hasMeasuredProperty-MassFraction</t>
         </is>
       </c>
-      <c r="F25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1244,12 +1172,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
-      <c r="F26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -1282,12 +1210,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Porosity</t>
         </is>
       </c>
-      <c r="F28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -1308,12 +1236,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-D50ParticleSize</t>
         </is>
       </c>
-      <c r="F29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -1338,22 +1266,18 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C31" s="4" t="n"/>
       <c r="D31" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -1366,22 +1290,18 @@
           <t>15p_Cu</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-schema:productID</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1394,22 +1314,18 @@
           <t>SGLCarbon</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -1422,22 +1338,18 @@
           <t>39BB</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-schema:productID</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1450,22 +1362,18 @@
           <t>Millipore Sigma</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C35" s="4" t="n"/>
       <c r="D35" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -1476,22 +1384,18 @@
       <c r="B36" s="8" t="n">
         <v>774081</v>
       </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-schema:productID</t>
         </is>
       </c>
-      <c r="F36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -1504,22 +1408,18 @@
           <t>Chemours</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C37" s="4" t="n"/>
       <c r="D37" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasBinder-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -1532,22 +1432,18 @@
           <t>D521CS</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasBinder-schema:productID</t>
         </is>
       </c>
-      <c r="F38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -1572,22 +1468,18 @@
           <t>ImmersionElectrode</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C40" s="4" t="n"/>
       <c r="D40" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode</t>
         </is>
       </c>
-      <c r="F40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -1600,22 +1492,18 @@
           <t>PerforatedFoil</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C41" s="12" t="n"/>
       <c r="D41" s="12" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate</t>
         </is>
       </c>
-      <c r="F41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -1628,22 +1516,18 @@
           <t>Titanium</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C42" s="4" t="n"/>
       <c r="D42" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate</t>
         </is>
       </c>
-      <c r="F42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -1664,12 +1548,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
-      <c r="F43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -1682,22 +1566,18 @@
           <t>Electrocatalyst</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
         </is>
       </c>
-      <c r="F44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -1710,22 +1590,18 @@
           <t>IridiumIIIOxide</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C45" s="12" t="n"/>
       <c r="D45" s="12" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
         </is>
       </c>
-      <c r="F45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -1746,12 +1622,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassLoading</t>
         </is>
       </c>
-      <c r="F46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -1772,12 +1648,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassFraction</t>
         </is>
       </c>
-      <c r="F47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -1790,22 +1666,18 @@
           <t>IonomerCompound</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasBinder</t>
         </is>
       </c>
-      <c r="F48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -1818,22 +1690,18 @@
           <t>PerfluorosulfonicAcid</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C49" s="12" t="n"/>
       <c r="D49" s="12" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasBinder</t>
         </is>
       </c>
-      <c r="F49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -1854,12 +1722,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasBinder-hasMeasuredProperty-MassFraction</t>
         </is>
       </c>
-      <c r="F50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -1880,12 +1748,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
-      <c r="F51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
@@ -1918,12 +1786,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Porosity</t>
         </is>
       </c>
-      <c r="F53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -1944,12 +1812,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="E54" s="12" t="n"/>
+      <c r="F54" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-D50ParticleSize</t>
         </is>
       </c>
-      <c r="F54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
@@ -1974,22 +1842,18 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C56" s="4" t="n"/>
       <c r="D56" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -2002,22 +1866,18 @@
           <t>18x_Ti</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C57" s="12" t="n"/>
       <c r="D57" s="12" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-schema:productID</t>
         </is>
       </c>
-      <c r="F57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -2030,22 +1890,18 @@
           <t>Fuel Cell Store</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C58" s="4" t="n"/>
       <c r="D58" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -2056,22 +1912,18 @@
       <c r="B59" s="12" t="n">
         <v>40050001</v>
       </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C59" s="12" t="n"/>
       <c r="D59" s="12" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E59" s="12" t="n"/>
+      <c r="F59" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-schema:productID</t>
         </is>
       </c>
-      <c r="F59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -2084,22 +1936,18 @@
           <t>Fuel Cell Store</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C60" s="4" t="n"/>
       <c r="D60" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -2110,22 +1958,18 @@
       <c r="B61" s="12" t="n">
         <v>57080249</v>
       </c>
-      <c r="C61" s="12" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C61" s="12" t="n"/>
       <c r="D61" s="12" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E61" s="12" t="n"/>
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-schema:productID</t>
         </is>
       </c>
-      <c r="F61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -2138,22 +1982,18 @@
           <t>Chemours</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C62" s="4" t="n"/>
       <c r="D62" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E62" s="4" t="n"/>
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasBinder-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -2166,22 +2006,18 @@
           <t>D521CS</t>
         </is>
       </c>
-      <c r="C63" s="12" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C63" s="12" t="n"/>
       <c r="D63" s="12" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="E63" s="12" t="n"/>
+      <c r="F63" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasBinder-schema:productID</t>
         </is>
       </c>
-      <c r="F63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
@@ -2206,22 +2042,18 @@
           <t>CarbonDioxide</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-Gas</t>
         </is>
       </c>
-      <c r="F65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
@@ -2242,12 +2074,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E66" s="16" t="inlineStr">
+      <c r="E66" s="16" t="n"/>
+      <c r="F66" s="16" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F66" s="16" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -2260,22 +2092,18 @@
           <t>Argon</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C67" s="4" t="n"/>
       <c r="D67" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-Gas</t>
         </is>
       </c>
-      <c r="F67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
@@ -2296,12 +2124,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E68" s="16" t="inlineStr">
+      <c r="E68" s="16" t="n"/>
+      <c r="F68" s="16" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F68" s="16" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -2322,12 +2150,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
-      <c r="F69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
@@ -2348,12 +2176,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E70" s="16" t="inlineStr">
+      <c r="E70" s="16" t="n"/>
+      <c r="F70" s="16" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
-      <c r="F70" s="16" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
@@ -2378,22 +2206,18 @@
           <t>Water</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C72" s="4" t="n"/>
       <c r="D72" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolvent-hasConstituentA</t>
         </is>
       </c>
-      <c r="F72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
@@ -2414,12 +2238,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E73" s="16" t="inlineStr">
+      <c r="E73" s="16" t="n"/>
+      <c r="F73" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F73" s="16" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -2428,22 +2252,18 @@
         </is>
       </c>
       <c r="B74" s="4" t="n"/>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C74" s="4" t="n"/>
       <c r="D74" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
-      <c r="F74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
@@ -2462,12 +2282,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E75" s="16" t="inlineStr">
+      <c r="E75" s="16" t="n"/>
+      <c r="F75" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F75" s="16" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -2480,22 +2300,18 @@
           <t>PotassiumCarbonate</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C76" s="4" t="n"/>
       <c r="D76" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentA</t>
         </is>
       </c>
-      <c r="F76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
@@ -2516,12 +2332,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E77" s="16" t="inlineStr">
+      <c r="E77" s="16" t="n"/>
+      <c r="F77" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
-      <c r="F77" s="16" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -2530,22 +2346,18 @@
         </is>
       </c>
       <c r="B78" s="4" t="n"/>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C78" s="4" t="n"/>
       <c r="D78" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E78" s="4" t="n"/>
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentB</t>
         </is>
       </c>
-      <c r="F78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
@@ -2564,12 +2376,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E79" s="16" t="inlineStr">
+      <c r="E79" s="16" t="n"/>
+      <c r="F79" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
-      <c r="F79" s="16" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -2590,12 +2402,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-Volume</t>
         </is>
       </c>
-      <c r="F80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
@@ -2616,12 +2428,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E81" s="16" t="inlineStr">
+      <c r="E81" s="16" t="n"/>
+      <c r="F81" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
-      <c r="F81" s="16" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -2642,12 +2454,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
-      <c r="F82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="17" t="inlineStr">
@@ -2680,12 +2492,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E84" s="4" t="n"/>
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
-      <c r="F84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
@@ -2706,12 +2518,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E85" s="16" t="inlineStr">
+      <c r="E85" s="16" t="n"/>
+      <c r="F85" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-PH</t>
         </is>
       </c>
-      <c r="F85" s="16" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -2732,12 +2544,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="E86" s="4" t="n"/>
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-Density</t>
         </is>
       </c>
-      <c r="F86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
@@ -2758,12 +2570,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E87" s="16" t="inlineStr">
+      <c r="E87" s="16" t="n"/>
+      <c r="F87" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-CelsiusTemperature</t>
         </is>
       </c>
-      <c r="F87" s="16" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="17" t="inlineStr">
@@ -2788,22 +2600,18 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C89" s="4" t="n"/>
       <c r="D89" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="16" t="inlineStr">
@@ -2816,22 +2624,18 @@
           <t>KCl_1M_catholyte</t>
         </is>
       </c>
-      <c r="C90" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C90" s="16" t="n"/>
       <c r="D90" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E90" s="16" t="inlineStr">
+      <c r="E90" s="16" t="n"/>
+      <c r="F90" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-schema:productID</t>
         </is>
       </c>
-      <c r="F90" s="16" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -2840,22 +2644,18 @@
         </is>
       </c>
       <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C91" s="4" t="n"/>
       <c r="D91" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E91" s="4" t="n"/>
+      <c r="F91" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolventA-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="16" t="inlineStr">
@@ -2864,22 +2664,18 @@
         </is>
       </c>
       <c r="B92" s="16" t="n"/>
-      <c r="C92" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C92" s="16" t="n"/>
       <c r="D92" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E92" s="16" t="inlineStr">
+      <c r="E92" s="16" t="n"/>
+      <c r="F92" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolventA-schema:productID</t>
         </is>
       </c>
-      <c r="F92" s="16" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -2888,22 +2684,18 @@
         </is>
       </c>
       <c r="B93" s="4" t="n"/>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C93" s="4" t="n"/>
       <c r="D93" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolventB-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="16" t="inlineStr">
@@ -2912,22 +2704,18 @@
         </is>
       </c>
       <c r="B94" s="16" t="n"/>
-      <c r="C94" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C94" s="16" t="n"/>
       <c r="D94" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E94" s="16" t="inlineStr">
+      <c r="E94" s="16" t="n"/>
+      <c r="F94" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolventB-schema:productID</t>
         </is>
       </c>
-      <c r="F94" s="16" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -2940,22 +2728,18 @@
           <t>Thermo Fisher Scientific</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C95" s="4" t="n"/>
       <c r="D95" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E95" s="4" t="n"/>
+      <c r="F95" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSoluteA-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="16" t="inlineStr">
@@ -2966,22 +2750,18 @@
       <c r="B96" s="16" t="n">
         <v>424090010</v>
       </c>
-      <c r="C96" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C96" s="16" t="n"/>
       <c r="D96" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E96" s="16" t="inlineStr">
+      <c r="E96" s="16" t="n"/>
+      <c r="F96" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSoluteA-schema:productID</t>
         </is>
       </c>
-      <c r="F96" s="16" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -2990,22 +2770,18 @@
         </is>
       </c>
       <c r="B97" s="4" t="n"/>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C97" s="4" t="n"/>
       <c r="D97" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="E97" s="4" t="n"/>
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSoluteB-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="16" t="inlineStr">
@@ -3014,22 +2790,18 @@
         </is>
       </c>
       <c r="B98" s="16" t="n"/>
-      <c r="C98" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C98" s="16" t="n"/>
       <c r="D98" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E98" s="16" t="inlineStr">
+      <c r="E98" s="16" t="n"/>
+      <c r="F98" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSoluteB-schema:productID</t>
         </is>
       </c>
-      <c r="F98" s="16" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="14" t="inlineStr">
@@ -3054,22 +2826,18 @@
           <t>Nitrogen</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C100" s="4" t="n"/>
       <c r="D100" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-Gas</t>
         </is>
       </c>
-      <c r="F100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="16" t="inlineStr">
@@ -3090,12 +2858,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E101" s="16" t="inlineStr">
+      <c r="E101" s="16" t="n"/>
+      <c r="F101" s="16" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F101" s="16" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -3104,22 +2872,18 @@
         </is>
       </c>
       <c r="B102" s="4" t="n"/>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C102" s="4" t="n"/>
       <c r="D102" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
+      <c r="E102" s="4" t="n"/>
+      <c r="F102" s="4" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-Gas</t>
         </is>
       </c>
-      <c r="F102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="16" t="inlineStr">
@@ -3138,12 +2902,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E103" s="16" t="inlineStr">
+      <c r="E103" s="16" t="n"/>
+      <c r="F103" s="16" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F103" s="16" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -3164,12 +2928,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
-      <c r="F104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="16" t="inlineStr">
@@ -3190,12 +2954,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E105" s="16" t="inlineStr">
+      <c r="E105" s="16" t="n"/>
+      <c r="F105" s="16" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
-      <c r="F105" s="16" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
@@ -3220,22 +2984,18 @@
           <t>Water</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C107" s="4" t="n"/>
       <c r="D107" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-hasConstituentA</t>
         </is>
       </c>
-      <c r="F107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="16" t="inlineStr">
@@ -3256,12 +3016,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E108" s="16" t="inlineStr">
+      <c r="E108" s="16" t="n"/>
+      <c r="F108" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F108" s="16" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -3270,22 +3030,18 @@
         </is>
       </c>
       <c r="B109" s="4" t="n"/>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C109" s="4" t="n"/>
       <c r="D109" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
+      <c r="E109" s="4" t="n"/>
+      <c r="F109" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
-      <c r="F109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="16" t="inlineStr">
@@ -3304,12 +3060,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E110" s="16" t="inlineStr">
+      <c r="E110" s="16" t="n"/>
+      <c r="F110" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F110" s="16" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -3322,22 +3078,18 @@
           <t>SulfuricAcid</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C111" s="4" t="n"/>
       <c r="D111" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentA</t>
         </is>
       </c>
-      <c r="F111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="16" t="inlineStr">
@@ -3358,12 +3110,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E112" s="16" t="inlineStr">
+      <c r="E112" s="16" t="n"/>
+      <c r="F112" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
-      <c r="F112" s="16" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -3372,22 +3124,18 @@
         </is>
       </c>
       <c r="B113" s="4" t="n"/>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C113" s="4" t="n"/>
       <c r="D113" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
+      <c r="E113" s="4" t="n"/>
+      <c r="F113" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentB</t>
         </is>
       </c>
-      <c r="F113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="16" t="inlineStr">
@@ -3406,12 +3154,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E114" s="16" t="inlineStr">
+      <c r="E114" s="16" t="n"/>
+      <c r="F114" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
-      <c r="F114" s="16" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -3432,12 +3180,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
+      <c r="E115" s="4" t="n"/>
+      <c r="F115" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-Volume</t>
         </is>
       </c>
-      <c r="F115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="16" t="inlineStr">
@@ -3458,12 +3206,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E116" s="16" t="inlineStr">
+      <c r="E116" s="16" t="n"/>
+      <c r="F116" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
-      <c r="F116" s="16" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -3484,12 +3232,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
+      <c r="E117" s="4" t="n"/>
+      <c r="F117" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
-      <c r="F117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="17" t="inlineStr">
@@ -3522,12 +3270,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
+      <c r="E119" s="4" t="n"/>
+      <c r="F119" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
-      <c r="F119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="16" t="inlineStr">
@@ -3548,12 +3296,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E120" s="16" t="inlineStr">
+      <c r="E120" s="16" t="n"/>
+      <c r="F120" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-PH</t>
         </is>
       </c>
-      <c r="F120" s="16" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -3574,12 +3322,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
+      <c r="E121" s="4" t="n"/>
+      <c r="F121" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-Density</t>
         </is>
       </c>
-      <c r="F121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="16" t="inlineStr">
@@ -3600,12 +3348,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E122" s="16" t="inlineStr">
+      <c r="E122" s="16" t="n"/>
+      <c r="F122" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-CelsiusTemperature</t>
         </is>
       </c>
-      <c r="F122" s="16" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="17" t="inlineStr">
@@ -3630,22 +3378,18 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C124" s="4" t="n"/>
       <c r="D124" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
+      <c r="E124" s="4" t="n"/>
+      <c r="F124" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="16" t="inlineStr">
@@ -3658,22 +3402,18 @@
           <t>H2SO4_1M_anolyte</t>
         </is>
       </c>
-      <c r="C125" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C125" s="16" t="n"/>
       <c r="D125" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E125" s="16" t="inlineStr">
+      <c r="E125" s="16" t="n"/>
+      <c r="F125" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-schema:productID</t>
         </is>
       </c>
-      <c r="F125" s="16" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -3682,22 +3422,18 @@
         </is>
       </c>
       <c r="B126" s="4" t="n"/>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C126" s="4" t="n"/>
       <c r="D126" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
+      <c r="E126" s="4" t="n"/>
+      <c r="F126" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="16" t="inlineStr">
@@ -3706,22 +3442,18 @@
         </is>
       </c>
       <c r="B127" s="16" t="n"/>
-      <c r="C127" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C127" s="16" t="n"/>
       <c r="D127" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E127" s="16" t="inlineStr">
+      <c r="E127" s="16" t="n"/>
+      <c r="F127" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-schema:productID</t>
         </is>
       </c>
-      <c r="F127" s="16" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -3730,22 +3462,18 @@
         </is>
       </c>
       <c r="B128" s="4" t="n"/>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C128" s="4" t="n"/>
       <c r="D128" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
+      <c r="E128" s="4" t="n"/>
+      <c r="F128" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="16" t="inlineStr">
@@ -3754,22 +3482,18 @@
         </is>
       </c>
       <c r="B129" s="16" t="n"/>
-      <c r="C129" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C129" s="16" t="n"/>
       <c r="D129" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E129" s="16" t="inlineStr">
+      <c r="E129" s="16" t="n"/>
+      <c r="F129" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-schema:productID</t>
         </is>
       </c>
-      <c r="F129" s="16" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -3782,22 +3506,18 @@
           <t>Millipore Sigma</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C130" s="4" t="n"/>
       <c r="D130" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
+      <c r="E130" s="4" t="n"/>
+      <c r="F130" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="16" t="inlineStr">
@@ -3808,22 +3528,18 @@
       <c r="B131" s="16" t="n">
         <v>258105</v>
       </c>
-      <c r="C131" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C131" s="16" t="n"/>
       <c r="D131" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E131" s="16" t="inlineStr">
+      <c r="E131" s="16" t="n"/>
+      <c r="F131" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-schema:productID</t>
         </is>
       </c>
-      <c r="F131" s="16" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -3832,22 +3548,18 @@
         </is>
       </c>
       <c r="B132" s="4" t="n"/>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C132" s="4" t="n"/>
       <c r="D132" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
+      <c r="E132" s="4" t="n"/>
+      <c r="F132" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="16" t="inlineStr">
@@ -3856,22 +3568,18 @@
         </is>
       </c>
       <c r="B133" s="16" t="n"/>
-      <c r="C133" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C133" s="16" t="n"/>
       <c r="D133" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E133" s="16" t="inlineStr">
+      <c r="E133" s="16" t="n"/>
+      <c r="F133" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-schema:productID</t>
         </is>
       </c>
-      <c r="F133" s="16" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -3896,22 +3604,18 @@
           <t>IonExchangeMembrane</t>
         </is>
       </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C135" s="4" t="n"/>
       <c r="D135" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
+      <c r="E135" s="4" t="n"/>
+      <c r="F135" s="4" t="inlineStr">
         <is>
           <t>hasSeparator</t>
         </is>
       </c>
-      <c r="F135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -3924,22 +3628,18 @@
           <t>BilayerMembrane</t>
         </is>
       </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C136" s="5" t="n"/>
       <c r="D136" s="5" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E136" s="5" t="inlineStr">
+      <c r="E136" s="5" t="n"/>
+      <c r="F136" s="5" t="inlineStr">
         <is>
           <t>hasSeparator</t>
         </is>
       </c>
-      <c r="F136" s="5" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -3952,22 +3652,18 @@
           <t>AnionExchangeMembrane</t>
         </is>
       </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C137" s="4" t="n"/>
       <c r="D137" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
+      <c r="E137" s="4" t="n"/>
+      <c r="F137" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA</t>
         </is>
       </c>
-      <c r="F137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -3980,22 +3676,18 @@
           <t>PolyArylPiperidinium</t>
         </is>
       </c>
-      <c r="C138" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C138" s="5" t="n"/>
       <c r="D138" s="5" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E138" s="5" t="inlineStr">
+      <c r="E138" s="5" t="n"/>
+      <c r="F138" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA</t>
         </is>
       </c>
-      <c r="F138" s="5" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -4016,12 +3708,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
+      <c r="E139" s="4" t="n"/>
+      <c r="F139" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
-      <c r="F139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -4042,12 +3734,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E140" s="5" t="inlineStr">
+      <c r="E140" s="5" t="n"/>
+      <c r="F140" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
-      <c r="F140" s="5" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -4060,22 +3752,18 @@
           <t>CationExchangeMembrane</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C141" s="4" t="n"/>
       <c r="D141" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
+      <c r="E141" s="4" t="n"/>
+      <c r="F141" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB</t>
         </is>
       </c>
-      <c r="F141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -4088,22 +3776,18 @@
           <t>PerfluorosulfonicAcid</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C142" s="5" t="n"/>
       <c r="D142" s="5" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E142" s="5" t="inlineStr">
+      <c r="E142" s="5" t="n"/>
+      <c r="F142" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB</t>
         </is>
       </c>
-      <c r="F142" s="5" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -4124,12 +3808,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
+      <c r="E143" s="4" t="n"/>
+      <c r="F143" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
-      <c r="F143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -4150,12 +3834,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E144" s="5" t="inlineStr">
+      <c r="E144" s="5" t="n"/>
+      <c r="F144" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
-      <c r="F144" s="5" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -4188,12 +3872,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
+      <c r="E146" s="4" t="n"/>
+      <c r="F146" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
-      <c r="F146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
@@ -4214,12 +3898,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E147" s="5" t="inlineStr">
+      <c r="E147" s="5" t="n"/>
+      <c r="F147" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
-      <c r="F147" s="5" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -4244,22 +3928,18 @@
           <t>Fuel Cell Store</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C149" s="4" t="n"/>
       <c r="D149" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
+      <c r="E149" s="4" t="n"/>
+      <c r="F149" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -4270,22 +3950,18 @@
       <c r="B150" s="5" t="n">
         <v>72010015</v>
       </c>
-      <c r="C150" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C150" s="5" t="n"/>
       <c r="D150" s="5" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E150" s="5" t="inlineStr">
+      <c r="E150" s="5" t="n"/>
+      <c r="F150" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA-schema:productID</t>
         </is>
       </c>
-      <c r="F150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -4298,22 +3974,18 @@
           <t>Chemours</t>
         </is>
       </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C151" s="4" t="n"/>
       <c r="D151" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
+      <c r="E151" s="4" t="n"/>
+      <c r="F151" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -4326,22 +3998,18 @@
           <t>N117</t>
         </is>
       </c>
-      <c r="C152" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C152" s="5" t="n"/>
       <c r="D152" s="5" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E152" s="5" t="inlineStr">
+      <c r="E152" s="5" t="n"/>
+      <c r="F152" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB-schema:productID</t>
         </is>
       </c>
-      <c r="F152" s="5" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -4366,22 +4034,18 @@
           <t>FlowCell</t>
         </is>
       </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C154" s="4" t="n"/>
       <c r="D154" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
+      <c r="E154" s="4" t="n"/>
+      <c r="F154" s="4" t="inlineStr">
         <is>
           <t>hasCase</t>
         </is>
       </c>
-      <c r="F154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
@@ -4394,22 +4058,18 @@
           <t>FlowField</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C155" s="5" t="n"/>
       <c r="D155" s="5" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E155" s="5" t="inlineStr">
+      <c r="E155" s="5" t="n"/>
+      <c r="F155" s="5" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasComponent</t>
         </is>
       </c>
-      <c r="F155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -4430,12 +4090,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
+      <c r="E156" s="4" t="n"/>
+      <c r="F156" s="4" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasMeasuredProperty-Width</t>
         </is>
       </c>
-      <c r="F156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -4456,12 +4116,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E157" s="5" t="inlineStr">
+      <c r="E157" s="5" t="n"/>
+      <c r="F157" s="5" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasMeasuredProperty-Area</t>
         </is>
       </c>
-      <c r="F157" s="5" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -4482,12 +4142,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
+      <c r="E158" s="4" t="n"/>
+      <c r="F158" s="4" t="inlineStr">
         <is>
           <t>hasComponentB-type|CatholyteCompartment-hasMeasuredProperty-Width</t>
         </is>
       </c>
-      <c r="F158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -4508,12 +4168,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E159" s="5" t="inlineStr">
+      <c r="E159" s="5" t="n"/>
+      <c r="F159" s="5" t="inlineStr">
         <is>
           <t>hasComponentB-type|CatholyteCompartment-hasMeasuredProperty-Volume</t>
         </is>
       </c>
-      <c r="F159" s="5" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -4526,22 +4186,18 @@
           <t>SilverChlorideElectrode</t>
         </is>
       </c>
-      <c r="C160" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C160" s="4" t="n"/>
       <c r="D160" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E160" s="4" t="inlineStr">
+      <c r="E160" s="4" t="n"/>
+      <c r="F160" s="4" t="inlineStr">
         <is>
           <t>hasComponentB-type|CatholyteCompartment-hasReferenceElectrode</t>
         </is>
       </c>
-      <c r="F160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
@@ -4562,12 +4218,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E161" s="5" t="inlineStr">
+      <c r="E161" s="5" t="n"/>
+      <c r="F161" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasMeasuredProperty-Area</t>
         </is>
       </c>
-      <c r="F161" s="5" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -4588,12 +4244,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E162" s="4" t="inlineStr">
+      <c r="E162" s="4" t="n"/>
+      <c r="F162" s="4" t="inlineStr">
         <is>
           <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Volume</t>
         </is>
       </c>
-      <c r="F162" s="4" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
@@ -4614,12 +4270,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E163" s="5" t="inlineStr">
+      <c r="E163" s="5" t="n"/>
+      <c r="F163" s="5" t="inlineStr">
         <is>
           <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Width</t>
         </is>
       </c>
-      <c r="F163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -4632,22 +4288,18 @@
           <t>SilverChlorideElectrode</t>
         </is>
       </c>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C164" s="4" t="n"/>
       <c r="D164" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E164" s="4" t="inlineStr">
+      <c r="E164" s="4" t="n"/>
+      <c r="F164" s="4" t="inlineStr">
         <is>
           <t>hasComponentC-type|AnolyteCompartment-hasReferenceElectrode</t>
         </is>
       </c>
-      <c r="F164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
@@ -4668,12 +4320,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E165" s="5" t="inlineStr">
+      <c r="E165" s="5" t="n"/>
+      <c r="F165" s="5" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasMeasuredProperty-Area</t>
         </is>
       </c>
-      <c r="F165" s="5" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -4694,12 +4346,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E166" s="4" t="inlineStr">
+      <c r="E166" s="4" t="n"/>
+      <c r="F166" s="4" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasMeasuredProperty-Width</t>
         </is>
       </c>
-      <c r="F166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
@@ -4712,22 +4364,18 @@
           <t>FlowField</t>
         </is>
       </c>
-      <c r="C167" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C167" s="5" t="n"/>
       <c r="D167" s="5" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E167" s="5" t="inlineStr">
+      <c r="E167" s="5" t="n"/>
+      <c r="F167" s="5" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasComponent</t>
         </is>
       </c>
-      <c r="F167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -4748,12 +4396,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E168" s="4" t="inlineStr">
+      <c r="E168" s="4" t="n"/>
+      <c r="F168" s="4" t="inlineStr">
         <is>
           <t>hasComponentE-type|CatholyteTank-hasMeasuredProperty-Volume</t>
         </is>
       </c>
-      <c r="F168" s="4" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
@@ -4774,12 +4422,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E169" s="5" t="inlineStr">
+      <c r="E169" s="5" t="n"/>
+      <c r="F169" s="5" t="inlineStr">
         <is>
           <t>hasComponentF-type|AnolyteTank-hasMeasuredProperty-Volume</t>
         </is>
       </c>
-      <c r="F169" s="5" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="18" t="inlineStr">
@@ -4804,22 +4452,18 @@
           <t>Fuel Cell Store</t>
         </is>
       </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C171" s="4" t="n"/>
       <c r="D171" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E171" s="4" t="inlineStr">
+      <c r="E171" s="4" t="n"/>
+      <c r="F171" s="4" t="inlineStr">
         <is>
           <t>hasCase-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -4832,22 +4476,18 @@
           <t>Micro Flow Cell</t>
         </is>
       </c>
-      <c r="C172" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C172" s="5" t="n"/>
       <c r="D172" s="5" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E172" s="5" t="inlineStr">
+      <c r="E172" s="5" t="n"/>
+      <c r="F172" s="5" t="inlineStr">
         <is>
           <t>hasCase-schema:productID</t>
         </is>
       </c>
-      <c r="F172" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5311,22 +4951,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Term</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>IRI</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
@@ -5428,20 +5074,20 @@
   <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="74" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Predicate</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Default class</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -5728,7 +5374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B127"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5755,56 +5401,56 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Classes available to the @Schema sheet Value column. Classes must already exist in the ontology. You can declare your own custom classes in the @Context sheet. This column is a reference list, a value already known to the ontology works even if it is not listed.</t>
+          <t>Cell and device types. Classes available to the @Schema sheet Value column. Classes must already exist in the ontology. You can declare your own custom classes in the @Context sheet. This column is a reference list, a value already known to the ontology works even if it is not listed.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ElectrochemicalHalfCell</t>
+          <t>ElectrolyticCell</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BatteryCell</t>
+          <t>ElectrochemicalHalfCell</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ElectrolyticCell</t>
+          <t>BatteryCell</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FlowCell</t>
+          <t>CoinCell</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R2032</t>
+          <t>FlowCell</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CoinCell</t>
+          <t>ThreeElectrodeCellDevice</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ThreeElectrodeCellDevice</t>
+          <t>R2032</t>
         </is>
       </c>
     </row>
@@ -5815,6 +5461,11 @@
           <t>Component</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cell components and compartments</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5847,21 +5498,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FlowField</t>
+          <t>GasCompartment</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GasCompartment</t>
+          <t>NegativeElectrodeGasCompartment</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>requested</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NegativeElectrodeGasCompartment</t>
+          <t>PositiveElectrodeGasCompartment</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5873,12 +5529,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PositiveElectrodeGasCompartment</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>requested</t>
+          <t>FlowField</t>
         </is>
       </c>
     </row>
@@ -5889,6 +5540,11 @@
           <t>Electrode</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Electrodes</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5965,6 +5621,11 @@
           <t>Substrate</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Substrates and structures</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5976,33 +5637,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ElectrospunMesh</t>
+          <t>Mesh</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>requested</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ExpandedMesh</t>
+          <t>WovenMesh</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>WovenMesh</t>
+          <t>ExpandedMesh</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>requested</t>
+          <t>ElectrospunMesh</t>
         </is>
       </c>
     </row>
@@ -6027,20 +5688,25 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Solid</t>
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Metals and elemental substances</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6066,445 +5732,452 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CopperOxideCompound</t>
+          <t>Graphite</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Electrocatalyst</t>
+          <t>Lithium</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Nickel</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IridiumOxideCompound</t>
+          <t>Platinum</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IridiumIIIOxide</t>
+          <t>Silver</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IridiumDioxide</t>
+          <t>StainlessSteel</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Tantalum</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LithiumIronPhosphate</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>https://pubchem.ncbi.nlm.nih.gov/substance/485083898</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>LithiumNickelManganeseCobaltOxide</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>https://pubchem.ncbi.nlm.nih.gov/substance/485083898</t>
-        </is>
-      </c>
-    </row>
+          <t>Titanium</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LithiumTitanate</t>
+          <t>Electrocatalyst</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Catalysts and metal oxides</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>CopperOxideCompound</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>IridiumOxideCompound</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>IridiumIIIOxide</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>StainlessSteel</t>
+          <t>IridiumDioxide</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tantalum</t>
+          <t>TantalumOxideCompound</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TantalumOxideCompound</t>
+          <t>TitaniumOxideCompound</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>TitaniumIIOxide</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TitaniumOxideCompound</t>
+          <t>TitaniumIIIOxide</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TitaniumIIOxide</t>
+          <t>LithiumIronPhosphate</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://pubchem.ncbi.nlm.nih.gov/substance/485083898</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TitaniumIIIOxide</t>
-        </is>
-      </c>
-    </row>
-    <row r="67"/>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Separator</t>
-        </is>
-      </c>
-    </row>
+          <t>LithiumNickelManganeseCobaltOxide</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://pubchem.ncbi.nlm.nih.gov/substance/485083898</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>LithiumTitanate</t>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GlassFibreSeparator</t>
+          <t>Separator</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Separators and membranes</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IonExchangeMembrane</t>
+          <t>GlassFibreSeparator</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AnionExchangeMembrane</t>
+          <t>IonExchangeMembrane</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CationExchangeMembrane</t>
+          <t>AnionExchangeMembrane</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BilayerMembrane</t>
+          <t>CationExchangeMembrane</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>IonomerCompound</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>PerfluorocarboxylicAcid</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Flemion by AGC (CEM), Aciplex by Asahi Kasei (CEM), requested</t>
-        </is>
-      </c>
-    </row>
+          <t>BilayerMembrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PerfluorosulfonicAcid</t>
+          <t>IonomerCompound</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nafion by Chemours (long side-chain CEM), Aquivion by Solvay (short side-chain CEM), Fumapem SF by Fumatech (short side-chain CEM), Fumasep F by Fumatech)</t>
+          <t>Membrane and binder polymers</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PolyAryleneImidazolium</t>
+          <t>PerfluorocarboxylicAcid</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Aemion+ by Ionomr (AEM). AF1 by Ionomr (AEM), requested</t>
+          <t>Flemion by AGC (CEM), Aciplex by Asahi Kasei (CEM), requested</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PolyArylPiperidinium</t>
+          <t>PerfluorosulfonicAcid</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Piperion by Versogen (AEM), requested</t>
+          <t>Nafion by Chemours (long side-chain CEM), Aquivion by Solvay (short side-chain CEM), Fumapem SF by Fumatech (short side-chain CEM), Fumasep F by Fumatech)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PolyArylAmmonium</t>
+          <t>PolyAryleneImidazolium</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Fumasep FAA by Fumatech (AEM)</t>
+          <t>Aemion+ by Ionomr (AEM). AF1 by Ionomr (AEM), requested</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PolyetherEtherKetone</t>
+          <t>PolyArylPiperidinium</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Victrex by Solvay (PEEK), Ketaspire by Evonik (PEEK), Radel by Solvay (PEEK), requested</t>
+          <t>Piperion by Versogen (AEM), requested</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Polyolefin</t>
+          <t>PolyArylAmmonium</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Fumasep FAA by Fumatech (AEM)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Polypropylene</t>
+          <t>PolyetherEtherKetone</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Celgard by Polypore International now part of Asahi Kasei (PP)</t>
+          <t>Victrex by Solvay (PEEK), Ketaspire by Evonik (PEEK), Radel by Solvay (PEEK), requested</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Polytetrafluoroethylene</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Teflon by Chemours (PTFE), Polyflon by Daikin (PTFE),</t>
+          <t>Polyolefin</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PolyvinylideneFluoride</t>
+          <t>Polypropylene</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Kynar by Arkema (PVDF), Solef by Solvay (PVDF)</t>
+          <t>Celgard by Polypore International now part of Asahi Kasei (PP)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>QuaternaryAmmoniumPolySulfone</t>
+          <t>Polytetrafluoroethylene</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sustainion by Dioxide Materials (AEM), requested</t>
+          <t>Teflon by Chemours (PTFE), Polyflon by Daikin (PTFE),</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SulfonatedPolyEtherEtherKetone</t>
+          <t>PolyvinylideneFluoride</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Speek by Gore (CEM), requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="87"/>
+          <t>Kynar by Arkema (PVDF), Solef by Solvay (PVDF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>QuaternaryAmmoniumPolySulfone</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sustainion by Dioxide Materials (AEM), requested</t>
+        </is>
+      </c>
+    </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Electrolyte</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>LiquidElectrolyte</t>
-        </is>
-      </c>
-    </row>
+          <t>SulfonatedPolyEtherEtherKetone</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Speek by Gore (CEM), requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SolidElectrolyte</t>
+          <t>Electrolyte</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Electrolytes and solvents</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EthyleneCarbonate</t>
+          <t>LiquidElectrolyte</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EthylMethylCarbonate</t>
+          <t>SolidElectrolyte</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LithiumBisfluorosulfonylimide</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LithiumHexafluorophosphate</t>
+          <t>Methanol</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SodiumChloride</t>
+          <t>Ethanol</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SodiumHydroxide</t>
+          <t>EthyleneCarbonate</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PhosphoricAcid</t>
+          <t>EthylMethylCarbonate</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PotassiumCarbonate</t>
+          <t>VinyleneCarbonate</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SulfuricAcid</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
           <t>TrisTrimethylsilyPhosphite</t>
         </is>
       </c>
     </row>
+    <row r="100"/>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>VinyleneCarbonate</t>
+          <t>SulfuricAcid</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Acids, bases and salts</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>PhosphoricAcid</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6191,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PotassiumChloride</t>
+          <t>SodiumHydroxide</t>
         </is>
       </c>
     </row>
@@ -6532,76 +6205,81 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>PotassiumCarbonate</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ethanol</t>
-        </is>
-      </c>
-    </row>
-    <row r="108"/>
+          <t>PotassiumChloride</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SodiumChloride</t>
+        </is>
+      </c>
+    </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>LithiumBisfluorosulfonylimide</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GasMixture</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Argon</t>
-        </is>
-      </c>
-    </row>
+          <t>LithiumHexafluorophosphate</t>
+        </is>
+      </c>
+    </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Gases</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CarbonDioxide</t>
+          <t>GasMixture</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Nitrogen</t>
+          <t>Air</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>requested</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Argon</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CarbonMonoxide</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>requested</t>
+          <t>Nitrogen</t>
         </is>
       </c>
     </row>
@@ -6615,39 +6293,40 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ethylene</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>requested</t>
+          <t>Hydrogen</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Air</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
+          <t>CarbonDioxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>CarbonMonoxide</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
         <is>
           <t>requested</t>
         </is>
       </c>
     </row>
-    <row r="120"/>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Ammonia</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>Ethylene</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6656,41 +6335,66 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Purity</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
-    </row>
+    <row r="123"/>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Porosity</t>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Measured property types, for the Ontology link column rather than Value</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Tortuosity</t>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>requested</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Thickness</t>
+          <t>Purity</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>requested</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
+        <is>
+          <t>Porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Tortuosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>Width</t>
         </is>
@@ -6711,7 +6415,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="74" customWidth="1" min="4" max="4"/>
   </cols>
@@ -6724,7 +6428,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Class</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -7429,22 +7133,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Unit class</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -5508,21 +5508,11 @@
           <t>NegativeElectrodeGasCompartment</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
           <t>PositiveElectrodeGasCompartment</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>requested</t>
         </is>
       </c>
     </row>
@@ -5594,11 +5584,6 @@
           <t>MercuryOxideElectrode</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5640,11 +5625,6 @@
           <t>Mesh</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5860,21 +5840,11 @@
           <t>LithiumIronPhosphate</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>https://pubchem.ncbi.nlm.nih.gov/substance/485083898</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
           <t>LithiumNickelManganeseCobaltOxide</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>https://pubchem.ncbi.nlm.nih.gov/substance/485083898</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5924,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Flemion by AGC (CEM), Aciplex by Asahi Kasei (CEM), requested</t>
+          <t>Flemion by AGC (CEM), Aciplex by Asahi Kasei (CEM)</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5948,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Aemion+ by Ionomr (AEM). AF1 by Ionomr (AEM), requested</t>
+          <t>Aemion+ by Ionomr (AEM). AF1 by Ionomr (AEM)</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5960,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Piperion by Versogen (AEM), requested</t>
+          <t>Piperion by Versogen (AEM)</t>
         </is>
       </c>
     </row>
@@ -6014,7 +5984,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Victrex by Solvay (PEEK), Ketaspire by Evonik (PEEK), Radel by Solvay (PEEK), requested</t>
+          <t>Victrex by Solvay (PEEK), Ketaspire by Evonik (PEEK), Radel by Solvay (PEEK)</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6039,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sustainion by Dioxide Materials (AEM), requested</t>
+          <t>Sustainion by Dioxide Materials (AEM)</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6051,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Speek by Gore (CEM), requested</t>
+          <t>Speek by Gore (CEM)</t>
         </is>
       </c>
     </row>
@@ -6263,11 +6233,6 @@
           <t>Air</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6310,11 +6275,6 @@
           <t>CarbonMonoxide</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6327,11 +6287,6 @@
       <c r="A122" t="inlineStr">
         <is>
           <t>Ethylene</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>requested</t>
         </is>
       </c>
     </row>
@@ -6354,21 +6309,11 @@
           <t>PH</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
           <t>Purity</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>requested</t>
         </is>
       </c>
     </row>
@@ -6586,12 +6531,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>schema:Organization</t>
+          <t>schema:ResearchOrganization</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q683116</t>
+          <t>http://www.wikidata.org/entity/Q683116</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -6608,12 +6553,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>schema:Organization</t>
+          <t>schema:ResearchOrganization</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q262760</t>
+          <t>http://www.wikidata.org/entity/Q262760</t>
         </is>
       </c>
     </row>
@@ -6625,12 +6570,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>schema:Organization</t>
+          <t>schema:ResearchOrganization</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q11942</t>
+          <t>http://www.wikidata.org/entity/Q11942</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6592,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q367032</t>
+          <t>http://www.wikidata.org/entity/Q367032</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6669,7 +6614,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q310172</t>
+          <t>http://www.wikidata.org/entity/Q310172</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6691,7 +6636,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q122199856</t>
+          <t>http://www.wikidata.org/entity/Q122199856</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -6713,7 +6658,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q15829006</t>
+          <t>http://www.wikidata.org/entity/Q15829006</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6735,7 +6680,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q120784603</t>
+          <t>http://www.wikidata.org/entity/Q120784603</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -6757,7 +6702,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q879878</t>
+          <t>http://www.wikidata.org/entity/Q879878</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -6779,12 +6724,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q27868725</t>
+          <t>http://www.wikidata.org/entity/Q27868725</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fuel Cell Store; US-based distributor of membrane electrode assemblies, GDLs and ion exchange membranes including Sustainion, PiperION and Nafion. https://www.fuelcellstore.com. to be requested</t>
+          <t>Fuel Cell Store; US-based distributor of membrane electrode assemblies, GDLs and ion exchange membranes including Sustainion, PiperION and Nafion. https://www.fuelcellstore.com</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6746,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q21449964</t>
+          <t>http://www.wikidata.org/entity/Q21449964</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6823,12 +6768,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1669719</t>
+          <t>http://www.wikidata.org/entity/Q1669719</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MilliporeSigma (Merck KGaA subsidiary, US operations); supplier of high-purity electrolyte chemicals and reagents for research. https://www.sigmaaldrich.com. to be requested</t>
+          <t>MilliporeSigma (Merck KGaA subsidiary, US operations); supplier of high-purity electrolyte chemicals and reagents for research. https://www.sigmaaldrich.com</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6790,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q2361947</t>
+          <t>http://www.wikidata.org/entity/Q2361947</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6867,7 +6812,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q487209</t>
+          <t>http://www.wikidata.org/entity/Q487209</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -6889,7 +6834,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q30285492</t>
+          <t>http://www.wikidata.org/entity/Q30285492</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6911,7 +6856,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q306455</t>
+          <t>http://www.wikidata.org/entity/Q306455</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -6933,7 +6878,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q908461</t>
+          <t>http://www.wikidata.org/entity/Q908461</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6955,12 +6900,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q30254565</t>
+          <t>http://www.wikidata.org/entity/Q30254565</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FuMA-Tech GmbH; manufacturer of FAA-3-50 and FAP-375-PP AEM series, Fumapem F/SF CEM series, and FBM bipolar membrane. https://www.fumatech.com. to be requested</t>
+          <t>FuMA-Tech GmbH; manufacturer of FAA-3-50 and FAP-375-PP AEM series, Fumapem F/SF CEM series, and FBM bipolar membrane. https://www.fumatech.com</t>
         </is>
       </c>
     </row>
@@ -6977,12 +6922,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q138027768</t>
+          <t>http://www.wikidata.org/entity/Q138782243</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Hohsen Corp.; Japanese manufacturer of specialty separators and ion exchange membranes for electrochemical applications. to be requested</t>
+          <t>Hohsen Corp.; Japanese manufacturer of specialty separators and ion exchange membranes for electrochemical applications</t>
         </is>
       </c>
     </row>

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Organisation that made the cell, value should be in @classes with ID</t>
+          <t>Organisation that made the cell. List it in @Individuals to give it an IRI.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Person that made the cell, value should be in @classes with ID</t>
+          <t>Person that made the cell. List them in @Individuals to give them an ORCID.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -4513,7 +4513,17 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>References</t>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Extra values  -&gt;  affiliations for an author, a description for a data file, or more items for a list</t>
         </is>
       </c>
     </row>

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -8,10 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Schema" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@References" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Individuals" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,8 +525,8 @@
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="160" customWidth="1" min="5" max="5"/>
-    <col width="74" customWidth="1" min="6" max="6"/>
+    <col width="74" customWidth="1" min="5" max="5"/>
+    <col width="160" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -550,12 +552,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Ontology link</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
         </is>
       </c>
     </row>
@@ -582,11 +584,7 @@
           <t>ElectrolyticCell</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C3" s="4" t="n"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -594,12 +592,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
+          <t>Required, do not change</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>type|</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Required, do not change</t>
         </is>
       </c>
     </row>
@@ -614,11 +612,7 @@
           <t>empa__ecid_000001</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -626,12 +620,12 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>Unique ID for cell</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>schema:productID</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Unique ID for cell</t>
         </is>
       </c>
     </row>
@@ -646,11 +640,7 @@
           <t>240616_bco_gr-NMC_01</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -658,12 +648,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>Human-friendly name for the cell</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>schema:name</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Human-friendly name for the cell</t>
         </is>
       </c>
     </row>
@@ -678,11 +668,7 @@
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -690,12 +676,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>Assembly date in ISO8601 format (YYYY-MM-DD)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>schema:dateCreated</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Assembly date in ISO8601 format (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -710,11 +696,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -722,12 +704,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
+          <t>Organisation that made the cell. List it in @Individuals to give it an IRI.</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>schema:manufacturer</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Organisation that made the cell, value should be in @classes with ID</t>
         </is>
       </c>
     </row>
@@ -742,11 +724,7 @@
           <t>Corsin Battaglia</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -754,12 +732,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>Person that made the cell. List them in @Individuals to give them an ORCID.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>schema:creator</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Person that made the cell, value should be in @classes with ID</t>
         </is>
       </c>
     </row>
@@ -774,22 +752,18 @@
           <t>ETHB PREMISE/NCCR Catalysis</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>rdfs:comment</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -802,22 +776,18 @@
           <t>manually</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>rdfs:comment</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -830,11 +800,7 @@
           <t>ElectrolysisCellSchema</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -842,12 +808,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
+          <t>Name of this schema, do not change</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
           <t>rdfs:comment</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Name of this schema, do not change</t>
         </is>
       </c>
     </row>
@@ -859,14 +825,10 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>0.1.3</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+          <t>0.2.0</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -874,12 +836,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>Version of this schema, do not change</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>rdfs:comment</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Version of this schema, do not change</t>
         </is>
       </c>
     </row>
@@ -906,22 +868,18 @@
           <t>GasDiffusionElectrode</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -934,22 +892,18 @@
           <t>CarbonPaper</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C15" s="8" t="n"/>
       <c r="D15" s="8" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -962,22 +916,18 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -990,22 +940,18 @@
           <t>Polytetrafluoroethylene</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C17" s="8" t="n"/>
       <c r="D17" s="8" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-hasCoating</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1026,12 +972,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -1044,22 +990,18 @@
           <t>Electrocatalyst</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial</t>
         </is>
       </c>
-      <c r="F19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1072,22 +1014,18 @@
           <t>Copper</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -1108,12 +1046,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassLoading</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1134,12 +1072,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassFraction</t>
         </is>
       </c>
-      <c r="F22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -1152,22 +1090,18 @@
           <t>IonomerCompound</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasBinder</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1180,22 +1114,18 @@
           <t>PerfluorosulfonicAcid</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasBinder</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -1216,12 +1146,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasBinder-hasMeasuredProperty-MassFraction</t>
         </is>
       </c>
-      <c r="F25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1242,12 +1172,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
-      <c r="F26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -1280,12 +1210,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Porosity</t>
         </is>
       </c>
-      <c r="F28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -1306,12 +1236,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-D50ParticleSize</t>
         </is>
       </c>
-      <c r="F29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -1336,22 +1266,18 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C31" s="4" t="n"/>
       <c r="D31" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -1364,22 +1290,18 @@
           <t>15p_Cu</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-schema:productID</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1392,22 +1314,18 @@
           <t>SGLCarbon</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -1420,22 +1338,18 @@
           <t>39BB</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-schema:productID</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1448,22 +1362,18 @@
           <t>Millipore Sigma</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C35" s="4" t="n"/>
       <c r="D35" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -1474,22 +1384,18 @@
       <c r="B36" s="8" t="n">
         <v>774081</v>
       </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-schema:productID</t>
         </is>
       </c>
-      <c r="F36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -1502,22 +1408,18 @@
           <t>Chemours</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C37" s="4" t="n"/>
       <c r="D37" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasBinder-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -1530,22 +1432,18 @@
           <t>D521CS</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasBinder-schema:productID</t>
         </is>
       </c>
-      <c r="F38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -1570,22 +1468,18 @@
           <t>ImmersionElectrode</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C40" s="4" t="n"/>
       <c r="D40" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode</t>
         </is>
       </c>
-      <c r="F40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -1598,22 +1492,18 @@
           <t>PerforatedFoil</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C41" s="12" t="n"/>
       <c r="D41" s="12" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate</t>
         </is>
       </c>
-      <c r="F41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -1626,22 +1516,18 @@
           <t>Titanium</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C42" s="4" t="n"/>
       <c r="D42" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate</t>
         </is>
       </c>
-      <c r="F42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -1662,12 +1548,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
-      <c r="F43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -1680,22 +1566,18 @@
           <t>Electrocatalyst</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
         </is>
       </c>
-      <c r="F44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -1708,22 +1590,18 @@
           <t>IridiumIIIOxide</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C45" s="12" t="n"/>
       <c r="D45" s="12" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
         </is>
       </c>
-      <c r="F45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -1744,12 +1622,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassLoading</t>
         </is>
       </c>
-      <c r="F46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -1770,12 +1648,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassFraction</t>
         </is>
       </c>
-      <c r="F47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -1788,22 +1666,18 @@
           <t>IonomerCompound</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasBinder</t>
         </is>
       </c>
-      <c r="F48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -1816,22 +1690,18 @@
           <t>PerfluorosulfonicAcid</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C49" s="12" t="n"/>
       <c r="D49" s="12" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasBinder</t>
         </is>
       </c>
-      <c r="F49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -1852,12 +1722,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasBinder-hasMeasuredProperty-MassFraction</t>
         </is>
       </c>
-      <c r="F50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -1878,12 +1748,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
-      <c r="F51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
@@ -1916,12 +1786,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Porosity</t>
         </is>
       </c>
-      <c r="F53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -1942,12 +1812,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="E54" s="12" t="n"/>
+      <c r="F54" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-D50ParticleSize</t>
         </is>
       </c>
-      <c r="F54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
@@ -1972,22 +1842,18 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C56" s="4" t="n"/>
       <c r="D56" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -2000,22 +1866,18 @@
           <t>18x_Ti</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C57" s="12" t="n"/>
       <c r="D57" s="12" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-schema:productID</t>
         </is>
       </c>
-      <c r="F57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -2028,22 +1890,18 @@
           <t>Fuel Cell Store</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C58" s="4" t="n"/>
       <c r="D58" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -2054,22 +1912,18 @@
       <c r="B59" s="12" t="n">
         <v>40050001</v>
       </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C59" s="12" t="n"/>
       <c r="D59" s="12" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E59" s="12" t="n"/>
+      <c r="F59" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-schema:productID</t>
         </is>
       </c>
-      <c r="F59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -2082,22 +1936,18 @@
           <t>Fuel Cell Store</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C60" s="4" t="n"/>
       <c r="D60" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -2108,22 +1958,18 @@
       <c r="B61" s="12" t="n">
         <v>57080249</v>
       </c>
-      <c r="C61" s="12" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C61" s="12" t="n"/>
       <c r="D61" s="12" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E61" s="12" t="n"/>
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-schema:productID</t>
         </is>
       </c>
-      <c r="F61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -2136,22 +1982,18 @@
           <t>Chemours</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C62" s="4" t="n"/>
       <c r="D62" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E62" s="4" t="n"/>
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasBinder-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -2164,22 +2006,18 @@
           <t>D521CS</t>
         </is>
       </c>
-      <c r="C63" s="12" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C63" s="12" t="n"/>
       <c r="D63" s="12" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="E63" s="12" t="n"/>
+      <c r="F63" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasBinder-schema:productID</t>
         </is>
       </c>
-      <c r="F63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
@@ -2204,22 +2042,18 @@
           <t>CarbonDioxide</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-Gas</t>
         </is>
       </c>
-      <c r="F65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
@@ -2240,12 +2074,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E66" s="16" t="inlineStr">
+      <c r="E66" s="16" t="n"/>
+      <c r="F66" s="16" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F66" s="16" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -2258,22 +2092,18 @@
           <t>Argon</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C67" s="4" t="n"/>
       <c r="D67" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-Gas</t>
         </is>
       </c>
-      <c r="F67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
@@ -2294,12 +2124,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E68" s="16" t="inlineStr">
+      <c r="E68" s="16" t="n"/>
+      <c r="F68" s="16" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F68" s="16" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -2320,12 +2150,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
-      <c r="F69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
@@ -2346,12 +2176,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E70" s="16" t="inlineStr">
+      <c r="E70" s="16" t="n"/>
+      <c r="F70" s="16" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
-      <c r="F70" s="16" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
@@ -2376,22 +2206,18 @@
           <t>Water</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C72" s="4" t="n"/>
       <c r="D72" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolvent-hasConstituentA</t>
         </is>
       </c>
-      <c r="F72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
@@ -2412,12 +2238,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E73" s="16" t="inlineStr">
+      <c r="E73" s="16" t="n"/>
+      <c r="F73" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F73" s="16" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -2426,22 +2252,18 @@
         </is>
       </c>
       <c r="B74" s="4" t="n"/>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C74" s="4" t="n"/>
       <c r="D74" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
-      <c r="F74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
@@ -2460,12 +2282,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E75" s="16" t="inlineStr">
+      <c r="E75" s="16" t="n"/>
+      <c r="F75" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F75" s="16" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -2478,22 +2300,18 @@
           <t>PotassiumCarbonate</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C76" s="4" t="n"/>
       <c r="D76" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentA</t>
         </is>
       </c>
-      <c r="F76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
@@ -2514,12 +2332,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E77" s="16" t="inlineStr">
+      <c r="E77" s="16" t="n"/>
+      <c r="F77" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
-      <c r="F77" s="16" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -2528,22 +2346,18 @@
         </is>
       </c>
       <c r="B78" s="4" t="n"/>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C78" s="4" t="n"/>
       <c r="D78" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E78" s="4" t="n"/>
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentB</t>
         </is>
       </c>
-      <c r="F78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
@@ -2562,12 +2376,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E79" s="16" t="inlineStr">
+      <c r="E79" s="16" t="n"/>
+      <c r="F79" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
-      <c r="F79" s="16" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -2588,12 +2402,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-Volume</t>
         </is>
       </c>
-      <c r="F80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
@@ -2614,12 +2428,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E81" s="16" t="inlineStr">
+      <c r="E81" s="16" t="n"/>
+      <c r="F81" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
-      <c r="F81" s="16" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -2640,12 +2454,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
-      <c r="F82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="17" t="inlineStr">
@@ -2678,12 +2492,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E84" s="4" t="n"/>
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
-      <c r="F84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
@@ -2704,12 +2518,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E85" s="16" t="inlineStr">
+      <c r="E85" s="16" t="n"/>
+      <c r="F85" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-PH</t>
         </is>
       </c>
-      <c r="F85" s="16" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -2730,12 +2544,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="E86" s="4" t="n"/>
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-Density</t>
         </is>
       </c>
-      <c r="F86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
@@ -2756,12 +2570,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E87" s="16" t="inlineStr">
+      <c r="E87" s="16" t="n"/>
+      <c r="F87" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-CelsiusTemperature</t>
         </is>
       </c>
-      <c r="F87" s="16" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="17" t="inlineStr">
@@ -2786,22 +2600,18 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C89" s="4" t="n"/>
       <c r="D89" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="16" t="inlineStr">
@@ -2814,22 +2624,18 @@
           <t>KCl_1M_catholyte</t>
         </is>
       </c>
-      <c r="C90" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C90" s="16" t="n"/>
       <c r="D90" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E90" s="16" t="inlineStr">
+      <c r="E90" s="16" t="n"/>
+      <c r="F90" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-schema:productID</t>
         </is>
       </c>
-      <c r="F90" s="16" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -2838,22 +2644,18 @@
         </is>
       </c>
       <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C91" s="4" t="n"/>
       <c r="D91" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E91" s="4" t="n"/>
+      <c r="F91" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolventA-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="16" t="inlineStr">
@@ -2862,22 +2664,18 @@
         </is>
       </c>
       <c r="B92" s="16" t="n"/>
-      <c r="C92" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C92" s="16" t="n"/>
       <c r="D92" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E92" s="16" t="inlineStr">
+      <c r="E92" s="16" t="n"/>
+      <c r="F92" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolventA-schema:productID</t>
         </is>
       </c>
-      <c r="F92" s="16" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -2886,22 +2684,18 @@
         </is>
       </c>
       <c r="B93" s="4" t="n"/>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C93" s="4" t="n"/>
       <c r="D93" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolventB-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="16" t="inlineStr">
@@ -2910,22 +2704,18 @@
         </is>
       </c>
       <c r="B94" s="16" t="n"/>
-      <c r="C94" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C94" s="16" t="n"/>
       <c r="D94" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E94" s="16" t="inlineStr">
+      <c r="E94" s="16" t="n"/>
+      <c r="F94" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolventB-schema:productID</t>
         </is>
       </c>
-      <c r="F94" s="16" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -2938,22 +2728,18 @@
           <t>Thermo Fisher Scientific</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C95" s="4" t="n"/>
       <c r="D95" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E95" s="4" t="n"/>
+      <c r="F95" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSoluteA-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="16" t="inlineStr">
@@ -2964,22 +2750,18 @@
       <c r="B96" s="16" t="n">
         <v>424090010</v>
       </c>
-      <c r="C96" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C96" s="16" t="n"/>
       <c r="D96" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E96" s="16" t="inlineStr">
+      <c r="E96" s="16" t="n"/>
+      <c r="F96" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSoluteA-schema:productID</t>
         </is>
       </c>
-      <c r="F96" s="16" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -2988,22 +2770,18 @@
         </is>
       </c>
       <c r="B97" s="4" t="n"/>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C97" s="4" t="n"/>
       <c r="D97" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="E97" s="4" t="n"/>
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSoluteB-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="16" t="inlineStr">
@@ -3012,22 +2790,18 @@
         </is>
       </c>
       <c r="B98" s="16" t="n"/>
-      <c r="C98" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C98" s="16" t="n"/>
       <c r="D98" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E98" s="16" t="inlineStr">
+      <c r="E98" s="16" t="n"/>
+      <c r="F98" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSoluteB-schema:productID</t>
         </is>
       </c>
-      <c r="F98" s="16" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="14" t="inlineStr">
@@ -3052,22 +2826,18 @@
           <t>Nitrogen</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C100" s="4" t="n"/>
       <c r="D100" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-Gas</t>
         </is>
       </c>
-      <c r="F100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="16" t="inlineStr">
@@ -3088,12 +2858,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E101" s="16" t="inlineStr">
+      <c r="E101" s="16" t="n"/>
+      <c r="F101" s="16" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F101" s="16" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -3102,22 +2872,18 @@
         </is>
       </c>
       <c r="B102" s="4" t="n"/>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C102" s="4" t="n"/>
       <c r="D102" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
+      <c r="E102" s="4" t="n"/>
+      <c r="F102" s="4" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-Gas</t>
         </is>
       </c>
-      <c r="F102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="16" t="inlineStr">
@@ -3136,12 +2902,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E103" s="16" t="inlineStr">
+      <c r="E103" s="16" t="n"/>
+      <c r="F103" s="16" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F103" s="16" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -3162,12 +2928,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
-      <c r="F104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="16" t="inlineStr">
@@ -3188,12 +2954,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E105" s="16" t="inlineStr">
+      <c r="E105" s="16" t="n"/>
+      <c r="F105" s="16" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
-      <c r="F105" s="16" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
@@ -3218,22 +2984,18 @@
           <t>Water</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C107" s="4" t="n"/>
       <c r="D107" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-hasConstituentA</t>
         </is>
       </c>
-      <c r="F107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="16" t="inlineStr">
@@ -3254,12 +3016,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E108" s="16" t="inlineStr">
+      <c r="E108" s="16" t="n"/>
+      <c r="F108" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F108" s="16" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -3268,22 +3030,18 @@
         </is>
       </c>
       <c r="B109" s="4" t="n"/>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C109" s="4" t="n"/>
       <c r="D109" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
+      <c r="E109" s="4" t="n"/>
+      <c r="F109" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
-      <c r="F109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="16" t="inlineStr">
@@ -3302,12 +3060,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E110" s="16" t="inlineStr">
+      <c r="E110" s="16" t="n"/>
+      <c r="F110" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-      <c r="F110" s="16" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -3320,22 +3078,18 @@
           <t>SulfuricAcid</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C111" s="4" t="n"/>
       <c r="D111" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentA</t>
         </is>
       </c>
-      <c r="F111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="16" t="inlineStr">
@@ -3356,12 +3110,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E112" s="16" t="inlineStr">
+      <c r="E112" s="16" t="n"/>
+      <c r="F112" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
-      <c r="F112" s="16" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -3370,22 +3124,18 @@
         </is>
       </c>
       <c r="B113" s="4" t="n"/>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C113" s="4" t="n"/>
       <c r="D113" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
+      <c r="E113" s="4" t="n"/>
+      <c r="F113" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentB</t>
         </is>
       </c>
-      <c r="F113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="16" t="inlineStr">
@@ -3404,12 +3154,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E114" s="16" t="inlineStr">
+      <c r="E114" s="16" t="n"/>
+      <c r="F114" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
-      <c r="F114" s="16" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -3430,12 +3180,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
+      <c r="E115" s="4" t="n"/>
+      <c r="F115" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-Volume</t>
         </is>
       </c>
-      <c r="F115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="16" t="inlineStr">
@@ -3456,12 +3206,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E116" s="16" t="inlineStr">
+      <c r="E116" s="16" t="n"/>
+      <c r="F116" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
-      <c r="F116" s="16" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -3482,12 +3232,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
+      <c r="E117" s="4" t="n"/>
+      <c r="F117" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
-      <c r="F117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="17" t="inlineStr">
@@ -3520,12 +3270,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
+      <c r="E119" s="4" t="n"/>
+      <c r="F119" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
-      <c r="F119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="16" t="inlineStr">
@@ -3546,12 +3296,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E120" s="16" t="inlineStr">
+      <c r="E120" s="16" t="n"/>
+      <c r="F120" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-PH</t>
         </is>
       </c>
-      <c r="F120" s="16" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -3572,12 +3322,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
+      <c r="E121" s="4" t="n"/>
+      <c r="F121" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-Density</t>
         </is>
       </c>
-      <c r="F121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="16" t="inlineStr">
@@ -3598,12 +3348,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E122" s="16" t="inlineStr">
+      <c r="E122" s="16" t="n"/>
+      <c r="F122" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-CelsiusTemperature</t>
         </is>
       </c>
-      <c r="F122" s="16" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="17" t="inlineStr">
@@ -3628,22 +3378,18 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C124" s="4" t="n"/>
       <c r="D124" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
+      <c r="E124" s="4" t="n"/>
+      <c r="F124" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="16" t="inlineStr">
@@ -3656,22 +3402,18 @@
           <t>H2SO4_1M_anolyte</t>
         </is>
       </c>
-      <c r="C125" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C125" s="16" t="n"/>
       <c r="D125" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E125" s="16" t="inlineStr">
+      <c r="E125" s="16" t="n"/>
+      <c r="F125" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-schema:productID</t>
         </is>
       </c>
-      <c r="F125" s="16" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -3680,22 +3422,18 @@
         </is>
       </c>
       <c r="B126" s="4" t="n"/>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C126" s="4" t="n"/>
       <c r="D126" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
+      <c r="E126" s="4" t="n"/>
+      <c r="F126" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="16" t="inlineStr">
@@ -3704,22 +3442,18 @@
         </is>
       </c>
       <c r="B127" s="16" t="n"/>
-      <c r="C127" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C127" s="16" t="n"/>
       <c r="D127" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E127" s="16" t="inlineStr">
+      <c r="E127" s="16" t="n"/>
+      <c r="F127" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-schema:productID</t>
         </is>
       </c>
-      <c r="F127" s="16" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -3728,22 +3462,18 @@
         </is>
       </c>
       <c r="B128" s="4" t="n"/>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C128" s="4" t="n"/>
       <c r="D128" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
+      <c r="E128" s="4" t="n"/>
+      <c r="F128" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="16" t="inlineStr">
@@ -3752,22 +3482,18 @@
         </is>
       </c>
       <c r="B129" s="16" t="n"/>
-      <c r="C129" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C129" s="16" t="n"/>
       <c r="D129" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E129" s="16" t="inlineStr">
+      <c r="E129" s="16" t="n"/>
+      <c r="F129" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-schema:productID</t>
         </is>
       </c>
-      <c r="F129" s="16" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -3780,22 +3506,18 @@
           <t>Millipore Sigma</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C130" s="4" t="n"/>
       <c r="D130" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
+      <c r="E130" s="4" t="n"/>
+      <c r="F130" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="16" t="inlineStr">
@@ -3806,22 +3528,18 @@
       <c r="B131" s="16" t="n">
         <v>258105</v>
       </c>
-      <c r="C131" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C131" s="16" t="n"/>
       <c r="D131" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E131" s="16" t="inlineStr">
+      <c r="E131" s="16" t="n"/>
+      <c r="F131" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-schema:productID</t>
         </is>
       </c>
-      <c r="F131" s="16" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -3830,22 +3548,18 @@
         </is>
       </c>
       <c r="B132" s="4" t="n"/>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C132" s="4" t="n"/>
       <c r="D132" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
+      <c r="E132" s="4" t="n"/>
+      <c r="F132" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="16" t="inlineStr">
@@ -3854,22 +3568,18 @@
         </is>
       </c>
       <c r="B133" s="16" t="n"/>
-      <c r="C133" s="16" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C133" s="16" t="n"/>
       <c r="D133" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E133" s="16" t="inlineStr">
+      <c r="E133" s="16" t="n"/>
+      <c r="F133" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-schema:productID</t>
         </is>
       </c>
-      <c r="F133" s="16" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -3894,22 +3604,18 @@
           <t>IonExchangeMembrane</t>
         </is>
       </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C135" s="4" t="n"/>
       <c r="D135" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
+      <c r="E135" s="4" t="n"/>
+      <c r="F135" s="4" t="inlineStr">
         <is>
           <t>hasSeparator</t>
         </is>
       </c>
-      <c r="F135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -3922,22 +3628,18 @@
           <t>BilayerMembrane</t>
         </is>
       </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C136" s="5" t="n"/>
       <c r="D136" s="5" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E136" s="5" t="inlineStr">
+      <c r="E136" s="5" t="n"/>
+      <c r="F136" s="5" t="inlineStr">
         <is>
           <t>hasSeparator</t>
         </is>
       </c>
-      <c r="F136" s="5" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -3950,22 +3652,18 @@
           <t>AnionExchangeMembrane</t>
         </is>
       </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C137" s="4" t="n"/>
       <c r="D137" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
+      <c r="E137" s="4" t="n"/>
+      <c r="F137" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA</t>
         </is>
       </c>
-      <c r="F137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -3978,22 +3676,18 @@
           <t>PolyArylPiperidinium</t>
         </is>
       </c>
-      <c r="C138" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C138" s="5" t="n"/>
       <c r="D138" s="5" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E138" s="5" t="inlineStr">
+      <c r="E138" s="5" t="n"/>
+      <c r="F138" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA</t>
         </is>
       </c>
-      <c r="F138" s="5" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -4014,12 +3708,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
+      <c r="E139" s="4" t="n"/>
+      <c r="F139" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
-      <c r="F139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -4040,12 +3734,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E140" s="5" t="inlineStr">
+      <c r="E140" s="5" t="n"/>
+      <c r="F140" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
-      <c r="F140" s="5" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -4058,22 +3752,18 @@
           <t>CationExchangeMembrane</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C141" s="4" t="n"/>
       <c r="D141" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
+      <c r="E141" s="4" t="n"/>
+      <c r="F141" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB</t>
         </is>
       </c>
-      <c r="F141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -4086,22 +3776,18 @@
           <t>PerfluorosulfonicAcid</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C142" s="5" t="n"/>
       <c r="D142" s="5" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E142" s="5" t="inlineStr">
+      <c r="E142" s="5" t="n"/>
+      <c r="F142" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB</t>
         </is>
       </c>
-      <c r="F142" s="5" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -4122,12 +3808,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
+      <c r="E143" s="4" t="n"/>
+      <c r="F143" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
-      <c r="F143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -4148,12 +3834,12 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E144" s="5" t="inlineStr">
+      <c r="E144" s="5" t="n"/>
+      <c r="F144" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
-      <c r="F144" s="5" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -4186,12 +3872,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
+      <c r="E146" s="4" t="n"/>
+      <c r="F146" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
-      <c r="F146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
@@ -4212,12 +3898,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E147" s="5" t="inlineStr">
+      <c r="E147" s="5" t="n"/>
+      <c r="F147" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
-      <c r="F147" s="5" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -4242,22 +3928,18 @@
           <t>Fuel Cell Store</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C149" s="4" t="n"/>
       <c r="D149" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
+      <c r="E149" s="4" t="n"/>
+      <c r="F149" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -4268,22 +3950,18 @@
       <c r="B150" s="5" t="n">
         <v>72010015</v>
       </c>
-      <c r="C150" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C150" s="5" t="n"/>
       <c r="D150" s="5" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E150" s="5" t="inlineStr">
+      <c r="E150" s="5" t="n"/>
+      <c r="F150" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA-schema:productID</t>
         </is>
       </c>
-      <c r="F150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -4296,22 +3974,18 @@
           <t>Chemours</t>
         </is>
       </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C151" s="4" t="n"/>
       <c r="D151" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
+      <c r="E151" s="4" t="n"/>
+      <c r="F151" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -4324,22 +3998,18 @@
           <t>N117</t>
         </is>
       </c>
-      <c r="C152" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C152" s="5" t="n"/>
       <c r="D152" s="5" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E152" s="5" t="inlineStr">
+      <c r="E152" s="5" t="n"/>
+      <c r="F152" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB-schema:productID</t>
         </is>
       </c>
-      <c r="F152" s="5" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -4364,22 +4034,18 @@
           <t>FlowCell</t>
         </is>
       </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C154" s="4" t="n"/>
       <c r="D154" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
+      <c r="E154" s="4" t="n"/>
+      <c r="F154" s="4" t="inlineStr">
         <is>
           <t>hasCase</t>
         </is>
       </c>
-      <c r="F154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
@@ -4392,22 +4058,18 @@
           <t>FlowField</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C155" s="5" t="n"/>
       <c r="D155" s="5" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E155" s="5" t="inlineStr">
+      <c r="E155" s="5" t="n"/>
+      <c r="F155" s="5" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasComponent</t>
         </is>
       </c>
-      <c r="F155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -4428,12 +4090,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
+      <c r="E156" s="4" t="n"/>
+      <c r="F156" s="4" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasMeasuredProperty-Width</t>
         </is>
       </c>
-      <c r="F156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -4454,12 +4116,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E157" s="5" t="inlineStr">
+      <c r="E157" s="5" t="n"/>
+      <c r="F157" s="5" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasMeasuredProperty-Area</t>
         </is>
       </c>
-      <c r="F157" s="5" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -4480,12 +4142,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
+      <c r="E158" s="4" t="n"/>
+      <c r="F158" s="4" t="inlineStr">
         <is>
           <t>hasComponentB-type|CatholyteCompartment-hasMeasuredProperty-Width</t>
         </is>
       </c>
-      <c r="F158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -4506,12 +4168,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E159" s="5" t="inlineStr">
+      <c r="E159" s="5" t="n"/>
+      <c r="F159" s="5" t="inlineStr">
         <is>
           <t>hasComponentB-type|CatholyteCompartment-hasMeasuredProperty-Volume</t>
         </is>
       </c>
-      <c r="F159" s="5" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -4524,22 +4186,18 @@
           <t>SilverChlorideElectrode</t>
         </is>
       </c>
-      <c r="C160" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C160" s="4" t="n"/>
       <c r="D160" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E160" s="4" t="inlineStr">
+      <c r="E160" s="4" t="n"/>
+      <c r="F160" s="4" t="inlineStr">
         <is>
           <t>hasComponentB-type|CatholyteCompartment-hasReferenceElectrode</t>
         </is>
       </c>
-      <c r="F160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
@@ -4560,12 +4218,12 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E161" s="5" t="inlineStr">
+      <c r="E161" s="5" t="n"/>
+      <c r="F161" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasMeasuredProperty-Area</t>
         </is>
       </c>
-      <c r="F161" s="5" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -4586,12 +4244,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E162" s="4" t="inlineStr">
+      <c r="E162" s="4" t="n"/>
+      <c r="F162" s="4" t="inlineStr">
         <is>
           <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Volume</t>
         </is>
       </c>
-      <c r="F162" s="4" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
@@ -4612,12 +4270,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E163" s="5" t="inlineStr">
+      <c r="E163" s="5" t="n"/>
+      <c r="F163" s="5" t="inlineStr">
         <is>
           <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Width</t>
         </is>
       </c>
-      <c r="F163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -4630,22 +4288,18 @@
           <t>SilverChlorideElectrode</t>
         </is>
       </c>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C164" s="4" t="n"/>
       <c r="D164" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E164" s="4" t="inlineStr">
+      <c r="E164" s="4" t="n"/>
+      <c r="F164" s="4" t="inlineStr">
         <is>
           <t>hasComponentC-type|AnolyteCompartment-hasReferenceElectrode</t>
         </is>
       </c>
-      <c r="F164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
@@ -4666,12 +4320,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E165" s="5" t="inlineStr">
+      <c r="E165" s="5" t="n"/>
+      <c r="F165" s="5" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasMeasuredProperty-Area</t>
         </is>
       </c>
-      <c r="F165" s="5" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -4692,12 +4346,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E166" s="4" t="inlineStr">
+      <c r="E166" s="4" t="n"/>
+      <c r="F166" s="4" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasMeasuredProperty-Width</t>
         </is>
       </c>
-      <c r="F166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
@@ -4710,22 +4364,18 @@
           <t>FlowField</t>
         </is>
       </c>
-      <c r="C167" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C167" s="5" t="n"/>
       <c r="D167" s="5" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E167" s="5" t="inlineStr">
+      <c r="E167" s="5" t="n"/>
+      <c r="F167" s="5" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasComponent</t>
         </is>
       </c>
-      <c r="F167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -4746,12 +4396,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E168" s="4" t="inlineStr">
+      <c r="E168" s="4" t="n"/>
+      <c r="F168" s="4" t="inlineStr">
         <is>
           <t>hasComponentE-type|CatholyteTank-hasMeasuredProperty-Volume</t>
         </is>
       </c>
-      <c r="F168" s="4" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
@@ -4772,12 +4422,12 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E169" s="5" t="inlineStr">
+      <c r="E169" s="5" t="n"/>
+      <c r="F169" s="5" t="inlineStr">
         <is>
           <t>hasComponentF-type|AnolyteTank-hasMeasuredProperty-Volume</t>
         </is>
       </c>
-      <c r="F169" s="5" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="18" t="inlineStr">
@@ -4802,22 +4452,18 @@
           <t>Fuel Cell Store</t>
         </is>
       </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C171" s="4" t="n"/>
       <c r="D171" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E171" s="4" t="inlineStr">
+      <c r="E171" s="4" t="n"/>
+      <c r="F171" s="4" t="inlineStr">
         <is>
           <t>hasCase-schema:manufacturer</t>
         </is>
       </c>
-      <c r="F171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -4830,22 +4476,18 @@
           <t>Micro Flow Cell</t>
         </is>
       </c>
-      <c r="C172" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C172" s="5" t="n"/>
       <c r="D172" s="5" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E172" s="5" t="inlineStr">
+      <c r="E172" s="5" t="n"/>
+      <c r="F172" s="5" t="inlineStr">
         <is>
           <t>hasCase-schema:productID</t>
         </is>
       </c>
-      <c r="F172" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4858,106 +4500,453 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Metadata</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Extra values  -&gt;  affiliations for an author, a description for a data file, or more items for a list</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://schema.org/</t>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Include references in metadata file (yes/no)</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>emmo</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://w3id.org/emmo#</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>References for dataset</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>echem</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://w3id.org/emmo/domain/electrochemistry#</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Dataset name</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Dataset for the publication 'Balancing selectivity retention and catalyst restructuring in pulsed CO2 electroreduction on silver'</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://w3id.org/emmo/domain/battery#</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Dataset description</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Dataset for the publication containing raw and processed data used to compose the various figures.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>chemical</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://w3id.org/emmo/domain/chemical-substance#</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Dataset publisher</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://qudt.org/vocab/unit/</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Dataset license</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>rdfs</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Dataset date issued</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Dataset date published</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Dataset URL</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.22092428</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Dataset API URL</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/api/records/22092428</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorA</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Claudia Bissattini</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorB</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Richa Rajadhyax</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorC</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Alessandro Senocrate</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorD</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Corsin Battaglia</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>References for associated publications</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication DOI</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1039/D6EY00140H</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication title</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Balancing selectivity retention and catalyst restructuring in pulsed CO2 electroreduction on silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication figures</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Fig. 1a</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Fig. 2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorA</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Claudia Bissattini</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorB</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Richa Rajadhyax</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorC</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Alessandro Senocrate</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorD</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Corsin Battaglia</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>References for data files</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Data zip file</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Data.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Tabular data schema</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>https://w3id.org/catalysis-data-format/schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Data fileA</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>empa__ecid000001/empa__ecid000001.cdf.parquet</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Time series electrochemical data as parquet with Catalysis Data Format columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Data fileB</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>empa__ecid000001/empa__ecid000001.cdf.csv</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Time series electrochemical data as csv with Catalysis Data Format columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Raw data fileA</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>empa__ecid000001/empa__ecid000001_CA_C01.mpr</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Raw electrochemical data, Biologic EC-Lab mpr binary format</t>
         </is>
       </c>
     </row>
@@ -4972,248 +4961,112 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Term</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>IRI</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hasActiveMaterial</t>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://schema.org/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hasBinder</t>
+          <t>emmo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Binder</t>
+          <t>https://w3id.org/emmo#</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hasCase</t>
+          <t>echem</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://w3id.org/emmo/domain/electrochemistry#</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hasCoating</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Coating</t>
+          <t>https://w3id.org/emmo/domain/battery#</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hasConductiveAdditive</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ConductiveAdditive</t>
+          <t>https://w3id.org/emmo/domain/chemical-substance#</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hasCurrentCollector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CurrentCollector</t>
+          <t>https://qudt.org/vocab/unit/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hasElectrolyte</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Electrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Electrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>hasSeparator</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Separator</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>hasSolute</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Solute</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>hasSolvent</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Solvent</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>hasConstituent</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>hasInput</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>hasProperty</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>hasWaveSpring</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>hasSpacer</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>hasMeasuredProperty</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>hasOutput</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>hasReferenceElectrode</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ReferenceElectrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>hasSubstrate</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Substrate</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>hasWorkingElectrode</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>WorkingElectrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>hasCounterElectrode</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CounterElectrode</t>
+          <t>rdfs</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2000/01/rdf-schema#</t>
         </is>
       </c>
     </row>
@@ -5228,23 +5081,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C167"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="74" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Predicate</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Default class</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -5254,1463 +5107,269 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>If the item is listed here without unique ID (e.g. R2032), this means the item is already ontologized in BattInFo ontology. No additional ID is required.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hasActiveMaterial</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ActiveMaterial</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ElectrochemicalCell</t>
+          <t>hasAnolyte</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Anolyte</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ElectrochemicalHalfCell</t>
+          <t>hasBinder</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Binder</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BatteryCell</t>
+          <t>hasCatholyte</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Catholyte</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ElectrolyticCell</t>
+          <t>hasCoating</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Coating</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FlowCell</t>
+          <t>hasConductiveAdditive</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ConductiveAdditive</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R2032</t>
+          <t>hasCounterElectrode</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CounterElectrode</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CoinCell</t>
+          <t>hasCurrentCollector</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CurrentCollector</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ThreeElectrodeCell</t>
+          <t>hasElectrolyte</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Electrolyte</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ZeroGapCell</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>hasNegativeElectrode</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NegativeElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PositiveElectrode</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>hasReferenceElectrode</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ReferenceElectrode</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AnolyteCompartment</t>
+          <t>hasSeparator</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Separator</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AnolyteTank</t>
+          <t>hasSolute</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Solute</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CatholyteCompartment</t>
+          <t>hasSolvent</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Solvent</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CatholyteTank</t>
+          <t>hasSubstrate</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Substrate</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FlowField</t>
+          <t>hasWorkingElectrode</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>WorkingElectrode</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GasCompartment</t>
+          <t>hasCase</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NegativeElectrodeGasCompartment</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>requested</t>
+          <t>hasComponent</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PositiveElectrodeGasCompartment</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
+          <t>hasConstituent</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>hasDatum</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Electrode</t>
+          <t>hasInput</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GasDiffusionElectrode</t>
+          <t>hasMeasuredProperty</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ImmersionElectrode</t>
+          <t>hasOutput</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ReferenceElectrode</t>
+          <t>hasProperty</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GlassyCarbonElectrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LithiumElectrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>SilverChlorideElectrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>MercuryOxideElectrode</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>NormalHydrogenElectrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>ReversibleHydrogenElectrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Substrate</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>CarbonPaper</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ElectrospunMesh</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ExpandedMesh</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>WovenMesh</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>PerforatedFoil</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Foil</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Coating</t>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Solid</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Aluminium</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Carbon</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>CarbonBlack</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>CopperOxideCompound</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Electrocatalyst</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Graphite</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>IridiumOxideCompound</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>IridiumIIIOxide</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>IridiumDioxide</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Lithium</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>LithiumIronPhosphate</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>https://pubchem.ncbi.nlm.nih.gov/substance/485083898</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>LithiumNickleCobaltManganeseOxide</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>https://pubchem.ncbi.nlm.nih.gov/substance/485083898</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>LithiumTitanate</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>StainlessSteel</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Tantalum</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>TantalumOxideCompound</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Titanium</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>TitaniumOxideCompound</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>TitaniumIOxide</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>TitaniumIIOxide</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>TitaniumIIOxide</t>
-        </is>
-      </c>
-    </row>
-    <row r="70"/>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Separator</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>GlassFiberSeparator</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>IonExchangeMembrane</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>AnionExchangeMembrane</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>CationExchangeMembrane</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>BilayerMembrane</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>IonomerCompound</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>PerfluorocarboxylicAcid</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Flemion by AGC (CEM), Aciplex by Asahi Kasei (CEM), requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>PerfluorosulfonicAcid</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Nafion by Chemours (long side-chain CEM), Aquivion by Solvay (short side-chain CEM), Fumapem SF by Fumatech (short side-chain CEM), Fumasep F by Fumatech)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>PolyAryleneImidazolium</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Aemion+ by Ionomr (AEM). AF1 by Ionomr (AEM), requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>PolyArylPiperidinium</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Piperion by Versogen (AEM), requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>PolyArylAmmonium</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Fumasep FAA by Fumatech (AEM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>PolyetherEtherKetone</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Victrex by Solvay (PEEK), Ketaspire by Evonik (PEEK), Radel by Solvay (PEEK), requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Polyolefin</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Polypropylene</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Celgard by Polypore International now part of Asahi Kasei (PP)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Polytetrafluoroethylene</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Teflon by Chemours (PTFE), Polyflon by Daikin (PTFE),</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>PolyvinylideneFluoride</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Kynar by Arkema (PVDF), Solef by Solvay (PVDF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>QuaternaryAmmoniumPolySulfone</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Sustainion by Dioxide Materials (AEM), requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>SulfonatedPolyEtherEtherKetone</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Speek by Gore (CEM), requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="90"/>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Electrolyte</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>LiquidElectrolyte</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>SolidElectrolyte</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>EthyleneCarbonate</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>EthylMethylCarbonate</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>LithiumBisfluorosulfonylimide</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>LithiumHexafluorophosphate</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>SodiumChloride</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>SodiumHydroxide</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>PhosphoricAcid</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>PotassiumCarbonate</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>PotassiumBiCarbonate</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>SulfuricAcid</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>TrisTrimethylsilyPhosphite</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>VinyleneCarbonate</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>HydrochloricAcid</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>PotassiumChloride</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>PotassiumHydroxide</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Methanol</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Ethanol</t>
-        </is>
-      </c>
-    </row>
-    <row r="112"/>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Gas</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>GasMixture</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Argon</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>CarbonDioxide</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Nitrogen</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Ammonia</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>CarbonMonoxide</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Oxygen</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Ethylene</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Air</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="124"/>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Purity</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Porosity</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Tortuosity</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Thickness</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-    </row>
-    <row r="132"/>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Corsin Battaglia</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0002-5003-1134</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Graham Kimbell</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0001-9610-3589</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Nukorn Plainpan</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0009-0002-6447-8057</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Alessandro Senocrate</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0002-0952-0948</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Claudia Bissattini Alessi</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0002-3971-0398</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Claudia Bissattini</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0002-3971-0398</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Finn Beiglboeck</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0001-9158-1338</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Francesco Bernasconi</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0002-6563-0578</t>
-        </is>
-      </c>
-    </row>
-    <row r="141"/>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Empa</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q683116</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Swiss Federal Laboratories for Materials Science and Technology; research institution</t>
-        </is>
-      </c>
-    </row>
-    <row r="143"/>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>AGC</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q367032</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>AGC Inc. (formerly Asahi Glass); manufacturer of Selemion AEM/CEM series and Flemion CEM series. https://www.agc.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Agfa</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q310172</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Agfa-Gevaert; manufacturer of Zirfon Perl UTP 500 porous composite diaphragm for alkaline water electrolysis. https://www.agfa.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Astom</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Astom Corporation (formerly Tokuyama); manufacturer of Neosepta ion exchange membrane series (AMX, CMX, AHA, BP-1). https://www.astom-corp.jp. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>AvCarb</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>AvCarb Material Solutions; manufacturer of carbon GDL series (P75, MGL190, 1071HCB) and MPLs. https://www.avcarb.com. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Celgard</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q122199856</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Celgard LLC (Polypore subsidiary); manufacturer of microporous polyolefin separators and membranes for batteries and filtration. https://www.celgard.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Chemours</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q15829006</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>The Chemours Company; manufacturer of Nafion perfluorosulfonic acid CEM series (N117, N115, N212, N211). https://www.chemours.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Customcells</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q120784603</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Customcells Group; manufacturer of custom lithium-ion battery cells for R&amp;D and prototyping. https://www.customcells.org</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Dioxide Materials</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Dioxide Materials; manufacturer of Sustainion X37-50 anion exchange membrane (PolyArylPiperidinium backbone, 50 µm). https://www.dioxidematerials.com. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>El-Cell</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>EL-CELL GmbH; developer of high-precision electrochemical testing equipment and battery research solutions. https://el-cell.com, to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Freudenberg</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q879878</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Freudenberg Performance Materials; manufacturer of gas diffusion layer series (H23C6, H14C9, H23C2) for fuel cells and electrolyzers. https://www.freudenberg-pm.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Fuel Cell Store</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q27868725</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Fuel Cell Store; US-based distributor of membrane electrode assemblies, GDLs and ion exchange membranes including Sustainion, PiperION and Nafion. https://www.fuelcellstore.com. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Fumatech</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>FuMA-Tech GmbH; manufacturer of FAA-3-50 and FAP-375-PP AEM series, Fumapem F/SF CEM series, and FBM bipolar membrane. https://www.fumatech.com. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Goodfellow</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q21449964</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Goodfellow Group; supplier of metals, alloys, polymers, ceramics and other materials in small quantities for research and development. https://www.goodfellow.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Hohsen</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Hohsen Corp.; Japanese manufacturer of specialty separators and ion exchange membranes for electrochemical applications. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Ionomr</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Ionomr Innovations; manufacturer of Aemion+ AEM series (AF1-HNN5-50-X, AF1-HWW8-25-X) based on poly(arylene imidazolium) backbone. https://www.ionomr.com. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Millipore Sigma</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q1669719</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>MilliporeSigma (Merck KGaA subsidiary, US operations); supplier of high-purity electrolyte chemicals and reagents for research. https://www.sigmaaldrich.com. to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>SGLCarbon</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q2361947</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>SGL Carbon SE; manufacturer of Sigracet GDL series (22BB, 28BC, 29BC, 39BB, 39BC) for fuel cells and electrolyzers. https://www.sglcarbon.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Sigracet</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>SIGRACET Fuel Cell Components</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Sterlitech</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Sterlitech Corporation; provider of PTFE membranes (0.05 μm to 10.0 μm) for chemical venting, gas diffusion, and aggressive solvent filtration. https://www.sterlitech.com, to be requested</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Solvay</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q487209</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Solvay S.A.; manufacturer of Aquivion short-side-chain PFSA CEM series (E87-05S, E87-12S, E98-05S) for PEM electrolyzers. https://www.solvay.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Solvionic</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q30285492</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Solvionic; French manufacturer and supplier of ionic liquids and specialty electrolyte solutions for electrochemical research. https://www.solvionic.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Thermo Fisher Scientific</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q306455</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Thermo Fisher Scientific; global supplier of laboratory chemicals, reagents and analytical instruments. https://www.thermofisher.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Toray</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q908461</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Toray Industries; manufacturer of Toray carbon paper GDL series (TGP-H-060, TGP-H-090, TGP-H-120) for fuel cells and electrolyzers. https://www.toray.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Versogen</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Versogen Inc.; manufacturer of PiperION AEM series based on poly(aryl piperidinium) backbone for CO2 electrolysis and fuel cells. https://www.versogen.com. to be requested</t>
+          <t>hasStringValue</t>
         </is>
       </c>
     </row>
@@ -6725,22 +5384,1732 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Class</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ElectrochemicalCell</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cell and device types. Classes available to the @Schema sheet Value column. Classes must already exist in the ontology. You can declare your own custom classes in the @Context sheet. This column is a reference list, a value already known to the ontology works even if it is not listed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ElectrolyticCell</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ElectrochemicalHalfCell</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BatteryCell</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CoinCell</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FlowCell</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ThreeElectrodeCellDevice</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R2032</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cell components and compartments</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AnolyteCompartment</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AnolyteTank</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CatholyteCompartment</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CatholyteTank</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GasCompartment</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NegativeElectrodeGasCompartment</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PositiveElectrodeGasCompartment</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FlowField</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Electrode</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Electrodes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GasDiffusionElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ImmersionElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ReferenceElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GlassyCarbonElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LithiumElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SilverChlorideElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MercuryOxideElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NormalHydrogenElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ReversibleHydrogenElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Substrate</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Substrates and structures</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CarbonPaper</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>WovenMesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ExpandedMesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ElectrospunMesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PerforatedFoil</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Foil</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Coating</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Metals and elemental substances</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Carbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CarbonBlack</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Lithium</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>StainlessSteel</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Tantalum</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Titanium</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Electrocatalyst</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Catalysts and metal oxides</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CopperOxideCompound</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>IridiumOxideCompound</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>IridiumIIIOxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>IridiumDioxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TantalumOxideCompound</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TitaniumOxideCompound</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TitaniumIIOxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TitaniumIIIOxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>LithiumIronPhosphate</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>LithiumNickelManganeseCobaltOxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>LithiumTitanate</t>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Separator</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Separators and membranes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>GlassFibreSeparator</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>IonExchangeMembrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AnionExchangeMembrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CationExchangeMembrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BilayerMembrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>IonomerCompound</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Membrane and binder polymers</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PerfluorocarboxylicAcid</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Flemion by AGC (CEM), Aciplex by Asahi Kasei (CEM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PerfluorosulfonicAcid</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Nafion by Chemours (long side-chain CEM), Aquivion by Solvay (short side-chain CEM), Fumapem SF by Fumatech (short side-chain CEM), Fumasep F by Fumatech)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PolyAryleneImidazolium</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Aemion+ by Ionomr (AEM). AF1 by Ionomr (AEM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PolyArylPiperidinium</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Piperion by Versogen (AEM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PolyArylAmmonium</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Fumasep FAA by Fumatech (AEM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PolyetherEtherKetone</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Victrex by Solvay (PEEK), Ketaspire by Evonik (PEEK), Radel by Solvay (PEEK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Polyolefin</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Polypropylene</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Celgard by Polypore International now part of Asahi Kasei (PP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Polytetrafluoroethylene</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Teflon by Chemours (PTFE), Polyflon by Daikin (PTFE),</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PolyvinylideneFluoride</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Kynar by Arkema (PVDF), Solef by Solvay (PVDF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>QuaternaryAmmoniumPolySulfone</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sustainion by Dioxide Materials (AEM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SulfonatedPolyEtherEtherKetone</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Speek by Gore (CEM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89"/>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Electrolyte</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Electrolytes and solvents</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>LiquidElectrolyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SolidElectrolyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Methanol</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Ethanol</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>EthyleneCarbonate</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>EthylMethylCarbonate</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>VinyleneCarbonate</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TrisTrimethylsilyPhosphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SulfuricAcid</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Acids, bases and salts</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>PhosphoricAcid</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>HydrochloricAcidSolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SodiumHydroxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PotassiumHydroxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>PotassiumCarbonate</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>PotassiumChloride</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SodiumChloride</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>LithiumBisfluorosulfonylimide</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>LithiumHexafluorophosphate</t>
+        </is>
+      </c>
+    </row>
+    <row r="111"/>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Gases</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>GasMixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Air</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Nitrogen</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Oxygen</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>CarbonDioxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>CarbonMonoxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Ammonia</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Ethylene</t>
+        </is>
+      </c>
+    </row>
+    <row r="123"/>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Measured property types, for the Ontology link column rather than Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Purity</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Tortuosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>IRI</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Corsin Battaglia</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-5003-1134</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Graham Kimbell</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0001-9610-3589</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nukorn Plainpan</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0002-6447-8057</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Alessandro Senocrate</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-0952-0948</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Claudia Bissattini</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-3971-0398</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Finn Beiglboeck</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0001-9158-1338</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Francesco Bernasconi</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-6563-0578</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Richa Rajadhyax</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0004-2257-1610</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>schema:ResearchOrganization</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q683116</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Swiss Federal Laboratories for Materials Science and Technology; research institution</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>schema:ResearchOrganization</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q262760</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>schema:ResearchOrganization</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q11942</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q367032</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AGC Inc. (formerly Asahi Glass); manufacturer of Selemion AEM/CEM series and Flemion CEM series. https://www.agc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Agfa</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q310172</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Agfa-Gevaert; manufacturer of Zirfon Perl UTP 500 porous composite diaphragm for alkaline water electrolysis. https://www.agfa.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Celgard</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q122199856</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Celgard LLC (Polypore subsidiary); manufacturer of microporous polyolefin separators and membranes for batteries and filtration. https://www.celgard.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chemours</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q15829006</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>The Chemours Company; manufacturer of Nafion perfluorosulfonic acid CEM series (N117, N115, N212, N211). https://www.chemours.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Customcells</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q120784603</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Customcells Group; manufacturer of custom lithium-ion battery cells for R&amp;D and prototyping. https://www.customcells.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Freudenberg</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q879878</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Freudenberg Performance Materials; manufacturer of gas diffusion layer series (H23C6, H14C9, H23C2) for fuel cells and electrolyzers. https://www.freudenberg-pm.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuel Cell Store</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q27868725</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fuel Cell Store; US-based distributor of membrane electrode assemblies, GDLs and ion exchange membranes including Sustainion, PiperION and Nafion. https://www.fuelcellstore.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Goodfellow</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q21449964</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Goodfellow Group; supplier of metals, alloys, polymers, ceramics and other materials in small quantities for research and development. https://www.goodfellow.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Millipore Sigma</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q1669719</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MilliporeSigma (Merck KGaA subsidiary, US operations); supplier of high-purity electrolyte chemicals and reagents for research. https://www.sigmaaldrich.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SGLCarbon</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q2361947</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SGL Carbon SE; manufacturer of Sigracet GDL series (22BB, 28BC, 29BC, 39BB, 39BC) for fuel cells and electrolyzers. https://www.sglcarbon.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Solvay</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q487209</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Solvay S.A.; manufacturer of Aquivion short-side-chain PFSA CEM series (E87-05S, E87-12S, E98-05S) for PEM electrolyzers. https://www.solvay.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Solvionic</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q30285492</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Solvionic; French manufacturer and supplier of ionic liquids and specialty electrolyte solutions for electrochemical research. https://www.solvionic.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q306455</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific; global supplier of laboratory chemicals, reagents and analytical instruments. https://www.thermofisher.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Toray</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q908461</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Toray Industries; manufacturer of Toray carbon paper GDL series (TGP-H-060, TGP-H-090, TGP-H-120) for fuel cells and electrolyzers. https://www.toray.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Fumatech</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q30254565</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FuMA-Tech GmbH; manufacturer of FAA-3-50 and FAP-375-PP AEM series, Fumapem F/SF CEM series, and FBM bipolar membrane. https://www.fumatech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Hohsen</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q138782243</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Hohsen Corp.; Japanese manufacturer of specialty separators and ion exchange membranes for electrochemical applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Astom</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Astom Corporation (formerly Tokuyama); manufacturer of Neosepta ion exchange membrane series (AMX, CMX, AHA, BP-1). https://www.astom-corp.jp. to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AvCarb</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AvCarb Material Solutions; manufacturer of carbon GDL series (P75, MGL190, 1071HCB) and MPLs. https://www.avcarb.com. to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Dioxide Materials</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Dioxide Materials; manufacturer of Sustainion X37-50 anion exchange membrane (PolyArylPiperidinium backbone, 50 µm). https://www.dioxidematerials.com. to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>El-Cell</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EL-CELL GmbH; developer of high-precision electrochemical testing equipment and battery research solutions. https://el-cell.com, to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ionomr</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ionomr Innovations; manufacturer of Aemion+ AEM series (AF1-HNN5-50-X, AF1-HWW8-25-X) based on poly(arylene imidazolium) backbone. https://www.ionomr.com. to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sigracet</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SIGRACET Fuel Cell Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sterlitech</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sterlitech Corporation; provider of PTFE membranes (0.05 μm to 10.0 μm) for chemical venting, gas diffusion, and aggressive solvent filtration. https://www.sterlitech.com, to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Versogen</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Versogen Inc.; manufacturer of PiperION AEM series based on poly(aryl piperidinium) backbone for CO2 electrolysis and fuel cells. https://www.versogen.com. to be requested</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unit class</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -825,7 +825,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>0.2.0</t>
+          <t>0.2.1</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -4500,7 +4500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="74" customWidth="1" min="1" max="1"/>
@@ -4947,6 +4947,23 @@
       <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Raw electrochemical data, Biologic EC-Lab mpr binary format</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Input fileA</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>empa__ecid000001/empa__ecid000001.mps</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Measurement protocol, Biologic EC-Lab settings file</t>
         </is>
       </c>
     </row>

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>emmo:MilliAmpereHourPerSquareCentiMetre</t>
+          <t>MilliAmpereHourPerSquareCentiMetre</t>
         </is>
       </c>
     </row>

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F172"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="74" customWidth="1" min="1" max="1"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>240616_bco_gr-NMC_01</t>
+          <t>240616_bco_Cu-IrO2_01</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -1220,12 +1220,10 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Negative electrode coating active material particle size (leave blank for films)</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n">
-        <v>0.02</v>
-      </c>
+          <t>Negative electrode substrate mean pore size</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="inlineStr">
         <is>
           <t>um</t>
@@ -1239,610 +1237,624 @@
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="inlineStr">
         <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-MeanPoreSize</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode coating active material particle size (leave blank for films)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-D50ParticleSize</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Negative electrode optional component manufacturer information</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Negative electrode manufacturer</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Empa</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Negative electrode manufacturer product ID</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>15p_Cu</t>
         </is>
       </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Negative electrode substrate manufacturer</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>SGLCarbon</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>Negative electrode substrate product ID</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>39BB</t>
         </is>
       </c>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Negative electrode coating active material manufacturer</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Millipore Sigma</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Negative electrode coating active material product ID</t>
         </is>
       </c>
-      <c r="B36" s="8" t="n">
+      <c r="B37" s="8" t="n">
         <v>774081</v>
       </c>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Negative electrode coating binder manufacturer</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Chemours</t>
         </is>
       </c>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasBinder-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Negative electrode coating binder product ID</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>D521CS</t>
         </is>
       </c>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasBinder-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Positive electrode (counter electrode)</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Positive electrode type</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>ImmersionElectrode</t>
         </is>
       </c>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>Positive electrode substrate type</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>PerforatedFoil</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Positive electrode substrate material</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Titanium</t>
         </is>
       </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Positive electrode substrate thickness</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B44" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>um</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Positive electrode coating active material type</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Electrocatalyst</t>
         </is>
       </c>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Positive electrode coating active material</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>IridiumIIIOxide</t>
         </is>
       </c>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="C46" s="12" t="n"/>
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Positive electrode coating active material mass loading</t>
         </is>
       </c>
-      <c r="B46" s="4" t="n">
+      <c r="B47" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>mg/cm2</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassLoading</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>Positive electrode coating active material mass fraction</t>
         </is>
       </c>
-      <c r="B47" s="12" t="n">
+      <c r="B48" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n"/>
-      <c r="F47" s="12" t="inlineStr">
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassFraction</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Positive electrode coating binder type</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>IonomerCompound</t>
         </is>
       </c>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasBinder</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>Positive electrode coating binder material</t>
         </is>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>PerfluorosulfonicAcid</t>
         </is>
       </c>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n"/>
-      <c r="F49" s="12" t="inlineStr">
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasBinder</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Positive electrode coating binder mass fraction</t>
         </is>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="B51" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasBinder-hasMeasuredProperty-MassFraction</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>Positive electrode coating  thickness</t>
         </is>
       </c>
-      <c r="B51" s="12" t="n">
+      <c r="B52" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>um</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n"/>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="13" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>Positive electrode optional microstructural/physical parameters</t>
         </is>
       </c>
-      <c r="B52" s="11" t="n"/>
-      <c r="C52" s="11" t="n"/>
-      <c r="D52" s="11" t="n"/>
-      <c r="E52" s="11" t="n"/>
-      <c r="F52" s="11" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="B53" s="11" t="n"/>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="11" t="n"/>
+      <c r="F53" s="11" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Positive electrode substrate porosity</t>
         </is>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="B54" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Porosity</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>Positive electrode coating active material mean particle size (leave blank for films)</t>
-        </is>
-      </c>
-      <c r="B54" s="12" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="C54" s="12" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Positive electrode substrate mean pore size</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="n"/>
+      <c r="C55" s="12" t="inlineStr">
         <is>
           <t>um</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="n"/>
-      <c r="F54" s="12" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-D50ParticleSize</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>Positive electrode optional component manufacturer information</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="n"/>
-      <c r="C55" s="11" t="n"/>
-      <c r="D55" s="11" t="n"/>
-      <c r="E55" s="11" t="n"/>
-      <c r="F55" s="11" t="n"/>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="n"/>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-MeanPoreSize</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode manufacturer</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Empa</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="n"/>
+          <t>Positive electrode coating active material mean particle size (leave blank for films)</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -1851,43 +1863,31 @@
       <c r="E56" s="4" t="n"/>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-schema:manufacturer</t>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-D50ParticleSize</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>Positive electrode manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>18x_Ti</t>
-        </is>
-      </c>
-      <c r="C57" s="12" t="n"/>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E57" s="12" t="n"/>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-schema:productID</t>
-        </is>
-      </c>
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>Positive electrode optional component manufacturer information</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n"/>
+      <c r="C57" s="11" t="n"/>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="11" t="n"/>
+      <c r="F57" s="11" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode substrate manufacturer</t>
+          <t>Positive electrode manufacturer</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Fuel Cell Store</t>
+          <t>Empa</t>
         </is>
       </c>
       <c r="C58" s="4" t="n"/>
@@ -1899,18 +1899,20 @@
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasSubstrate-schema:manufacturer</t>
+          <t>hasPositiveElectrode-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Positive electrode substrate manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B59" s="12" t="n">
-        <v>40050001</v>
+          <t>Positive electrode manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>18x_Ti</t>
+        </is>
       </c>
       <c r="C59" s="12" t="n"/>
       <c r="D59" s="12" t="inlineStr">
@@ -1921,14 +1923,14 @@
       <c r="E59" s="12" t="n"/>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasSubstrate-schema:productID</t>
+          <t>hasPositiveElectrode-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material manufacturer</t>
+          <t>Positive electrode substrate manufacturer</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -1945,18 +1947,18 @@
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-schema:manufacturer</t>
+          <t>hasPositiveElectrode-hasSubstrate-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material manufacturer product ID</t>
+          <t>Positive electrode substrate manufacturer product ID</t>
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>57080249</v>
+        <v>40050001</v>
       </c>
       <c r="C61" s="12" t="n"/>
       <c r="D61" s="12" t="inlineStr">
@@ -1967,19 +1969,19 @@
       <c r="E61" s="12" t="n"/>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-schema:productID</t>
+          <t>hasPositiveElectrode-hasSubstrate-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode coating binder manufacturer</t>
+          <t>Positive electrode coating active material manufacturer</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Chemours</t>
+          <t>Fuel Cell Store</t>
         </is>
       </c>
       <c r="C62" s="4" t="n"/>
@@ -1991,20 +1993,18 @@
       <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-hasBinder-schema:manufacturer</t>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>Positive electrode coating binder manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B63" s="12" t="inlineStr">
-        <is>
-          <t>D521CS</t>
-        </is>
+          <t>Positive electrode coating active material manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="n">
+        <v>57080249</v>
       </c>
       <c r="C63" s="12" t="n"/>
       <c r="D63" s="12" t="inlineStr">
@@ -2015,81 +2015,79 @@
       <c r="E63" s="12" t="n"/>
       <c r="F63" s="12" t="inlineStr">
         <is>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode coating binder manufacturer</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Chemours</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="n"/>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-hasBinder-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>Positive electrode coating binder manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>D521CS</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="n"/>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="n"/>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
           <t>hasPositiveElectrode-hasCoating-hasBinder-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="14" t="inlineStr">
         <is>
           <t>Negative electrode gas supply</t>
         </is>
       </c>
-      <c r="B64" s="15" t="n"/>
-      <c r="C64" s="15" t="n"/>
-      <c r="D64" s="15" t="n"/>
-      <c r="E64" s="15" t="n"/>
-      <c r="F64" s="15" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>Negative electrode gas A</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>CarbonDioxide</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="n"/>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-Gas</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="16" t="inlineStr">
-        <is>
-          <t>Negative electrode gas A volume fraction</t>
-        </is>
-      </c>
-      <c r="B66" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="C66" s="16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E66" s="16" t="n"/>
-      <c r="F66" s="16" t="inlineStr">
-        <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
-        </is>
-      </c>
+      <c r="B66" s="15" t="n"/>
+      <c r="C66" s="15" t="n"/>
+      <c r="D66" s="15" t="n"/>
+      <c r="E66" s="15" t="n"/>
+      <c r="F66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Negative electrode gas B</t>
+          <t>Negative electrode gas A</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Argon</t>
+          <t>CarbonDioxide</t>
         </is>
       </c>
       <c r="C67" s="4" t="n"/>
@@ -2101,18 +2099,18 @@
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-Gas</t>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-Gas</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Negative electrode gas B volume fraction</t>
+          <t>Negative electrode gas A volume fraction</t>
         </is>
       </c>
       <c r="B68" s="16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C68" s="16" t="inlineStr">
         <is>
@@ -2127,24 +2125,22 @@
       <c r="E68" s="16" t="n"/>
       <c r="F68" s="16" t="inlineStr">
         <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Negative electrode gas flow rate</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>mL/min</t>
-        </is>
-      </c>
+          <t>Negative electrode gas B</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n"/>
       <c r="D69" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -2153,22 +2149,22 @@
       <c r="E69" s="4" t="n"/>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-Gas</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Negative electrode gas pressure</t>
+          <t>Negative electrode gas B volume fraction</t>
         </is>
       </c>
       <c r="B70" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C70" s="16" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
@@ -2179,99 +2175,107 @@
       <c r="E70" s="16" t="n"/>
       <c r="F70" s="16" t="inlineStr">
         <is>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode gas flow rate</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="n"/>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>Negative electrode gas pressure</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E72" s="16" t="n"/>
+      <c r="F72" s="16" t="inlineStr">
+        <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="14" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
         <is>
           <t>Catholyte</t>
         </is>
       </c>
-      <c r="B71" s="15" t="n"/>
-      <c r="C71" s="15" t="n"/>
-      <c r="D71" s="15" t="n"/>
-      <c r="E71" s="15" t="n"/>
-      <c r="F71" s="15" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>Catholyte solvent A</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="n"/>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="n"/>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="16" t="inlineStr">
-        <is>
-          <t>Catholyte solvent A volume fraction</t>
-        </is>
-      </c>
-      <c r="B73" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="C73" s="16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D73" s="16" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E73" s="16" t="n"/>
-      <c r="F73" s="16" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
-        </is>
-      </c>
+      <c r="B73" s="15" t="n"/>
+      <c r="C73" s="15" t="n"/>
+      <c r="D73" s="15" t="n"/>
+      <c r="E73" s="15" t="n"/>
+      <c r="F73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Catholyte solvent B</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="n"/>
+          <t>Catholyte solvent A</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
       <c r="C74" s="4" t="n"/>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>Catholyte solvent B volume fraction</t>
-        </is>
-      </c>
-      <c r="B75" s="16" t="n"/>
+          <t>Catholyte solvent A volume fraction</t>
+        </is>
+      </c>
+      <c r="B75" s="16" t="n">
+        <v>100</v>
+      </c>
       <c r="C75" s="16" t="inlineStr">
         <is>
           <t>%</t>
@@ -2279,93 +2283,93 @@
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E75" s="16" t="n"/>
       <c r="F75" s="16" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Catholyte solute A</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>PotassiumCarbonate</t>
-        </is>
-      </c>
+          <t>Catholyte solvent B</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n"/>
       <c r="C76" s="4" t="n"/>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>Catholyte solute A molarity</t>
-        </is>
-      </c>
-      <c r="B77" s="16" t="n">
-        <v>1</v>
-      </c>
+          <t>Catholyte solvent B volume fraction</t>
+        </is>
+      </c>
+      <c r="B77" s="16" t="n"/>
       <c r="C77" s="16" t="inlineStr">
         <is>
-          <t>mol/L</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E77" s="16" t="n"/>
       <c r="F77" s="16" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Catholyte solute B</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="n"/>
+          <t>Catholyte solute A</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>PotassiumCarbonate</t>
+        </is>
+      </c>
       <c r="C78" s="4" t="n"/>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>Catholyte solute B molarity</t>
-        </is>
-      </c>
-      <c r="B79" s="16" t="n"/>
+          <t>Catholyte solute A molarity</t>
+        </is>
+      </c>
+      <c r="B79" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="C79" s="16" t="inlineStr">
         <is>
           <t>mol/L</t>
@@ -2373,80 +2377,72 @@
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E79" s="16" t="n"/>
       <c r="F79" s="16" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Catholyte volume</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>mL</t>
-        </is>
-      </c>
+          <t>Catholyte solute B</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="n"/>
+      <c r="C80" s="4" t="n"/>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E80" s="4" t="n"/>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-Volume</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>Catholyte volume flow rate</t>
-        </is>
-      </c>
-      <c r="B81" s="16" t="n">
-        <v>5</v>
-      </c>
+          <t>Catholyte solute B molarity</t>
+        </is>
+      </c>
+      <c r="B81" s="16" t="n"/>
       <c r="C81" s="16" t="inlineStr">
         <is>
-          <t>mL/min</t>
+          <t>mol/L</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E81" s="16" t="n"/>
       <c r="F81" s="16" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-VolumeFlowRate</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Catholyte pressure</t>
+          <t>Catholyte volume</t>
         </is>
       </c>
       <c r="B82" s="4" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -2457,86 +2453,86 @@
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-Pressure</t>
+          <t>hasCatholyte-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="17" t="inlineStr">
-        <is>
-          <t>Catholyte optional physical parameters</t>
-        </is>
-      </c>
-      <c r="B83" s="15" t="n"/>
-      <c r="C83" s="15" t="n"/>
-      <c r="D83" s="15" t="n"/>
-      <c r="E83" s="15" t="n"/>
-      <c r="F83" s="15" t="n"/>
+      <c r="A83" s="16" t="inlineStr">
+        <is>
+          <t>Catholyte volume flow rate</t>
+        </is>
+      </c>
+      <c r="B83" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C83" s="16" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
+      <c r="D83" s="16" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E83" s="16" t="n"/>
+      <c r="F83" s="16" t="inlineStr">
+        <is>
+          <t>hasCatholyte-hasMeasuredProperty-VolumeFlowRate</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Catholyte conductivity</t>
+          <t>Catholyte pressure</t>
         </is>
       </c>
       <c r="B84" s="4" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>mS/cm</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E84" s="4" t="n"/>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-ElectrolyticConductivity</t>
+          <t>hasCatholyte-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="inlineStr">
-        <is>
-          <t>Catholyte pH</t>
-        </is>
-      </c>
-      <c r="B85" s="16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C85" s="16" t="inlineStr">
-        <is>
-          <t>unitless</t>
-        </is>
-      </c>
-      <c r="D85" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E85" s="16" t="n"/>
-      <c r="F85" s="16" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasMeasuredProperty-PH</t>
-        </is>
-      </c>
+      <c r="A85" s="17" t="inlineStr">
+        <is>
+          <t>Catholyte optional physical parameters</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="n"/>
+      <c r="C85" s="15" t="n"/>
+      <c r="D85" s="15" t="n"/>
+      <c r="E85" s="15" t="n"/>
+      <c r="F85" s="15" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Catholyte density</t>
+          <t>Catholyte conductivity</t>
         </is>
       </c>
       <c r="B86" s="4" t="n">
-        <v>1.1</v>
+        <v>100</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>g/cm3</t>
+          <t>mS/cm</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2547,22 +2543,22 @@
       <c r="E86" s="4" t="n"/>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-Density</t>
+          <t>hasCatholyte-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>Catholyte temperature</t>
+          <t>Catholyte pH</t>
         </is>
       </c>
       <c r="B87" s="16" t="n">
-        <v>25</v>
+        <v>3.8</v>
       </c>
       <c r="C87" s="16" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>unitless</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
@@ -2573,77 +2569,85 @@
       <c r="E87" s="16" t="n"/>
       <c r="F87" s="16" t="inlineStr">
         <is>
+          <t>hasCatholyte-hasMeasuredProperty-PH</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Catholyte density</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>g/cm3</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="n"/>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>hasCatholyte-hasMeasuredProperty-Density</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>Catholyte temperature</t>
+        </is>
+      </c>
+      <c r="B89" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="C89" s="16" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="n"/>
+      <c r="F89" s="16" t="inlineStr">
+        <is>
           <t>hasCatholyte-hasMeasuredProperty-CelsiusTemperature</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="17" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="17" t="inlineStr">
         <is>
           <t>Catholyte optional component manufacturer information</t>
         </is>
       </c>
-      <c r="B88" s="15" t="n"/>
-      <c r="C88" s="15" t="n"/>
-      <c r="D88" s="15" t="n"/>
-      <c r="E88" s="15" t="n"/>
-      <c r="F88" s="15" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>Catholyte manufacturer</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Empa</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="n"/>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="n"/>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>hasCatholyte-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="16" t="inlineStr">
-        <is>
-          <t>Catholyte manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B90" s="16" t="inlineStr">
-        <is>
-          <t>KCl_1M_catholyte</t>
-        </is>
-      </c>
-      <c r="C90" s="16" t="n"/>
-      <c r="D90" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E90" s="16" t="n"/>
-      <c r="F90" s="16" t="inlineStr">
-        <is>
-          <t>hasCatholyte-schema:productID</t>
-        </is>
-      </c>
+      <c r="B90" s="15" t="n"/>
+      <c r="C90" s="15" t="n"/>
+      <c r="D90" s="15" t="n"/>
+      <c r="E90" s="15" t="n"/>
+      <c r="F90" s="15" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Catholyte solvent A manufacturer</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n"/>
+          <t>Catholyte manufacturer</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
       <c r="C91" s="4" t="n"/>
       <c r="D91" s="4" t="inlineStr">
         <is>
@@ -2653,17 +2657,21 @@
       <c r="E91" s="4" t="n"/>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolventA-schema:manufacturer</t>
+          <t>hasCatholyte-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="16" t="inlineStr">
         <is>
-          <t>Catholyte solvent A manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B92" s="16" t="n"/>
+          <t>Catholyte manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>KCl_1M_catholyte</t>
+        </is>
+      </c>
       <c r="C92" s="16" t="n"/>
       <c r="D92" s="16" t="inlineStr">
         <is>
@@ -2673,14 +2681,14 @@
       <c r="E92" s="16" t="n"/>
       <c r="F92" s="16" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolventA-schema:productID</t>
+          <t>hasCatholyte-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Catholyte solvent B manufacturer</t>
+          <t>Catholyte solvent A manufacturer</t>
         </is>
       </c>
       <c r="B93" s="4" t="n"/>
@@ -2693,14 +2701,14 @@
       <c r="E93" s="4" t="n"/>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolventB-schema:manufacturer</t>
+          <t>hasCatholyte-hasSolventA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="16" t="inlineStr">
         <is>
-          <t>Catholyte solvent B manufacturer product ID</t>
+          <t>Catholyte solvent A manufacturer product ID</t>
         </is>
       </c>
       <c r="B94" s="16" t="n"/>
@@ -2713,21 +2721,17 @@
       <c r="E94" s="16" t="n"/>
       <c r="F94" s="16" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolventB-schema:productID</t>
+          <t>hasCatholyte-hasSolventA-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Catholyte solute A manufacturer</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Thermo Fisher Scientific</t>
-        </is>
-      </c>
+          <t>Catholyte solvent B manufacturer</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="n"/>
       <c r="C95" s="4" t="n"/>
       <c r="D95" s="4" t="inlineStr">
         <is>
@@ -2737,19 +2741,17 @@
       <c r="E95" s="4" t="n"/>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSoluteA-schema:manufacturer</t>
+          <t>hasCatholyte-hasSolventB-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="16" t="inlineStr">
         <is>
-          <t>Catholyte solute A manufacturer productD</t>
-        </is>
-      </c>
-      <c r="B96" s="16" t="n">
-        <v>424090010</v>
-      </c>
+          <t>Catholyte solvent B manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B96" s="16" t="n"/>
       <c r="C96" s="16" t="n"/>
       <c r="D96" s="16" t="inlineStr">
         <is>
@@ -2759,17 +2761,21 @@
       <c r="E96" s="16" t="n"/>
       <c r="F96" s="16" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSoluteA-schema:productID</t>
+          <t>hasCatholyte-hasSolventB-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Catholyte solute B manufacturer</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="n"/>
+          <t>Catholyte solute A manufacturer</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
       <c r="C97" s="4" t="n"/>
       <c r="D97" s="4" t="inlineStr">
         <is>
@@ -2779,17 +2785,19 @@
       <c r="E97" s="4" t="n"/>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSoluteB-schema:manufacturer</t>
+          <t>hasCatholyte-hasSoluteA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="16" t="inlineStr">
         <is>
-          <t>Catholyte solute B manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B98" s="16" t="n"/>
+          <t>Catholyte solute A manufacturer productD</t>
+        </is>
+      </c>
+      <c r="B98" s="16" t="n">
+        <v>424090010</v>
+      </c>
       <c r="C98" s="16" t="n"/>
       <c r="D98" s="16" t="inlineStr">
         <is>
@@ -2799,79 +2807,73 @@
       <c r="E98" s="16" t="n"/>
       <c r="F98" s="16" t="inlineStr">
         <is>
+          <t>hasCatholyte-hasSoluteA-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>Catholyte solute B manufacturer</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="n"/>
+      <c r="C99" s="4" t="n"/>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="n"/>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>hasCatholyte-hasSoluteB-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Catholyte solute B manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B100" s="16" t="n"/>
+      <c r="C100" s="16" t="n"/>
+      <c r="D100" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E100" s="16" t="n"/>
+      <c r="F100" s="16" t="inlineStr">
+        <is>
           <t>hasCatholyte-hasSoluteB-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="14" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="14" t="inlineStr">
         <is>
           <t>Positive electrode gas supply</t>
         </is>
       </c>
-      <c r="B99" s="15" t="n"/>
-      <c r="C99" s="15" t="n"/>
-      <c r="D99" s="15" t="n"/>
-      <c r="E99" s="15" t="n"/>
-      <c r="F99" s="15" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>Positive electrode gas A</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>Nitrogen</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="n"/>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="n"/>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-Gas</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="16" t="inlineStr">
-        <is>
-          <t>Positive electrode gas A volume fraction</t>
-        </is>
-      </c>
-      <c r="B101" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="C101" s="16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D101" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E101" s="16" t="n"/>
-      <c r="F101" s="16" t="inlineStr">
-        <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
-        </is>
-      </c>
+      <c r="B101" s="15" t="n"/>
+      <c r="C101" s="15" t="n"/>
+      <c r="D101" s="15" t="n"/>
+      <c r="E101" s="15" t="n"/>
+      <c r="F101" s="15" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode gas B</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="n"/>
+          <t>Positive electrode gas A</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Nitrogen</t>
+        </is>
+      </c>
       <c r="C102" s="4" t="n"/>
       <c r="D102" s="4" t="inlineStr">
         <is>
@@ -2881,17 +2883,19 @@
       <c r="E102" s="4" t="n"/>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-Gas</t>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-Gas</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="16" t="inlineStr">
         <is>
-          <t>Positive electrode gas B volume fraction</t>
-        </is>
-      </c>
-      <c r="B103" s="16" t="n"/>
+          <t>Positive electrode gas A volume fraction</t>
+        </is>
+      </c>
+      <c r="B103" s="16" t="n">
+        <v>100</v>
+      </c>
       <c r="C103" s="16" t="inlineStr">
         <is>
           <t>%</t>
@@ -2905,24 +2909,18 @@
       <c r="E103" s="16" t="n"/>
       <c r="F103" s="16" t="inlineStr">
         <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode gas flow rate</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>mL/min</t>
-        </is>
-      </c>
+          <t>Positive electrode gas B</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="n"/>
+      <c r="C104" s="4" t="n"/>
       <c r="D104" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2931,22 +2929,20 @@
       <c r="E104" s="4" t="n"/>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-Gas</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="16" t="inlineStr">
         <is>
-          <t>Positive electrode gas pressure</t>
-        </is>
-      </c>
-      <c r="B105" s="16" t="n">
-        <v>1</v>
-      </c>
+          <t>Positive electrode gas B volume fraction</t>
+        </is>
+      </c>
+      <c r="B105" s="16" t="n"/>
       <c r="C105" s="16" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D105" s="16" t="inlineStr">
@@ -2957,99 +2953,107 @@
       <c r="E105" s="16" t="n"/>
       <c r="F105" s="16" t="inlineStr">
         <is>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode gas flow rate</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="n"/>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="16" t="inlineStr">
+        <is>
+          <t>Positive electrode gas pressure</t>
+        </is>
+      </c>
+      <c r="B107" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" s="16" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="D107" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E107" s="16" t="n"/>
+      <c r="F107" s="16" t="inlineStr">
+        <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="14" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="14" t="inlineStr">
         <is>
           <t>Anolyte</t>
         </is>
       </c>
-      <c r="B106" s="15" t="n"/>
-      <c r="C106" s="15" t="n"/>
-      <c r="D106" s="15" t="n"/>
-      <c r="E106" s="15" t="n"/>
-      <c r="F106" s="15" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>Anolyte solvent A</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="n"/>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="n"/>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="16" t="inlineStr">
-        <is>
-          <t>Anolyte solvent A volume fraction</t>
-        </is>
-      </c>
-      <c r="B108" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="C108" s="16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D108" s="16" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E108" s="16" t="n"/>
-      <c r="F108" s="16" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
-        </is>
-      </c>
+      <c r="B108" s="15" t="n"/>
+      <c r="C108" s="15" t="n"/>
+      <c r="D108" s="15" t="n"/>
+      <c r="E108" s="15" t="n"/>
+      <c r="F108" s="15" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Anolyte solvent B</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="n"/>
+          <t>Anolyte solvent A</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
       <c r="C109" s="4" t="n"/>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E109" s="4" t="n"/>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="16" t="inlineStr">
         <is>
-          <t>Anolyte solvent B volume fraction</t>
-        </is>
-      </c>
-      <c r="B110" s="16" t="n"/>
+          <t>Anolyte solvent A volume fraction</t>
+        </is>
+      </c>
+      <c r="B110" s="16" t="n">
+        <v>100</v>
+      </c>
       <c r="C110" s="16" t="inlineStr">
         <is>
           <t>%</t>
@@ -3057,93 +3061,93 @@
       </c>
       <c r="D110" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E110" s="16" t="n"/>
       <c r="F110" s="16" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Anolyte solute A</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>SulfuricAcid</t>
-        </is>
-      </c>
+          <t>Anolyte solvent B</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="n"/>
       <c r="C111" s="4" t="n"/>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E111" s="4" t="n"/>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="16" t="inlineStr">
         <is>
-          <t>Anolyte solute A molarity</t>
-        </is>
-      </c>
-      <c r="B112" s="16" t="n">
-        <v>1</v>
-      </c>
+          <t>Anolyte solvent B volume fraction</t>
+        </is>
+      </c>
+      <c r="B112" s="16" t="n"/>
       <c r="C112" s="16" t="inlineStr">
         <is>
-          <t>mol/L</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D112" s="16" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E112" s="16" t="n"/>
       <c r="F112" s="16" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Anolyte solute B</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="n"/>
+          <t>Anolyte solute A</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>SulfuricAcid</t>
+        </is>
+      </c>
       <c r="C113" s="4" t="n"/>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E113" s="4" t="n"/>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="16" t="inlineStr">
         <is>
-          <t>Anolyte solute B molarity</t>
-        </is>
-      </c>
-      <c r="B114" s="16" t="n"/>
+          <t>Anolyte solute A molarity</t>
+        </is>
+      </c>
+      <c r="B114" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="C114" s="16" t="inlineStr">
         <is>
           <t>mol/L</t>
@@ -3151,80 +3155,72 @@
       </c>
       <c r="D114" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E114" s="16" t="n"/>
       <c r="F114" s="16" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>Anolyte volume</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>mL</t>
-        </is>
-      </c>
+          <t>Anolyte solute B</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="n"/>
+      <c r="C115" s="4" t="n"/>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E115" s="4" t="n"/>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-Volume</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="16" t="inlineStr">
         <is>
-          <t>Anolyte volume flow rate</t>
-        </is>
-      </c>
-      <c r="B116" s="16" t="n">
-        <v>5</v>
-      </c>
+          <t>Anolyte solute B molarity</t>
+        </is>
+      </c>
+      <c r="B116" s="16" t="n"/>
       <c r="C116" s="16" t="inlineStr">
         <is>
-          <t>mL/min</t>
+          <t>mol/L</t>
         </is>
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E116" s="16" t="n"/>
       <c r="F116" s="16" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-VolumeFlowRate</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>Anolyte pressure</t>
+          <t>Anolyte volume</t>
         </is>
       </c>
       <c r="B117" s="4" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -3235,86 +3231,86 @@
       <c r="E117" s="4" t="n"/>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-Pressure</t>
+          <t>hasAnolyte-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="17" t="inlineStr">
-        <is>
-          <t>Anolyte optional physical parameters</t>
-        </is>
-      </c>
-      <c r="B118" s="15" t="n"/>
-      <c r="C118" s="15" t="n"/>
-      <c r="D118" s="15" t="n"/>
-      <c r="E118" s="15" t="n"/>
-      <c r="F118" s="15" t="n"/>
+      <c r="A118" s="16" t="inlineStr">
+        <is>
+          <t>Anolyte volume flow rate</t>
+        </is>
+      </c>
+      <c r="B118" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C118" s="16" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
+      <c r="D118" s="16" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E118" s="16" t="n"/>
+      <c r="F118" s="16" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasMeasuredProperty-VolumeFlowRate</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>Anolyte conductivity</t>
+          <t>Anolyte pressure</t>
         </is>
       </c>
       <c r="B119" s="4" t="n">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>mS/cm</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E119" s="4" t="n"/>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-ElectrolyticConductivity</t>
+          <t>hasAnolyte-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="16" t="inlineStr">
-        <is>
-          <t>Anolyte pH</t>
-        </is>
-      </c>
-      <c r="B120" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C120" s="16" t="inlineStr">
-        <is>
-          <t>unitless</t>
-        </is>
-      </c>
-      <c r="D120" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E120" s="16" t="n"/>
-      <c r="F120" s="16" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasMeasuredProperty-PH</t>
-        </is>
-      </c>
+      <c r="A120" s="17" t="inlineStr">
+        <is>
+          <t>Anolyte optional physical parameters</t>
+        </is>
+      </c>
+      <c r="B120" s="15" t="n"/>
+      <c r="C120" s="15" t="n"/>
+      <c r="D120" s="15" t="n"/>
+      <c r="E120" s="15" t="n"/>
+      <c r="F120" s="15" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>Anolyte density</t>
+          <t>Anolyte conductivity</t>
         </is>
       </c>
       <c r="B121" s="4" t="n">
-        <v>1.06</v>
+        <v>800</v>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>g/cm3</t>
+          <t>mS/cm</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -3325,22 +3321,22 @@
       <c r="E121" s="4" t="n"/>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-Density</t>
+          <t>hasAnolyte-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="16" t="inlineStr">
         <is>
-          <t>Anolyte temperature</t>
+          <t>Anolyte pH</t>
         </is>
       </c>
       <c r="B122" s="16" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C122" s="16" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>unitless</t>
         </is>
       </c>
       <c r="D122" s="16" t="inlineStr">
@@ -3351,77 +3347,85 @@
       <c r="E122" s="16" t="n"/>
       <c r="F122" s="16" t="inlineStr">
         <is>
+          <t>hasAnolyte-hasMeasuredProperty-PH</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>Anolyte density</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>g/cm3</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="n"/>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasMeasuredProperty-Density</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="16" t="inlineStr">
+        <is>
+          <t>Anolyte temperature</t>
+        </is>
+      </c>
+      <c r="B124" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="C124" s="16" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="D124" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E124" s="16" t="n"/>
+      <c r="F124" s="16" t="inlineStr">
+        <is>
           <t>hasAnolyte-hasMeasuredProperty-CelsiusTemperature</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="17" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="17" t="inlineStr">
         <is>
           <t>Anolyte optional component manufacturer information</t>
         </is>
       </c>
-      <c r="B123" s="15" t="n"/>
-      <c r="C123" s="15" t="n"/>
-      <c r="D123" s="15" t="n"/>
-      <c r="E123" s="15" t="n"/>
-      <c r="F123" s="15" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="4" t="inlineStr">
-        <is>
-          <t>Anolyte manufacturer</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>Empa</t>
-        </is>
-      </c>
-      <c r="C124" s="4" t="n"/>
-      <c r="D124" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="n"/>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>hasAnolyte-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="16" t="inlineStr">
-        <is>
-          <t>Anolyte manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B125" s="16" t="inlineStr">
-        <is>
-          <t>H2SO4_1M_anolyte</t>
-        </is>
-      </c>
-      <c r="C125" s="16" t="n"/>
-      <c r="D125" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E125" s="16" t="n"/>
-      <c r="F125" s="16" t="inlineStr">
-        <is>
-          <t>hasAnolyte-schema:productID</t>
-        </is>
-      </c>
+      <c r="B125" s="15" t="n"/>
+      <c r="C125" s="15" t="n"/>
+      <c r="D125" s="15" t="n"/>
+      <c r="E125" s="15" t="n"/>
+      <c r="F125" s="15" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>Anolyte solvent A manufacturer</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="n"/>
+          <t>Anolyte manufacturer</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
       <c r="C126" s="4" t="n"/>
       <c r="D126" s="4" t="inlineStr">
         <is>
@@ -3431,17 +3435,21 @@
       <c r="E126" s="4" t="n"/>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-schema:manufacturer</t>
+          <t>hasAnolyte-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="16" t="inlineStr">
         <is>
-          <t>Anolyte solvent A manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B127" s="16" t="n"/>
+          <t>Anolyte manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B127" s="16" t="inlineStr">
+        <is>
+          <t>H2SO4_1M_anolyte</t>
+        </is>
+      </c>
       <c r="C127" s="16" t="n"/>
       <c r="D127" s="16" t="inlineStr">
         <is>
@@ -3451,14 +3459,14 @@
       <c r="E127" s="16" t="n"/>
       <c r="F127" s="16" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-schema:productID</t>
+          <t>hasAnolyte-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>Anolyte solvent B manufacturer</t>
+          <t>Anolyte solvent A manufacturer</t>
         </is>
       </c>
       <c r="B128" s="4" t="n"/>
@@ -3478,7 +3486,7 @@
     <row r="129">
       <c r="A129" s="16" t="inlineStr">
         <is>
-          <t>Anolyte solvent B manufacturer product ID</t>
+          <t>Anolyte solvent A manufacturer product ID</t>
         </is>
       </c>
       <c r="B129" s="16" t="n"/>
@@ -3498,14 +3506,10 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>Anolyte solute A manufacturer</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>Millipore Sigma</t>
-        </is>
-      </c>
+          <t>Anolyte solvent B manufacturer</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="n"/>
       <c r="C130" s="4" t="n"/>
       <c r="D130" s="4" t="inlineStr">
         <is>
@@ -3515,19 +3519,17 @@
       <c r="E130" s="4" t="n"/>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-schema:manufacturer</t>
+          <t>hasAnolyte-hasSolvent-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="16" t="inlineStr">
         <is>
-          <t>Anolyte solute A manufacturer productD</t>
-        </is>
-      </c>
-      <c r="B131" s="16" t="n">
-        <v>258105</v>
-      </c>
+          <t>Anolyte solvent B manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B131" s="16" t="n"/>
       <c r="C131" s="16" t="n"/>
       <c r="D131" s="16" t="inlineStr">
         <is>
@@ -3537,17 +3539,21 @@
       <c r="E131" s="16" t="n"/>
       <c r="F131" s="16" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-schema:productID</t>
+          <t>hasAnolyte-hasSolvent-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>Anolyte solute B manufacturer</t>
-        </is>
-      </c>
-      <c r="B132" s="4" t="n"/>
+          <t>Anolyte solute A manufacturer</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>Millipore Sigma</t>
+        </is>
+      </c>
       <c r="C132" s="4" t="n"/>
       <c r="D132" s="4" t="inlineStr">
         <is>
@@ -3564,10 +3570,12 @@
     <row r="133">
       <c r="A133" s="16" t="inlineStr">
         <is>
-          <t>Anolyte solute B manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B133" s="16" t="n"/>
+          <t>Anolyte solute A manufacturer productD</t>
+        </is>
+      </c>
+      <c r="B133" s="16" t="n">
+        <v>258105</v>
+      </c>
       <c r="C133" s="16" t="n"/>
       <c r="D133" s="16" t="inlineStr">
         <is>
@@ -3582,74 +3590,66 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>Anolyte solute B manufacturer</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="n"/>
+      <c r="C134" s="4" t="n"/>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="n"/>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasSolute-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="16" t="inlineStr">
+        <is>
+          <t>Anolyte solute B manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B135" s="16" t="n"/>
+      <c r="C135" s="16" t="n"/>
+      <c r="D135" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E135" s="16" t="n"/>
+      <c r="F135" s="16" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasSolute-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>Membrane</t>
         </is>
       </c>
-      <c r="B134" s="3" t="n"/>
-      <c r="C134" s="3" t="n"/>
-      <c r="D134" s="3" t="n"/>
-      <c r="E134" s="3" t="n"/>
-      <c r="F134" s="3" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>Membrane type</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>IonExchangeMembrane</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="n"/>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="n"/>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>hasSeparator</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>Membrane type  (BilayerMembrane or leave blank)</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>BilayerMembrane</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="n"/>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="n"/>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>hasSeparator</t>
-        </is>
-      </c>
+      <c r="B136" s="3" t="n"/>
+      <c r="C136" s="3" t="n"/>
+      <c r="D136" s="3" t="n"/>
+      <c r="E136" s="3" t="n"/>
+      <c r="F136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>Membrane A type (facing catholyte)</t>
+          <t>Membrane type</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>AnionExchangeMembrane</t>
+          <t>IonExchangeMembrane</t>
         </is>
       </c>
       <c r="C137" s="4" t="n"/>
@@ -3661,317 +3661,323 @@
       <c r="E137" s="4" t="n"/>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasElectrolyteA</t>
+          <t>hasSeparator</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Membrane A material A (facing catholyte)</t>
+          <t>Membrane type</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>PolyArylPiperidinium</t>
+          <t>BilayerMembrane</t>
         </is>
       </c>
       <c r="C138" s="5" t="n"/>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="n"/>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>BilayerMembrane or leave blank</t>
+        </is>
+      </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>hasSeparator-hasElectrolyteA</t>
+          <t>hasSeparator</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>Membrane A thickness (facing catholyte)</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
+          <t>Membrane A type (facing catholyte)</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>AnionExchangeMembrane</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="n"/>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E139" s="4" t="n"/>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-Thickness</t>
+          <t>hasSeparator-hasElectrolyteA</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Membrane A ion exchange capacity (facing catholyte)</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C140" s="5" t="inlineStr">
-        <is>
-          <t>mEq/100g</t>
-        </is>
-      </c>
+          <t>Membrane A material A (facing catholyte)</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>PolyArylPiperidinium</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="n"/>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E140" s="5" t="n"/>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-AmountConcentration</t>
+          <t>hasSeparator-hasElectrolyteA</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>Membrane B type (facing anolyte)</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>CationExchangeMembrane</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="n"/>
+          <t>Membrane A thickness (facing catholyte)</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E141" s="4" t="n"/>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasElectrolyteB</t>
+          <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Membrane B material A (facing anolyte)</t>
-        </is>
-      </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>PerfluorosulfonicAcid</t>
-        </is>
-      </c>
-      <c r="C142" s="5" t="n"/>
+          <t>Membrane A ion exchange capacity (facing catholyte)</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>mEq/100g</t>
+        </is>
+      </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E142" s="5" t="n"/>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>hasSeparator-hasElectrolyteB</t>
+          <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>Membrane B thickness (facing anolyte)</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
+          <t>Membrane B type (facing anolyte)</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>CationExchangeMembrane</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="n"/>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E143" s="4" t="n"/>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-Thickness</t>
+          <t>hasSeparator-hasElectrolyteB</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>Membrane B ion exchange capacity (facing anolyte)</t>
-        </is>
-      </c>
-      <c r="B144" s="5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C144" s="5" t="inlineStr">
-        <is>
-          <t>mEq/100g</t>
-        </is>
-      </c>
+          <t>Membrane B material A (facing anolyte)</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>PerfluorosulfonicAcid</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="n"/>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E144" s="5" t="n"/>
       <c r="F144" s="5" t="inlineStr">
         <is>
+          <t>hasSeparator-hasElectrolyteB</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>Membrane B thickness (facing anolyte)</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="n"/>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-Thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>Membrane B ion exchange capacity (facing anolyte)</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>mEq/100g</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="n"/>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
           <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="18" t="inlineStr">
         <is>
           <t>Membrane optional physical parameters</t>
         </is>
       </c>
-      <c r="B145" s="3" t="n"/>
-      <c r="C145" s="3" t="n"/>
-      <c r="D145" s="3" t="n"/>
-      <c r="E145" s="3" t="n"/>
-      <c r="F145" s="3" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="4" t="inlineStr">
+      <c r="B147" s="3" t="n"/>
+      <c r="C147" s="3" t="n"/>
+      <c r="D147" s="3" t="n"/>
+      <c r="E147" s="3" t="n"/>
+      <c r="F147" s="3" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t>Membrane A area specific conductivity</t>
         </is>
       </c>
-      <c r="B146" s="4" t="n">
+      <c r="B148" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C146" s="4" t="inlineStr">
+      <c r="C148" s="4" t="inlineStr">
         <is>
           <t>mS/cm</t>
         </is>
       </c>
-      <c r="D146" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E146" s="4" t="n"/>
-      <c r="F146" s="4" t="inlineStr">
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="n"/>
+      <c r="F148" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="5" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
         <is>
           <t>Membrane B area specific conductivity</t>
         </is>
       </c>
-      <c r="B147" s="5" t="n">
+      <c r="B149" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C147" s="5" t="inlineStr">
+      <c r="C149" s="5" t="inlineStr">
         <is>
           <t>mS/cm</t>
         </is>
       </c>
-      <c r="D147" s="5" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E147" s="5" t="n"/>
-      <c r="F147" s="5" t="inlineStr">
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n"/>
+      <c r="F149" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="18" t="inlineStr">
         <is>
           <t>Membrane optional component manufacturer information</t>
         </is>
       </c>
-      <c r="B148" s="3" t="n"/>
-      <c r="C148" s="3" t="n"/>
-      <c r="D148" s="3" t="n"/>
-      <c r="E148" s="3" t="n"/>
-      <c r="F148" s="3" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>Membrane A manufacturer</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>Fuel Cell Store</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="n"/>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E149" s="4" t="n"/>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>hasSeparator-hasElectrolyteA-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>Membrane A manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B150" s="5" t="n">
-        <v>72010015</v>
-      </c>
-      <c r="C150" s="5" t="n"/>
-      <c r="D150" s="5" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E150" s="5" t="n"/>
-      <c r="F150" s="5" t="inlineStr">
-        <is>
-          <t>hasSeparator-hasElectrolyteA-schema:productID</t>
-        </is>
-      </c>
+      <c r="B150" s="3" t="n"/>
+      <c r="C150" s="3" t="n"/>
+      <c r="D150" s="3" t="n"/>
+      <c r="E150" s="3" t="n"/>
+      <c r="F150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>Membrane B manufacturer</t>
+          <t>Membrane A manufacturer</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Chemours</t>
+          <t>Fuel Cell Store</t>
         </is>
       </c>
       <c r="C151" s="4" t="n"/>
@@ -3983,20 +3989,18 @@
       <c r="E151" s="4" t="n"/>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasElectrolyteB-schema:manufacturer</t>
+          <t>hasSeparator-hasElectrolyteA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Membrane B manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B152" s="5" t="inlineStr">
-        <is>
-          <t>N117</t>
-        </is>
+          <t>Membrane A manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="n">
+        <v>72010015</v>
       </c>
       <c r="C152" s="5" t="n"/>
       <c r="D152" s="5" t="inlineStr">
@@ -4007,131 +4011,133 @@
       <c r="E152" s="5" t="n"/>
       <c r="F152" s="5" t="inlineStr">
         <is>
+          <t>hasSeparator-hasElectrolyteA-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>Membrane B manufacturer</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>Chemours</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="n"/>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="n"/>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>hasSeparator-hasElectrolyteB-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>Membrane B manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>N117</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="n"/>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="n"/>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
           <t>hasSeparator-hasElectrolyteB-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Cell assembly</t>
         </is>
       </c>
-      <c r="B153" s="3" t="n"/>
-      <c r="C153" s="3" t="n"/>
-      <c r="D153" s="3" t="n"/>
-      <c r="E153" s="3" t="n"/>
-      <c r="F153" s="3" t="n"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t>Cell case type (FlowCell or leave blank)</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>FlowCell</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="n"/>
-      <c r="D154" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E154" s="4" t="n"/>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>hasCase</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>Negative electrode gas compartment (FlowField or leave blank)</t>
-        </is>
-      </c>
-      <c r="B155" s="5" t="inlineStr">
-        <is>
-          <t>FlowField</t>
-        </is>
-      </c>
-      <c r="C155" s="5" t="n"/>
-      <c r="D155" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E155" s="5" t="n"/>
-      <c r="F155" s="5" t="inlineStr">
-        <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasComponent</t>
-        </is>
-      </c>
+      <c r="B155" s="3" t="n"/>
+      <c r="C155" s="3" t="n"/>
+      <c r="D155" s="3" t="n"/>
+      <c r="E155" s="3" t="n"/>
+      <c r="F155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>Negative electrode gas compartment width</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
+          <t>Cell case type</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>FlowCell</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="n"/>
       <c r="D156" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E156" s="4" t="n"/>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>FlowCell or leave blank</t>
+        </is>
+      </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasMeasuredProperty-Width</t>
+          <t>hasCase</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Negative electrode projected area</t>
-        </is>
-      </c>
-      <c r="B157" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C157" s="5" t="inlineStr">
-        <is>
-          <t>cm2</t>
-        </is>
-      </c>
+          <t>Negative electrode gas compartment</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>FlowField</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="n"/>
       <c r="D157" s="5" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E157" s="5" t="n"/>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>FlowField or leave blank</t>
+        </is>
+      </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode-hasMeasuredProperty-Area</t>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasComponent</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>Negative electrode to membrane gap/catholyte compartment width</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>Negative electrode gas compartment width</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="n"/>
       <c r="C158" s="4" t="inlineStr">
         <is>
           <t>mm</t>
@@ -4139,25 +4145,27 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E158" s="4" t="n"/>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>Leave blank if FlowField</t>
+        </is>
+      </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>hasComponentB-type|CatholyteCompartment-hasMeasuredProperty-Width</t>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasMeasuredProperty-Width</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Catholyte compartment volume</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="n">
-        <v>0.065</v>
-      </c>
+          <t>Negative electrode gas compartment volume</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="n"/>
       <c r="C159" s="5" t="inlineStr">
         <is>
           <t>mL</t>
@@ -4165,49 +4173,53 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E159" s="5" t="n"/>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>Leave blank if FlowField</t>
+        </is>
+      </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>hasComponentB-type|CatholyteCompartment-hasMeasuredProperty-Volume</t>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>Reference electrode in catholyte compartment</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>SilverChlorideElectrode</t>
-        </is>
-      </c>
-      <c r="C160" s="4" t="n"/>
+          <t>Negative electrode geometric surface area</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E160" s="4" t="n"/>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>hasComponentB-type|CatholyteCompartment-hasReferenceElectrode</t>
+          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrodeGeometricSurfaceArea</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Membrane projected area</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>Negative electrode real surface area</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="n"/>
       <c r="C161" s="5" t="inlineStr">
         <is>
           <t>cm2</t>
@@ -4221,40 +4233,38 @@
       <c r="E161" s="5" t="n"/>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>hasSeparator-hasMeasuredProperty-Area</t>
+          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrodeRealSurfaceArea</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>Anolyte compartment volume</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="n">
-        <v>0.065</v>
-      </c>
+          <t>Negative electrode electrochemically active surface area</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="n"/>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>cm2</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E162" s="4" t="n"/>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Volume</t>
+          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrochemicallyActiveSurfaceArea</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Positive electrode to membrane gap/anolyte compartment width</t>
+          <t>Negative electrode to separator gap width</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
@@ -4273,46 +4283,48 @@
       <c r="E163" s="5" t="n"/>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Width</t>
+          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrodeToSeparatorGapWidth</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>Reference electrode in anolyte compartment</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>SilverChlorideElectrode</t>
-        </is>
-      </c>
-      <c r="C164" s="4" t="n"/>
+          <t>Catholyte compartment width</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E164" s="4" t="n"/>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>hasComponentC-type|AnolyteCompartment-hasReferenceElectrode</t>
+          <t>hasComponentB-type|CatholyteCompartment-hasMeasuredProperty-Width</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>Positive electrode projected area</t>
+          <t>Catholyte compartment volume</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
-        <v>1</v>
+        <v>0.065</v>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>cm2</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
@@ -4323,72 +4335,72 @@
       <c r="E165" s="5" t="n"/>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasMeasuredProperty-Area</t>
+          <t>hasComponentB-type|CatholyteCompartment-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode gas compartment width</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
+          <t>Reference electrode in catholyte compartment</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>SilverChlorideElectrode</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="n"/>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E166" s="4" t="n"/>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasMeasuredProperty-Width</t>
+          <t>hasComponentB-type|CatholyteCompartment-hasReferenceElectrode</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>Positive electrode gas compartment (FlowField or leave blank)</t>
-        </is>
-      </c>
-      <c r="B167" s="5" t="inlineStr">
-        <is>
-          <t>FlowField</t>
-        </is>
-      </c>
-      <c r="C167" s="5" t="n"/>
+          <t>Membrane projected area</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E167" s="5" t="n"/>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasComponent</t>
+          <t>hasSeparator-hasMeasuredProperty-Area</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>Catholyte tank volume</t>
+          <t>Anolyte compartment width</t>
         </is>
       </c>
       <c r="B168" s="4" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -4399,18 +4411,18 @@
       <c r="E168" s="4" t="n"/>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>hasComponentE-type|CatholyteTank-hasMeasuredProperty-Volume</t>
+          <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Width</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>Anolyte tank volume</t>
+          <t>Anolyte compartment volume</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
-        <v>120</v>
+        <v>0.065</v>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
@@ -4425,65 +4437,325 @@
       <c r="E169" s="5" t="n"/>
       <c r="F169" s="5" t="inlineStr">
         <is>
+          <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>Reference electrode in anolyte compartment</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>SilverChlorideElectrode</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="n"/>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="n"/>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentC-type|AnolyteCompartment-hasReferenceElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>Positive electrode geometric surface area</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="n"/>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrodeGeometricSurfaceArea</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode real surface area</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="n"/>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="n"/>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrodeRealSurfaceArea</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>Positive electrode electrochemically active surface area</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="n"/>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="n"/>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrochemicallyActiveSurfaceArea</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode to separator gap width</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="n"/>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrodeToSeparatorGapWidth</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>Positive electrode gas compartment</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>FlowField</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="n"/>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>FlowField or leave blank</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasComponent</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode gas compartment width</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="n"/>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>Leave blank if FlowField</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasMeasuredProperty-Width</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>Positive electrode gas compartment volume</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="n"/>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>Leave blank if FlowField</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasMeasuredProperty-Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>Catholyte tank volume</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="n"/>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentE-type|CatholyteTank-hasMeasuredProperty-Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>Anolyte tank volume</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="n"/>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
           <t>hasComponentF-type|AnolyteTank-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="18" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="18" t="inlineStr">
         <is>
           <t>Cell optional component supplier information</t>
         </is>
       </c>
-      <c r="B170" s="3" t="n"/>
-      <c r="C170" s="3" t="n"/>
-      <c r="D170" s="3" t="n"/>
-      <c r="E170" s="3" t="n"/>
-      <c r="F170" s="3" t="n"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="4" t="inlineStr">
+      <c r="B180" s="3" t="n"/>
+      <c r="C180" s="3" t="n"/>
+      <c r="D180" s="3" t="n"/>
+      <c r="E180" s="3" t="n"/>
+      <c r="F180" s="3" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
         <is>
           <t>Cell case manufacturer</t>
         </is>
       </c>
-      <c r="B171" s="4" t="inlineStr">
+      <c r="B181" s="4" t="inlineStr">
         <is>
           <t>Fuel Cell Store</t>
         </is>
       </c>
-      <c r="C171" s="4" t="n"/>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="n"/>
-      <c r="F171" s="4" t="inlineStr">
+      <c r="C181" s="4" t="n"/>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="n"/>
+      <c r="F181" s="4" t="inlineStr">
         <is>
           <t>hasCase-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="5" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
         <is>
           <t>Cell case manufacturer product ID</t>
         </is>
       </c>
-      <c r="B172" s="5" t="inlineStr">
+      <c r="B182" s="5" t="inlineStr">
         <is>
           <t>Micro Flow Cell</t>
         </is>
       </c>
-      <c r="C172" s="5" t="n"/>
-      <c r="D172" s="5" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E172" s="5" t="n"/>
-      <c r="F172" s="5" t="inlineStr">
+      <c r="C182" s="5" t="n"/>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="n"/>
+      <c r="F182" s="5" t="inlineStr">
         <is>
           <t>hasCase-schema:productID</t>
         </is>
@@ -6383,7 +6655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7091,6 +7363,30 @@
       <c r="D36" t="inlineStr">
         <is>
           <t>Versogen Inc.; manufacturer of PiperION AEM series based on poly(aryl piperidinium) backbone for CO2 electrolysis and fuel cells. https://www.versogen.com. to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Baoji Qixin Titanium</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Redox.me</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
         </is>
       </c>
     </row>

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -1182,7 +1182,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Negative electrode optional microstructral/physical parameters</t>
+          <t>Negative electrode optional microstructural/physical parameters</t>
         </is>
       </c>
       <c r="B27" s="7" t="n"/>
@@ -1756,7 +1756,7 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Positive electrode coating  thickness</t>
+          <t>Positive electrode coating thickness</t>
         </is>
       </c>
       <c r="B52" s="12" t="n">
@@ -2099,7 +2099,7 @@
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-Gas</t>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-type|Gas</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       <c r="E69" s="4" t="n"/>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-Gas</t>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-type|Gas</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       <c r="E93" s="4" t="n"/>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolventA-schema:manufacturer</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       <c r="E94" s="16" t="n"/>
       <c r="F94" s="16" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolventA-schema:productID</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       <c r="E95" s="4" t="n"/>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolventB-schema:manufacturer</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       <c r="E96" s="16" t="n"/>
       <c r="F96" s="16" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolventB-schema:productID</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-schema:productID</t>
         </is>
       </c>
     </row>
@@ -2785,14 +2785,14 @@
       <c r="E97" s="4" t="n"/>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSoluteA-schema:manufacturer</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="16" t="inlineStr">
         <is>
-          <t>Catholyte solute A manufacturer productD</t>
+          <t>Catholyte solute A manufacturer product ID</t>
         </is>
       </c>
       <c r="B98" s="16" t="n">
@@ -2807,7 +2807,7 @@
       <c r="E98" s="16" t="n"/>
       <c r="F98" s="16" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSoluteA-schema:productID</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       <c r="E99" s="4" t="n"/>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSoluteB-schema:manufacturer</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       <c r="E100" s="16" t="n"/>
       <c r="F100" s="16" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSoluteB-schema:productID</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-schema:productID</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
       <c r="E102" s="4" t="n"/>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-Gas</t>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-type|Gas</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       <c r="E104" s="4" t="n"/>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-Gas</t>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-type|Gas</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       <c r="E128" s="4" t="n"/>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-schema:manufacturer</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       <c r="E129" s="16" t="n"/>
       <c r="F129" s="16" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-schema:productID</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
       <c r="E130" s="4" t="n"/>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-schema:manufacturer</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       <c r="E131" s="16" t="n"/>
       <c r="F131" s="16" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-schema:productID</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-schema:productID</t>
         </is>
       </c>
     </row>
@@ -3563,14 +3563,14 @@
       <c r="E132" s="4" t="n"/>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-schema:manufacturer</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="16" t="inlineStr">
         <is>
-          <t>Anolyte solute A manufacturer productD</t>
+          <t>Anolyte solute A manufacturer product ID</t>
         </is>
       </c>
       <c r="B133" s="16" t="n">
@@ -3585,7 +3585,7 @@
       <c r="E133" s="16" t="n"/>
       <c r="F133" s="16" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-schema:productID</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       <c r="E134" s="4" t="n"/>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-schema:manufacturer</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       <c r="E135" s="16" t="n"/>
       <c r="F135" s="16" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-schema:productID</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-schema:productID</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Membrane type</t>
+          <t>Membrane type (BilayerMembrane or leave blank)</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -3682,11 +3682,7 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>BilayerMembrane or leave blank</t>
-        </is>
-      </c>
+      <c r="E138" s="5" t="n"/>
       <c r="F138" s="5" t="inlineStr">
         <is>
           <t>hasSeparator</t>
@@ -3908,7 +3904,7 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>Membrane A area specific conductivity</t>
+          <t>Membrane A conductivity</t>
         </is>
       </c>
       <c r="B148" s="4" t="n">
@@ -3934,7 +3930,7 @@
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Membrane B area specific conductivity</t>
+          <t>Membrane B conductivity</t>
         </is>
       </c>
       <c r="B149" s="5" t="n">

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:F186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="74" customWidth="1" min="1" max="1"/>
@@ -609,7 +609,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>empa__ecid_000001</t>
+          <t>empa__ecid000251</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>240616_bco_Cu-IrO2_01</t>
+          <t>20251118_S200-KHCO3-cont-puls-01</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="C6" s="5" t="n"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Corsin Battaglia</t>
+          <t>Claudia Bissattini Alessi</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -749,7 +749,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ETHB PREMISE/NCCR Catalysis</t>
+          <t>SFOE SWEET Refuel.ch/ETHB ORD PREMISE</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>manually</t>
+          <t>Manually</t>
         </is>
       </c>
       <c r="C10" s="5" t="n"/>
@@ -889,7 +889,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>CarbonPaper</t>
+          <t>ElectrospunMesh</t>
         </is>
       </c>
       <c r="C15" s="8" t="n"/>
@@ -913,7 +913,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Carbon</t>
+          <t>PolyvinylideneFluoride</t>
         </is>
       </c>
       <c r="C16" s="4" t="n"/>
@@ -935,11 +935,7 @@
           <t>Negative electrode substrate coating material</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Polytetrafluoroethylene</t>
-        </is>
-      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
       <c r="D17" s="8" t="inlineStr">
         <is>
@@ -960,7 +956,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>315</v>
+        <v>110</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
@@ -1011,7 +1007,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
@@ -1034,7 +1030,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
@@ -1060,7 +1056,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
@@ -1085,15 +1081,11 @@
           <t>Negative electrode coating binder type</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>IonomerCompound</t>
-        </is>
-      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E23" s="8" t="n"/>
@@ -1109,15 +1101,11 @@
           <t>Negative electrode coating binder material</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>PerfluorosulfonicAcid</t>
-        </is>
-      </c>
+      <c r="B24" s="4" t="n"/>
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E24" s="4" t="n"/>
@@ -1133,9 +1121,7 @@
           <t>Negative electrode coating binder mass fraction</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="inlineStr">
         <is>
           <t>%</t>
@@ -1197,9 +1183,7 @@
           <t>Negative electrode substrate porosity</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n">
-        <v>85</v>
-      </c>
+      <c r="B28" s="4" t="n"/>
       <c r="C28" s="4" t="inlineStr">
         <is>
           <t>%</t>
@@ -1223,7 +1207,9 @@
           <t>Negative electrode substrate mean pore size</t>
         </is>
       </c>
-      <c r="B29" s="8" t="n"/>
+      <c r="B29" s="8" t="n">
+        <v>0.2</v>
+      </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
           <t>um</t>
@@ -1244,12 +1230,10 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Negative electrode coating active material particle size (leave blank for films)</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>0.02</v>
-      </c>
+          <t>Negative electrode coating active material median particle size (leave blank for films)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
       <c r="C30" s="4" t="inlineStr">
         <is>
           <t>um</t>
@@ -1309,11 +1293,7 @@
           <t>Negative electrode manufacturer product ID</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>15p_Cu</t>
-        </is>
-      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
@@ -1333,11 +1313,7 @@
           <t>Negative electrode substrate manufacturer</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>SGLCarbon</t>
-        </is>
-      </c>
+      <c r="B34" s="4" t="n"/>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="inlineStr">
         <is>
@@ -1354,14 +1330,10 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Negative electrode substrate product ID</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>39BB</t>
-        </is>
-      </c>
+          <t>Negative electrode substrate manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
@@ -1383,7 +1355,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Millipore Sigma</t>
+          <t>Empa</t>
         </is>
       </c>
       <c r="C36" s="4" t="n"/>
@@ -1402,12 +1374,10 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Negative electrode coating active material product ID</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="n">
-        <v>774081</v>
-      </c>
+          <t>Negative electrode coating active material manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
@@ -1427,11 +1397,7 @@
           <t>Negative electrode coating binder manufacturer</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Chemours</t>
-        </is>
-      </c>
+      <c r="B38" s="4" t="n"/>
       <c r="C38" s="4" t="n"/>
       <c r="D38" s="4" t="inlineStr">
         <is>
@@ -1448,14 +1414,10 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Negative electrode coating binder product ID</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>D521CS</t>
-        </is>
-      </c>
+          <t>Negative electrode coating binder manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
@@ -1560,7 +1522,7 @@
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
@@ -1606,12 +1568,12 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material</t>
+          <t>Positive electrode coating active material A</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>IridiumIIIOxide</t>
+          <t>IridiumOxideCompound</t>
         </is>
       </c>
       <c r="C46" s="12" t="n"/>
@@ -1623,118 +1585,120 @@
       <c r="E46" s="12" t="n"/>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasConstituentA</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material mass loading</t>
+          <t>Positive electrode coating active material A mass fraction</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>mg/cm2</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassLoading</t>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasConstituentA-hasMeasuredProperty-MassFraction</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material mass fraction</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>Positive electrode coating active material B</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>TantalumOxideCompound</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n"/>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E48" s="12" t="n"/>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassFraction</t>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode coating binder type</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>IonomerCompound</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="n"/>
+          <t>Positive electrode coating active material B mass fraction</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-hasBinder</t>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasConstituentB-hasMeasuredProperty-MassFraction</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>Positive electrode coating binder material</t>
-        </is>
-      </c>
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t>PerfluorosulfonicAcid</t>
-        </is>
-      </c>
-      <c r="C50" s="12" t="n"/>
+          <t>Positive electrode coating active material mass loading</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>mg/cm2</t>
+        </is>
+      </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E50" s="12" t="n"/>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-hasBinder</t>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassLoading</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode coating binder mass fraction</t>
+          <t>Positive electrode coating active material mass fraction</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
@@ -1749,24 +1713,18 @@
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-hasBinder-hasMeasuredProperty-MassFraction</t>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassFraction</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Positive electrode coating thickness</t>
-        </is>
-      </c>
-      <c r="B52" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C52" s="12" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
+          <t>Positive electrode coating binder type</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="n"/>
+      <c r="C52" s="12" t="n"/>
       <c r="D52" s="12" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -1775,486 +1733,468 @@
       <c r="E52" s="12" t="n"/>
       <c r="F52" s="12" t="inlineStr">
         <is>
+          <t>hasPositiveElectrode-hasCoating-hasBinder</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode coating binder material</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-hasBinder</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Positive electrode coating binder mass fraction</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="n"/>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="n"/>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-hasBinder-hasMeasuredProperty-MassFraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode coating thickness</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
           <t>hasPositiveElectrode-hasCoating-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="13" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
         <is>
           <t>Positive electrode optional microstructural/physical parameters</t>
         </is>
       </c>
-      <c r="B53" s="11" t="n"/>
-      <c r="C53" s="11" t="n"/>
-      <c r="D53" s="11" t="n"/>
-      <c r="E53" s="11" t="n"/>
-      <c r="F53" s="11" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="B56" s="11" t="n"/>
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="11" t="n"/>
+      <c r="F56" s="11" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Positive electrode substrate porosity</t>
         </is>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B57" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Porosity</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="12" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>Positive electrode substrate mean pore size</t>
         </is>
       </c>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="B58" s="12" t="n"/>
+      <c r="C58" s="12" t="inlineStr">
         <is>
           <t>um</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E55" s="12" t="n"/>
-      <c r="F55" s="12" t="inlineStr">
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-MeanPoreSize</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>Positive electrode coating active material mean particle size (leave blank for films)</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode coating active material median particle size (leave blank for films)</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
         <v>0.007</v>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>um</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="n"/>
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-D50ParticleSize</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="13" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>Positive electrode optional component manufacturer information</t>
         </is>
       </c>
-      <c r="B57" s="11" t="n"/>
-      <c r="C57" s="11" t="n"/>
-      <c r="D57" s="11" t="n"/>
-      <c r="E57" s="11" t="n"/>
-      <c r="F57" s="11" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="B60" s="11" t="n"/>
+      <c r="C60" s="11" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="11" t="n"/>
+      <c r="F60" s="11" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Positive electrode manufacturer</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>Empa</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Baoji Qixin Titanium</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>Positive electrode manufacturer product ID</t>
         </is>
       </c>
-      <c r="B59" s="12" t="inlineStr">
-        <is>
-          <t>18x_Ti</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="12" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E59" s="12" t="n"/>
-      <c r="F59" s="12" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>Iridium Oxide Coated Titanium Anodes</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="n"/>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="n"/>
+      <c r="F62" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Positive electrode substrate manufacturer</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Fuel Cell Store</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="n"/>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>Positive electrode substrate manufacturer product ID</t>
         </is>
       </c>
-      <c r="B61" s="12" t="n">
-        <v>40050001</v>
-      </c>
-      <c r="C61" s="12" t="n"/>
-      <c r="D61" s="12" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E61" s="12" t="n"/>
-      <c r="F61" s="12" t="inlineStr">
+      <c r="B64" s="12" t="n"/>
+      <c r="C64" s="12" t="n"/>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="n"/>
+      <c r="F64" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Positive electrode coating active material manufacturer</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>Fuel Cell Store</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="n"/>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="B65" s="4" t="n"/>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>Positive electrode coating active material manufacturer product ID</t>
         </is>
       </c>
-      <c r="B63" s="12" t="n">
-        <v>57080249</v>
-      </c>
-      <c r="C63" s="12" t="n"/>
-      <c r="D63" s="12" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E63" s="12" t="n"/>
-      <c r="F63" s="12" t="inlineStr">
+      <c r="B66" s="12" t="n"/>
+      <c r="C66" s="12" t="n"/>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="n"/>
+      <c r="F66" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-schema:productID</t>
         </is>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>Positive electrode coating binder manufacturer</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>Chemours</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasCoating-hasBinder-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
-        <is>
-          <t>Positive electrode coating binder manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B65" s="12" t="inlineStr">
-        <is>
-          <t>D521CS</t>
-        </is>
-      </c>
-      <c r="C65" s="12" t="n"/>
-      <c r="D65" s="12" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E65" s="12" t="n"/>
-      <c r="F65" s="12" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasCoating-hasBinder-schema:productID</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>Negative electrode gas supply</t>
-        </is>
-      </c>
-      <c r="B66" s="15" t="n"/>
-      <c r="C66" s="15" t="n"/>
-      <c r="D66" s="15" t="n"/>
-      <c r="E66" s="15" t="n"/>
-      <c r="F66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Negative electrode gas A</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>CarbonDioxide</t>
-        </is>
-      </c>
+          <t>Positive electrode coating binder manufacturer</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n"/>
       <c r="C67" s="4" t="n"/>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="inlineStr">
         <is>
+          <t>hasPositiveElectrode-hasCoating-hasBinder-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>Positive electrode coating binder manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="n"/>
+      <c r="C68" s="12" t="n"/>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="n"/>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-hasBinder-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>Negative electrode gas supply</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="n"/>
+      <c r="C69" s="15" t="n"/>
+      <c r="D69" s="15" t="n"/>
+      <c r="E69" s="15" t="n"/>
+      <c r="F69" s="15" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode gas A</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>CarbonDioxide</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n"/>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="n"/>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-type|Gas</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="16" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
         <is>
           <t>Negative electrode gas A volume fraction</t>
         </is>
       </c>
-      <c r="B68" s="16" t="n">
+      <c r="B71" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="C68" s="16" t="inlineStr">
+      <c r="C71" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E68" s="16" t="n"/>
-      <c r="F68" s="16" t="inlineStr">
+      <c r="E71" s="16" t="n"/>
+      <c r="F71" s="16" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>Negative electrode gas B</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Argon</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="n"/>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="B72" s="4" t="n"/>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-type|Gas</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="16" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="16" t="inlineStr">
         <is>
           <t>Negative electrode gas B volume fraction</t>
         </is>
       </c>
-      <c r="B70" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" s="16" t="inlineStr">
+      <c r="B73" s="16" t="n"/>
+      <c r="C73" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D70" s="16" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E70" s="16" t="n"/>
-      <c r="F70" s="16" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E73" s="16" t="n"/>
+      <c r="F73" s="16" t="inlineStr">
         <is>
           <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>Negative electrode gas flow rate</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>mL/min</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="n"/>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="16" t="inlineStr">
-        <is>
-          <t>Negative electrode gas pressure</t>
-        </is>
-      </c>
-      <c r="B72" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="16" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="D72" s="16" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E72" s="16" t="n"/>
-      <c r="F72" s="16" t="inlineStr">
-        <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-Pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="14" t="inlineStr">
-        <is>
-          <t>Catholyte</t>
-        </is>
-      </c>
-      <c r="B73" s="15" t="n"/>
-      <c r="C73" s="15" t="n"/>
-      <c r="D73" s="15" t="n"/>
-      <c r="E73" s="15" t="n"/>
-      <c r="F73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Catholyte solvent A</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="n"/>
+          <t>Negative electrode gas flow rate</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -2263,22 +2203,22 @@
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA</t>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>Catholyte solvent A volume fraction</t>
+          <t>Negative electrode gas pressure</t>
         </is>
       </c>
       <c r="B75" s="16" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="C75" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
@@ -2289,366 +2229,364 @@
       <c r="E75" s="16" t="n"/>
       <c r="F75" s="16" t="inlineStr">
         <is>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-Pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>Catholyte</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="n"/>
+      <c r="C76" s="15" t="n"/>
+      <c r="D76" s="15" t="n"/>
+      <c r="E76" s="15" t="n"/>
+      <c r="F76" s="15" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Catholyte solvent A</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n"/>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>hasCatholyte-hasSolvent-hasConstituentA</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>Catholyte solvent A volume fraction</t>
+        </is>
+      </c>
+      <c r="B78" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C78" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E78" s="16" t="n"/>
+      <c r="F78" s="16" t="inlineStr">
+        <is>
           <t>hasCatholyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Catholyte solvent B</t>
         </is>
       </c>
-      <c r="B76" s="4" t="n"/>
-      <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="n"/>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="B79" s="4" t="n"/>
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="n"/>
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="16" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="16" t="inlineStr">
         <is>
           <t>Catholyte solvent B volume fraction</t>
         </is>
       </c>
-      <c r="B77" s="16" t="n"/>
-      <c r="C77" s="16" t="inlineStr">
+      <c r="B80" s="16" t="n"/>
+      <c r="C80" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D77" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E77" s="16" t="n"/>
-      <c r="F77" s="16" t="inlineStr">
+      <c r="D80" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="n"/>
+      <c r="F80" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>Catholyte solute A</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>PotassiumCarbonate</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="n"/>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>PotassiumBicarbonate</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E78" s="4" t="n"/>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentA</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="16" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="16" t="inlineStr">
         <is>
           <t>Catholyte solute A molarity</t>
         </is>
       </c>
-      <c r="B79" s="16" t="n">
+      <c r="B82" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C79" s="16" t="inlineStr">
+      <c r="C82" s="16" t="inlineStr">
         <is>
           <t>mol/L</t>
         </is>
       </c>
-      <c r="D79" s="16" t="inlineStr">
+      <c r="D82" s="16" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E79" s="16" t="n"/>
-      <c r="F79" s="16" t="inlineStr">
+      <c r="E82" s="16" t="n"/>
+      <c r="F82" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>Catholyte solute B</t>
         </is>
       </c>
-      <c r="B80" s="4" t="n"/>
-      <c r="C80" s="4" t="n"/>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="n"/>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="B83" s="4" t="n"/>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentB</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="16" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
         <is>
           <t>Catholyte solute B molarity</t>
         </is>
       </c>
-      <c r="B81" s="16" t="n"/>
-      <c r="C81" s="16" t="inlineStr">
+      <c r="B84" s="16" t="n"/>
+      <c r="C84" s="16" t="inlineStr">
         <is>
           <t>mol/L</t>
         </is>
       </c>
-      <c r="D81" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E81" s="16" t="n"/>
-      <c r="F81" s="16" t="inlineStr">
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E84" s="16" t="n"/>
+      <c r="F84" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>Catholyte volume</t>
         </is>
       </c>
-      <c r="B82" s="4" t="n">
+      <c r="B85" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="16" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="16" t="inlineStr">
         <is>
           <t>Catholyte volume flow rate</t>
         </is>
       </c>
-      <c r="B83" s="16" t="n">
+      <c r="B86" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C83" s="16" t="inlineStr">
+      <c r="C86" s="16" t="inlineStr">
         <is>
           <t>mL/min</t>
         </is>
       </c>
-      <c r="D83" s="16" t="inlineStr">
+      <c r="D86" s="16" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E83" s="16" t="n"/>
-      <c r="F83" s="16" t="inlineStr">
+      <c r="E86" s="16" t="n"/>
+      <c r="F86" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>Catholyte pressure</t>
         </is>
       </c>
-      <c r="B84" s="4" t="n">
+      <c r="B87" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>bar</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E84" s="4" t="n"/>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="E87" s="4" t="n"/>
+      <c r="F87" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="17" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="17" t="inlineStr">
         <is>
           <t>Catholyte optional physical parameters</t>
         </is>
       </c>
-      <c r="B85" s="15" t="n"/>
-      <c r="C85" s="15" t="n"/>
-      <c r="D85" s="15" t="n"/>
-      <c r="E85" s="15" t="n"/>
-      <c r="F85" s="15" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="B88" s="15" t="n"/>
+      <c r="C88" s="15" t="n"/>
+      <c r="D88" s="15" t="n"/>
+      <c r="E88" s="15" t="n"/>
+      <c r="F88" s="15" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>Catholyte conductivity</t>
         </is>
       </c>
-      <c r="B86" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="B89" s="4" t="n"/>
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>mS/cm</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="n"/>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="16" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
         <is>
           <t>Catholyte pH</t>
         </is>
       </c>
-      <c r="B87" s="16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C87" s="16" t="inlineStr">
+      <c r="B90" s="16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
         <is>
           <t>unitless</t>
         </is>
       </c>
-      <c r="D87" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E87" s="16" t="n"/>
-      <c r="F87" s="16" t="inlineStr">
+      <c r="D90" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E90" s="16" t="n"/>
+      <c r="F90" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-PH</t>
         </is>
       </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>Catholyte density</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>g/cm3</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="n"/>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasMeasuredProperty-Density</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="16" t="inlineStr">
-        <is>
-          <t>Catholyte temperature</t>
-        </is>
-      </c>
-      <c r="B89" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="C89" s="16" t="inlineStr">
-        <is>
-          <t>°C</t>
-        </is>
-      </c>
-      <c r="D89" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E89" s="16" t="n"/>
-      <c r="F89" s="16" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasMeasuredProperty-CelsiusTemperature</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="17" t="inlineStr">
-        <is>
-          <t>Catholyte optional component manufacturer information</t>
-        </is>
-      </c>
-      <c r="B90" s="15" t="n"/>
-      <c r="C90" s="15" t="n"/>
-      <c r="D90" s="15" t="n"/>
-      <c r="E90" s="15" t="n"/>
-      <c r="F90" s="15" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Catholyte manufacturer</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>Empa</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="n"/>
+          <t>Catholyte density</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>g/cm3</t>
+        </is>
+      </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2657,22 +2595,24 @@
       <c r="E91" s="4" t="n"/>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-schema:manufacturer</t>
+          <t>hasCatholyte-hasMeasuredProperty-Density</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="16" t="inlineStr">
         <is>
-          <t>Catholyte manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B92" s="16" t="inlineStr">
-        <is>
-          <t>KCl_1M_catholyte</t>
-        </is>
-      </c>
-      <c r="C92" s="16" t="n"/>
+          <t>Catholyte temperature</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2681,199 +2621,203 @@
       <c r="E92" s="16" t="n"/>
       <c r="F92" s="16" t="inlineStr">
         <is>
+          <t>hasCatholyte-hasMeasuredProperty-CelsiusTemperature</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="17" t="inlineStr">
+        <is>
+          <t>Catholyte optional component manufacturer information</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="n"/>
+      <c r="C93" s="15" t="n"/>
+      <c r="D93" s="15" t="n"/>
+      <c r="E93" s="15" t="n"/>
+      <c r="F93" s="15" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Catholyte manufacturer</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>hasCatholyte-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Catholyte manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B95" s="16" t="inlineStr">
+        <is>
+          <t>KHCO3_1M_catholyte</t>
+        </is>
+      </c>
+      <c r="C95" s="16" t="n"/>
+      <c r="D95" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E95" s="16" t="n"/>
+      <c r="F95" s="16" t="inlineStr">
+        <is>
           <t>hasCatholyte-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>Catholyte solvent A manufacturer</t>
         </is>
       </c>
-      <c r="B93" s="4" t="n"/>
-      <c r="C93" s="4" t="n"/>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="n"/>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="B96" s="4" t="n"/>
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="n"/>
+      <c r="F96" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolvent-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="16" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
         <is>
           <t>Catholyte solvent A manufacturer product ID</t>
         </is>
       </c>
-      <c r="B94" s="16" t="n"/>
-      <c r="C94" s="16" t="n"/>
-      <c r="D94" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E94" s="16" t="n"/>
-      <c r="F94" s="16" t="inlineStr">
+      <c r="B97" s="16" t="n"/>
+      <c r="C97" s="16" t="n"/>
+      <c r="D97" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E97" s="16" t="n"/>
+      <c r="F97" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolvent-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>Catholyte solvent B manufacturer</t>
         </is>
       </c>
-      <c r="B95" s="4" t="n"/>
-      <c r="C95" s="4" t="n"/>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="n"/>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="B98" s="4" t="n"/>
+      <c r="C98" s="4" t="n"/>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="n"/>
+      <c r="F98" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolvent-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="16" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t>Catholyte solvent B manufacturer product ID</t>
         </is>
       </c>
-      <c r="B96" s="16" t="n"/>
-      <c r="C96" s="16" t="n"/>
-      <c r="D96" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E96" s="16" t="n"/>
-      <c r="F96" s="16" t="inlineStr">
+      <c r="B99" s="16" t="n"/>
+      <c r="C99" s="16" t="n"/>
+      <c r="D99" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E99" s="16" t="n"/>
+      <c r="F99" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolvent-hasConstituentB-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>Catholyte solute A manufacturer</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Thermo Fisher Scientific</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="n"/>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="n"/>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Millipore Sigma</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="16" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="16" t="inlineStr">
         <is>
           <t>Catholyte solute A manufacturer product ID</t>
         </is>
       </c>
-      <c r="B98" s="16" t="n">
-        <v>424090010</v>
-      </c>
-      <c r="C98" s="16" t="n"/>
-      <c r="D98" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E98" s="16" t="n"/>
-      <c r="F98" s="16" t="inlineStr">
+      <c r="B101" s="16" t="n">
+        <v>237205</v>
+      </c>
+      <c r="C101" s="16" t="n"/>
+      <c r="D101" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E101" s="16" t="n"/>
+      <c r="F101" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentA-schema:productID</t>
         </is>
       </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>Catholyte solute B manufacturer</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="n"/>
-      <c r="C99" s="4" t="n"/>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="n"/>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="16" t="inlineStr">
-        <is>
-          <t>Catholyte solute B manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B100" s="16" t="n"/>
-      <c r="C100" s="16" t="n"/>
-      <c r="D100" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E100" s="16" t="n"/>
-      <c r="F100" s="16" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-schema:productID</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="14" t="inlineStr">
-        <is>
-          <t>Positive electrode gas supply</t>
-        </is>
-      </c>
-      <c r="B101" s="15" t="n"/>
-      <c r="C101" s="15" t="n"/>
-      <c r="D101" s="15" t="n"/>
-      <c r="E101" s="15" t="n"/>
-      <c r="F101" s="15" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode gas A</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>Nitrogen</t>
-        </is>
-      </c>
+          <t>Catholyte solute B manufacturer</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="n"/>
       <c r="C102" s="4" t="n"/>
       <c r="D102" s="4" t="inlineStr">
         <is>
@@ -2883,24 +2827,18 @@
       <c r="E102" s="4" t="n"/>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-type|Gas</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="16" t="inlineStr">
         <is>
-          <t>Positive electrode gas A volume fraction</t>
-        </is>
-      </c>
-      <c r="B103" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="C103" s="16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>Catholyte solute B manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B103" s="16" t="n"/>
+      <c r="C103" s="16" t="n"/>
       <c r="D103" s="16" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2909,524 +2847,512 @@
       <c r="E103" s="16" t="n"/>
       <c r="F103" s="16" t="inlineStr">
         <is>
+          <t>hasCatholyte-hasSolute-hasConstituentB-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="14" t="inlineStr">
+        <is>
+          <t>Positive electrode gas supply</t>
+        </is>
+      </c>
+      <c r="B104" s="15" t="n"/>
+      <c r="C104" s="15" t="n"/>
+      <c r="D104" s="15" t="n"/>
+      <c r="E104" s="15" t="n"/>
+      <c r="F104" s="15" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode gas A</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="n"/>
+      <c r="C105" s="4" t="n"/>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="n"/>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-type|Gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="16" t="inlineStr">
+        <is>
+          <t>Positive electrode gas A volume fraction</t>
+        </is>
+      </c>
+      <c r="B106" s="16" t="n"/>
+      <c r="C106" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D106" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E106" s="16" t="n"/>
+      <c r="F106" s="16" t="inlineStr">
+        <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t>Positive electrode gas B</t>
         </is>
       </c>
-      <c r="B104" s="4" t="n"/>
-      <c r="C104" s="4" t="n"/>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="n"/>
-      <c r="F104" s="4" t="inlineStr">
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="4" t="n"/>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-type|Gas</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="16" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="16" t="inlineStr">
         <is>
           <t>Positive electrode gas B volume fraction</t>
         </is>
       </c>
-      <c r="B105" s="16" t="n"/>
-      <c r="C105" s="16" t="inlineStr">
+      <c r="B108" s="16" t="n"/>
+      <c r="C108" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D105" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E105" s="16" t="n"/>
-      <c r="F105" s="16" t="inlineStr">
+      <c r="D108" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E108" s="16" t="n"/>
+      <c r="F108" s="16" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>Positive electrode gas flow rate</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>mL/min</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="n"/>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="16" t="inlineStr">
-        <is>
-          <t>Positive electrode gas pressure</t>
-        </is>
-      </c>
-      <c r="B107" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C107" s="16" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="D107" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E107" s="16" t="n"/>
-      <c r="F107" s="16" t="inlineStr">
-        <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-Pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="14" t="inlineStr">
-        <is>
-          <t>Anolyte</t>
-        </is>
-      </c>
-      <c r="B108" s="15" t="n"/>
-      <c r="C108" s="15" t="n"/>
-      <c r="D108" s="15" t="n"/>
-      <c r="E108" s="15" t="n"/>
-      <c r="F108" s="15" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Anolyte solvent A</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="n"/>
+          <t>Positive electrode gas flow rate</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E109" s="4" t="n"/>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA</t>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="16" t="inlineStr">
         <is>
-          <t>Anolyte solvent A volume fraction</t>
-        </is>
-      </c>
-      <c r="B110" s="16" t="n">
-        <v>100</v>
-      </c>
+          <t>Positive electrode gas pressure</t>
+        </is>
+      </c>
+      <c r="B110" s="16" t="n"/>
       <c r="C110" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="D110" s="16" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E110" s="16" t="n"/>
       <c r="F110" s="16" t="inlineStr">
         <is>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-Pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="14" t="inlineStr">
+        <is>
+          <t>Anolyte</t>
+        </is>
+      </c>
+      <c r="B111" s="15" t="n"/>
+      <c r="C111" s="15" t="n"/>
+      <c r="D111" s="15" t="n"/>
+      <c r="E111" s="15" t="n"/>
+      <c r="F111" s="15" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>Anolyte solvent A</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="n"/>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasSolvent-hasConstituentA</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="16" t="inlineStr">
+        <is>
+          <t>Anolyte solvent A volume fraction</t>
+        </is>
+      </c>
+      <c r="B113" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C113" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D113" s="16" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E113" s="16" t="n"/>
+      <c r="F113" s="16" t="inlineStr">
+        <is>
           <t>hasAnolyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
         <is>
           <t>Anolyte solvent B</t>
         </is>
       </c>
-      <c r="B111" s="4" t="n"/>
-      <c r="C111" s="4" t="n"/>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="n"/>
-      <c r="F111" s="4" t="inlineStr">
+      <c r="B114" s="4" t="n"/>
+      <c r="C114" s="4" t="n"/>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="n"/>
+      <c r="F114" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="16" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="16" t="inlineStr">
         <is>
           <t>Anolyte solvent B volume fraction</t>
         </is>
       </c>
-      <c r="B112" s="16" t="n"/>
-      <c r="C112" s="16" t="inlineStr">
+      <c r="B115" s="16" t="n"/>
+      <c r="C115" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D112" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E112" s="16" t="n"/>
-      <c r="F112" s="16" t="inlineStr">
+      <c r="D115" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E115" s="16" t="n"/>
+      <c r="F115" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
         <is>
           <t>Anolyte solute A</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B116" s="4" t="inlineStr">
         <is>
           <t>SulfuricAcid</t>
         </is>
       </c>
-      <c r="C113" s="4" t="n"/>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="C116" s="4" t="n"/>
+      <c r="D116" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E113" s="4" t="n"/>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="E116" s="4" t="n"/>
+      <c r="F116" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentA</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="16" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="16" t="inlineStr">
         <is>
           <t>Anolyte solute A molarity</t>
         </is>
       </c>
-      <c r="B114" s="16" t="n">
+      <c r="B117" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C114" s="16" t="inlineStr">
+      <c r="C117" s="16" t="inlineStr">
         <is>
           <t>mol/L</t>
         </is>
       </c>
-      <c r="D114" s="16" t="inlineStr">
+      <c r="D117" s="16" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E114" s="16" t="n"/>
-      <c r="F114" s="16" t="inlineStr">
+      <c r="E117" s="16" t="n"/>
+      <c r="F117" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
         <is>
           <t>Anolyte solute B</t>
         </is>
       </c>
-      <c r="B115" s="4" t="n"/>
-      <c r="C115" s="4" t="n"/>
-      <c r="D115" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="n"/>
-      <c r="F115" s="4" t="inlineStr">
+      <c r="B118" s="4" t="n"/>
+      <c r="C118" s="4" t="n"/>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="n"/>
+      <c r="F118" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentB</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="16" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="16" t="inlineStr">
         <is>
           <t>Anolyte solute B molarity</t>
         </is>
       </c>
-      <c r="B116" s="16" t="n"/>
-      <c r="C116" s="16" t="inlineStr">
+      <c r="B119" s="16" t="n"/>
+      <c r="C119" s="16" t="inlineStr">
         <is>
           <t>mol/L</t>
         </is>
       </c>
-      <c r="D116" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E116" s="16" t="n"/>
-      <c r="F116" s="16" t="inlineStr">
+      <c r="D119" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E119" s="16" t="n"/>
+      <c r="F119" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>Anolyte volume</t>
         </is>
       </c>
-      <c r="B117" s="4" t="n">
+      <c r="B120" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D120" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E117" s="4" t="n"/>
-      <c r="F117" s="4" t="inlineStr">
+      <c r="E120" s="4" t="n"/>
+      <c r="F120" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="16" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="16" t="inlineStr">
         <is>
           <t>Anolyte volume flow rate</t>
         </is>
       </c>
-      <c r="B118" s="16" t="n">
+      <c r="B121" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C118" s="16" t="inlineStr">
+      <c r="C121" s="16" t="inlineStr">
         <is>
           <t>mL/min</t>
         </is>
       </c>
-      <c r="D118" s="16" t="inlineStr">
+      <c r="D121" s="16" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E118" s="16" t="n"/>
-      <c r="F118" s="16" t="inlineStr">
+      <c r="E121" s="16" t="n"/>
+      <c r="F121" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
         <is>
           <t>Anolyte pressure</t>
         </is>
       </c>
-      <c r="B119" s="4" t="n">
+      <c r="B122" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C122" s="4" t="inlineStr">
         <is>
           <t>bar</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="D122" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E119" s="4" t="n"/>
-      <c r="F119" s="4" t="inlineStr">
+      <c r="E122" s="4" t="n"/>
+      <c r="F122" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="17" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="17" t="inlineStr">
         <is>
           <t>Anolyte optional physical parameters</t>
         </is>
       </c>
-      <c r="B120" s="15" t="n"/>
-      <c r="C120" s="15" t="n"/>
-      <c r="D120" s="15" t="n"/>
-      <c r="E120" s="15" t="n"/>
-      <c r="F120" s="15" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="4" t="inlineStr">
+      <c r="B123" s="15" t="n"/>
+      <c r="C123" s="15" t="n"/>
+      <c r="D123" s="15" t="n"/>
+      <c r="E123" s="15" t="n"/>
+      <c r="F123" s="15" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
         <is>
           <t>Anolyte conductivity</t>
         </is>
       </c>
-      <c r="B121" s="4" t="n">
-        <v>800</v>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="B124" s="4" t="n"/>
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>mS/cm</t>
         </is>
       </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="n"/>
-      <c r="F121" s="4" t="inlineStr">
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="n"/>
+      <c r="F124" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="16" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="16" t="inlineStr">
         <is>
           <t>Anolyte pH</t>
         </is>
       </c>
-      <c r="B122" s="16" t="n">
+      <c r="B125" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C122" s="16" t="inlineStr">
+      <c r="C125" s="16" t="inlineStr">
         <is>
           <t>unitless</t>
         </is>
       </c>
-      <c r="D122" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E122" s="16" t="n"/>
-      <c r="F122" s="16" t="inlineStr">
+      <c r="D125" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E125" s="16" t="n"/>
+      <c r="F125" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-PH</t>
         </is>
       </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>Anolyte density</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>g/cm3</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="n"/>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasMeasuredProperty-Density</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="16" t="inlineStr">
-        <is>
-          <t>Anolyte temperature</t>
-        </is>
-      </c>
-      <c r="B124" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="C124" s="16" t="inlineStr">
-        <is>
-          <t>°C</t>
-        </is>
-      </c>
-      <c r="D124" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E124" s="16" t="n"/>
-      <c r="F124" s="16" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasMeasuredProperty-CelsiusTemperature</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="17" t="inlineStr">
-        <is>
-          <t>Anolyte optional component manufacturer information</t>
-        </is>
-      </c>
-      <c r="B125" s="15" t="n"/>
-      <c r="C125" s="15" t="n"/>
-      <c r="D125" s="15" t="n"/>
-      <c r="E125" s="15" t="n"/>
-      <c r="F125" s="15" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>Anolyte manufacturer</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>Empa</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="n"/>
+          <t>Anolyte density</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>g/cm3</t>
+        </is>
+      </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3435,22 +3361,24 @@
       <c r="E126" s="4" t="n"/>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-schema:manufacturer</t>
+          <t>hasAnolyte-hasMeasuredProperty-Density</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="16" t="inlineStr">
         <is>
-          <t>Anolyte manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B127" s="16" t="inlineStr">
-        <is>
-          <t>H2SO4_1M_anolyte</t>
-        </is>
-      </c>
-      <c r="C127" s="16" t="n"/>
+          <t>Anolyte temperature</t>
+        </is>
+      </c>
+      <c r="B127" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="C127" s="16" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
       <c r="D127" s="16" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3459,460 +3387,442 @@
       <c r="E127" s="16" t="n"/>
       <c r="F127" s="16" t="inlineStr">
         <is>
+          <t>hasAnolyte-hasMeasuredProperty-CelsiusTemperature</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="17" t="inlineStr">
+        <is>
+          <t>Anolyte optional component manufacturer information</t>
+        </is>
+      </c>
+      <c r="B128" s="15" t="n"/>
+      <c r="C128" s="15" t="n"/>
+      <c r="D128" s="15" t="n"/>
+      <c r="E128" s="15" t="n"/>
+      <c r="F128" s="15" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>Anolyte manufacturer</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="n"/>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="n"/>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>hasAnolyte-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="16" t="inlineStr">
+        <is>
+          <t>Anolyte manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B130" s="16" t="inlineStr">
+        <is>
+          <t>H2SO4_1M_anolyte</t>
+        </is>
+      </c>
+      <c r="C130" s="16" t="n"/>
+      <c r="D130" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E130" s="16" t="n"/>
+      <c r="F130" s="16" t="inlineStr">
+        <is>
           <t>hasAnolyte-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="4" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
         <is>
           <t>Anolyte solvent A manufacturer</t>
         </is>
       </c>
-      <c r="B128" s="4" t="n"/>
-      <c r="C128" s="4" t="n"/>
-      <c r="D128" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="n"/>
-      <c r="F128" s="4" t="inlineStr">
+      <c r="B131" s="4" t="n"/>
+      <c r="C131" s="4" t="n"/>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="n"/>
+      <c r="F131" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="16" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="16" t="inlineStr">
         <is>
           <t>Anolyte solvent A manufacturer product ID</t>
         </is>
       </c>
-      <c r="B129" s="16" t="n"/>
-      <c r="C129" s="16" t="n"/>
-      <c r="D129" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E129" s="16" t="n"/>
-      <c r="F129" s="16" t="inlineStr">
+      <c r="B132" s="16" t="n"/>
+      <c r="C132" s="16" t="n"/>
+      <c r="D132" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E132" s="16" t="n"/>
+      <c r="F132" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="4" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
         <is>
           <t>Anolyte solvent B manufacturer</t>
         </is>
       </c>
-      <c r="B130" s="4" t="n"/>
-      <c r="C130" s="4" t="n"/>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="n"/>
-      <c r="F130" s="4" t="inlineStr">
+      <c r="B133" s="4" t="n"/>
+      <c r="C133" s="4" t="n"/>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="n"/>
+      <c r="F133" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="16" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="16" t="inlineStr">
         <is>
           <t>Anolyte solvent B manufacturer product ID</t>
         </is>
       </c>
-      <c r="B131" s="16" t="n"/>
-      <c r="C131" s="16" t="n"/>
-      <c r="D131" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E131" s="16" t="n"/>
-      <c r="F131" s="16" t="inlineStr">
+      <c r="B134" s="16" t="n"/>
+      <c r="C134" s="16" t="n"/>
+      <c r="D134" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E134" s="16" t="n"/>
+      <c r="F134" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolvent-hasConstituentB-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="4" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
         <is>
           <t>Anolyte solute A manufacturer</t>
         </is>
       </c>
-      <c r="B132" s="4" t="inlineStr">
+      <c r="B135" s="4" t="inlineStr">
         <is>
           <t>Millipore Sigma</t>
         </is>
       </c>
-      <c r="C132" s="4" t="n"/>
-      <c r="D132" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="n"/>
-      <c r="F132" s="4" t="inlineStr">
+      <c r="C135" s="4" t="n"/>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="n"/>
+      <c r="F135" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="16" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="16" t="inlineStr">
         <is>
           <t>Anolyte solute A manufacturer product ID</t>
         </is>
       </c>
-      <c r="B133" s="16" t="n">
+      <c r="B136" s="16" t="n">
         <v>258105</v>
       </c>
-      <c r="C133" s="16" t="n"/>
-      <c r="D133" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E133" s="16" t="n"/>
-      <c r="F133" s="16" t="inlineStr">
+      <c r="C136" s="16" t="n"/>
+      <c r="D136" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E136" s="16" t="n"/>
+      <c r="F136" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentA-schema:productID</t>
         </is>
       </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>Anolyte solute B manufacturer</t>
-        </is>
-      </c>
-      <c r="B134" s="4" t="n"/>
-      <c r="C134" s="4" t="n"/>
-      <c r="D134" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="n"/>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="16" t="inlineStr">
-        <is>
-          <t>Anolyte solute B manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B135" s="16" t="n"/>
-      <c r="C135" s="16" t="n"/>
-      <c r="D135" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E135" s="16" t="n"/>
-      <c r="F135" s="16" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-schema:productID</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>Membrane</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="n"/>
-      <c r="C136" s="3" t="n"/>
-      <c r="D136" s="3" t="n"/>
-      <c r="E136" s="3" t="n"/>
-      <c r="F136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>Membrane type</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>IonExchangeMembrane</t>
-        </is>
-      </c>
+          <t>Anolyte solute B manufacturer</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="n"/>
       <c r="C137" s="4" t="n"/>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E137" s="4" t="n"/>
       <c r="F137" s="4" t="inlineStr">
         <is>
+          <t>hasAnolyte-hasSolute-hasConstituentB-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="16" t="inlineStr">
+        <is>
+          <t>Anolyte solute B manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B138" s="16" t="n"/>
+      <c r="C138" s="16" t="n"/>
+      <c r="D138" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E138" s="16" t="n"/>
+      <c r="F138" s="16" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasSolute-hasConstituentB-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Membrane</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="n"/>
+      <c r="C139" s="3" t="n"/>
+      <c r="D139" s="3" t="n"/>
+      <c r="E139" s="3" t="n"/>
+      <c r="F139" s="3" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>Membrane type</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>IonExchangeMembrane</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="n"/>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="n"/>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
           <t>hasSeparator</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="5" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
         <is>
           <t>Membrane type (BilayerMembrane or leave blank)</t>
         </is>
       </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>BilayerMembrane</t>
-        </is>
-      </c>
-      <c r="C138" s="5" t="n"/>
-      <c r="D138" s="5" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="n"/>
-      <c r="F138" s="5" t="inlineStr">
+      <c r="B141" s="5" t="n"/>
+      <c r="C141" s="5" t="n"/>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n"/>
+      <c r="F141" s="5" t="inlineStr">
         <is>
           <t>hasSeparator</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="4" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
         <is>
           <t>Membrane A type (facing catholyte)</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>AnionExchangeMembrane</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="n"/>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>CationExchangeMembrane</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="n"/>
+      <c r="D142" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E139" s="4" t="n"/>
-      <c r="F139" s="4" t="inlineStr">
+      <c r="E142" s="4" t="n"/>
+      <c r="F142" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>Membrane A material A (facing catholyte)</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>PolyArylPiperidinium</t>
-        </is>
-      </c>
-      <c r="C140" s="5" t="n"/>
-      <c r="D140" s="5" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>Membrane A material (facing catholyte)</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>PerfluorosulfonicAcid</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="n"/>
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E140" s="5" t="n"/>
-      <c r="F140" s="5" t="inlineStr">
+      <c r="E143" s="5" t="n"/>
+      <c r="F143" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="4" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
         <is>
           <t>Membrane A thickness (facing catholyte)</t>
         </is>
       </c>
-      <c r="B141" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="B144" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
         <is>
           <t>um</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr">
+      <c r="D144" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E141" s="4" t="n"/>
-      <c r="F141" s="4" t="inlineStr">
+      <c r="E144" s="4" t="n"/>
+      <c r="F144" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="5" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>Membrane A ion exchange capacity (facing catholyte)</t>
         </is>
       </c>
-      <c r="B142" s="5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C142" s="5" t="inlineStr">
+      <c r="B145" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
         <is>
           <t>mEq/100g</t>
         </is>
       </c>
-      <c r="D142" s="5" t="inlineStr">
+      <c r="D145" s="5" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E142" s="5" t="n"/>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-AmountConcentration</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="4" t="inlineStr">
+      <c r="E145" s="5" t="n"/>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-IonExchangeCapacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
         <is>
           <t>Membrane B type (facing anolyte)</t>
         </is>
       </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>CationExchangeMembrane</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="n"/>
-      <c r="D143" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E143" s="4" t="n"/>
-      <c r="F143" s="4" t="inlineStr">
+      <c r="B146" s="4" t="n"/>
+      <c r="C146" s="4" t="n"/>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="n"/>
+      <c r="F146" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>Membrane B material A (facing anolyte)</t>
-        </is>
-      </c>
-      <c r="B144" s="5" t="inlineStr">
-        <is>
-          <t>PerfluorosulfonicAcid</t>
-        </is>
-      </c>
-      <c r="C144" s="5" t="n"/>
-      <c r="D144" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E144" s="5" t="n"/>
-      <c r="F144" s="5" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>Membrane B material (facing anolyte)</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="n"/>
+      <c r="C147" s="5" t="n"/>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n"/>
+      <c r="F147" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteB</t>
         </is>
       </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>Membrane B thickness (facing anolyte)</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E145" s="4" t="n"/>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-Thickness</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>Membrane B ion exchange capacity (facing anolyte)</t>
-        </is>
-      </c>
-      <c r="B146" s="5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C146" s="5" t="inlineStr">
-        <is>
-          <t>mEq/100g</t>
-        </is>
-      </c>
-      <c r="D146" s="5" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E146" s="5" t="n"/>
-      <c r="F146" s="5" t="inlineStr">
-        <is>
-          <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-AmountConcentration</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="18" t="inlineStr">
-        <is>
-          <t>Membrane optional physical parameters</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="n"/>
-      <c r="C147" s="3" t="n"/>
-      <c r="D147" s="3" t="n"/>
-      <c r="E147" s="3" t="n"/>
-      <c r="F147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>Membrane A conductivity</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="n">
-        <v>8</v>
-      </c>
+          <t>Membrane B thickness (facing anolyte)</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="n"/>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>mS/cm</t>
+          <t>um</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -3923,22 +3833,20 @@
       <c r="E148" s="4" t="n"/>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-ElectrolyticConductivity</t>
+          <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Membrane B conductivity</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="n">
-        <v>8</v>
-      </c>
+          <t>Membrane B ion exchange capacity (facing anolyte)</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="n"/>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>mS/cm</t>
+          <t>mEq/100g</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
@@ -3949,14 +3857,14 @@
       <c r="E149" s="5" t="n"/>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-ElectrolyticConductivity</t>
+          <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-IonExchangeCapacity</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="18" t="inlineStr">
         <is>
-          <t>Membrane optional component manufacturer information</t>
+          <t>Membrane optional physical parameters</t>
         </is>
       </c>
       <c r="B150" s="3" t="n"/>
@@ -3968,15 +3876,15 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>Membrane A manufacturer</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>Fuel Cell Store</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="n"/>
+          <t>Membrane A conductivity</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="n"/>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>mS/cm</t>
+        </is>
+      </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3985,20 +3893,22 @@
       <c r="E151" s="4" t="n"/>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasElectrolyteA-schema:manufacturer</t>
+          <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Membrane A manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B152" s="5" t="n">
-        <v>72010015</v>
-      </c>
-      <c r="C152" s="5" t="n"/>
+          <t>Membrane B conductivity</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="n"/>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>mS/cm</t>
+        </is>
+      </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4007,751 +3917,813 @@
       <c r="E152" s="5" t="n"/>
       <c r="F152" s="5" t="inlineStr">
         <is>
+          <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-ElectrolyticConductivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="18" t="inlineStr">
+        <is>
+          <t>Membrane optional component manufacturer information</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="n"/>
+      <c r="C153" s="3" t="n"/>
+      <c r="D153" s="3" t="n"/>
+      <c r="E153" s="3" t="n"/>
+      <c r="F153" s="3" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>Membrane A manufacturer</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>Fuel Cell Store</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="n"/>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="n"/>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>hasSeparator-hasElectrolyteA-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>Membrane A manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="n">
+        <v>87010020</v>
+      </c>
+      <c r="C155" s="5" t="n"/>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="n"/>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
           <t>hasSeparator-hasElectrolyteA-schema:productID</t>
         </is>
       </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>Membrane B manufacturer</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>Chemours</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="n"/>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E153" s="4" t="n"/>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>hasSeparator-hasElectrolyteB-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>Membrane B manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B154" s="5" t="inlineStr">
-        <is>
-          <t>N117</t>
-        </is>
-      </c>
-      <c r="C154" s="5" t="n"/>
-      <c r="D154" s="5" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E154" s="5" t="n"/>
-      <c r="F154" s="5" t="inlineStr">
-        <is>
-          <t>hasSeparator-hasElectrolyteB-schema:productID</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>Cell assembly</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="n"/>
-      <c r="C155" s="3" t="n"/>
-      <c r="D155" s="3" t="n"/>
-      <c r="E155" s="3" t="n"/>
-      <c r="F155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>Cell case type</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>FlowCell</t>
-        </is>
-      </c>
+          <t>Membrane B manufacturer</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="n"/>
       <c r="C156" s="4" t="n"/>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>FlowCell or leave blank</t>
-        </is>
-      </c>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="n"/>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>hasCase</t>
+          <t>hasSeparator-hasElectrolyteB-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Negative electrode gas compartment</t>
-        </is>
-      </c>
-      <c r="B157" s="5" t="inlineStr">
-        <is>
-          <t>FlowField</t>
-        </is>
-      </c>
+          <t>Membrane B manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="n"/>
       <c r="C157" s="5" t="n"/>
       <c r="D157" s="5" t="inlineStr">
         <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="n"/>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>hasSeparator-hasElectrolyteB-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Cell assembly</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="n"/>
+      <c r="C158" s="3" t="n"/>
+      <c r="D158" s="3" t="n"/>
+      <c r="E158" s="3" t="n"/>
+      <c r="F158" s="3" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>Cell case type</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>FlowCell</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="n"/>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>FlowCell or leave blank</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>hasCase</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>Negative electrode gas compartment</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="n"/>
+      <c r="C160" s="5" t="n"/>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>FlowField or leave blank</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasComponent</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode gas compartment width</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="n"/>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>Leave blank if FlowField</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasMeasuredProperty-Width</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Negative electrode gas compartment volume</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="n"/>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>Leave blank if FlowField</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasMeasuredProperty-Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode geometric surface area</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E157" s="5" t="inlineStr">
+      <c r="E163" s="4" t="n"/>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrodeGeometricSurfaceArea</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>Negative electrode real surface area</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="n"/>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="n"/>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrodeRealSurfaceArea</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode electrochemically active surface area</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="n"/>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="n"/>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrochemicallyActiveSurfaceArea</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>Negative electrode to separator gap width</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="n"/>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrodeToSeparatorGapWidth</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>Catholyte compartment width</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="n"/>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentB-type|CatholyteCompartment-hasMeasuredProperty-Width</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>Catholyte compartment volume</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="n"/>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>hasComponentB-type|CatholyteCompartment-hasMeasuredProperty-Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>Reference electrode in catholyte compartment</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>SilverChlorideElectrode</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="n"/>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="n"/>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentB-type|CatholyteCompartment-hasReferenceElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>Membrane projected area</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="n"/>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>hasSeparator-hasMeasuredProperty-Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>Anolyte compartment width</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="n"/>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Width</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>Anolyte compartment volume</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="n"/>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>Reference electrode in anolyte compartment</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="n"/>
+      <c r="C173" s="4" t="n"/>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="n"/>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentC-type|AnolyteCompartment-hasReferenceElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>Positive electrode geometric surface area</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="n"/>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrodeGeometricSurfaceArea</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode real surface area</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="n"/>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="n"/>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrodeRealSurfaceArea</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>Positive electrode electrochemically active surface area</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="n"/>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="n"/>
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrochemicallyActiveSurfaceArea</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode to separator gap width</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="n"/>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrodeToSeparatorGapWidth</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>Positive electrode gas compartment</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="n"/>
+      <c r="C178" s="5" t="n"/>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="inlineStr">
         <is>
           <t>FlowField or leave blank</t>
         </is>
       </c>
-      <c r="F157" s="5" t="inlineStr">
-        <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasComponent</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>Negative electrode gas compartment width</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="n"/>
-      <c r="C158" s="4" t="inlineStr">
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasComponent</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode gas compartment width</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="n"/>
+      <c r="C179" s="4" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D158" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E158" s="4" t="inlineStr">
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
         <is>
           <t>Leave blank if FlowField</t>
         </is>
       </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasMeasuredProperty-Width</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>Negative electrode gas compartment volume</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="n"/>
-      <c r="C159" s="5" t="inlineStr">
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasMeasuredProperty-Width</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>Positive electrode gas compartment volume</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="n"/>
+      <c r="C180" s="5" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="D159" s="5" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E159" s="5" t="inlineStr">
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="inlineStr">
         <is>
           <t>Leave blank if FlowField</t>
         </is>
       </c>
-      <c r="F159" s="5" t="inlineStr">
-        <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasMeasuredProperty-Volume</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="4" t="inlineStr">
-        <is>
-          <t>Negative electrode geometric surface area</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C160" s="4" t="inlineStr">
-        <is>
-          <t>cm2</t>
-        </is>
-      </c>
-      <c r="D160" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="n"/>
-      <c r="F160" s="4" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrodeGeometricSurfaceArea</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>Negative electrode real surface area</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="n"/>
-      <c r="C161" s="5" t="inlineStr">
-        <is>
-          <t>cm2</t>
-        </is>
-      </c>
-      <c r="D161" s="5" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="n"/>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrodeRealSurfaceArea</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="4" t="inlineStr">
-        <is>
-          <t>Negative electrode electrochemically active surface area</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="n"/>
-      <c r="C162" s="4" t="inlineStr">
-        <is>
-          <t>cm2</t>
-        </is>
-      </c>
-      <c r="D162" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E162" s="4" t="n"/>
-      <c r="F162" s="4" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrochemicallyActiveSurfaceArea</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="5" t="inlineStr">
-        <is>
-          <t>Negative electrode to separator gap width</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C163" s="5" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D163" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="n"/>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrodeToSeparatorGapWidth</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="4" t="inlineStr">
-        <is>
-          <t>Catholyte compartment width</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D164" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="n"/>
-      <c r="F164" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentB-type|CatholyteCompartment-hasMeasuredProperty-Width</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="5" t="inlineStr">
-        <is>
-          <t>Catholyte compartment volume</t>
-        </is>
-      </c>
-      <c r="B165" s="5" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="C165" s="5" t="inlineStr">
-        <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="D165" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E165" s="5" t="n"/>
-      <c r="F165" s="5" t="inlineStr">
-        <is>
-          <t>hasComponentB-type|CatholyteCompartment-hasMeasuredProperty-Volume</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="4" t="inlineStr">
-        <is>
-          <t>Reference electrode in catholyte compartment</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="inlineStr">
-        <is>
-          <t>SilverChlorideElectrode</t>
-        </is>
-      </c>
-      <c r="C166" s="4" t="n"/>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="n"/>
-      <c r="F166" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentB-type|CatholyteCompartment-hasReferenceElectrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t>Membrane projected area</t>
-        </is>
-      </c>
-      <c r="B167" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C167" s="5" t="inlineStr">
-        <is>
-          <t>cm2</t>
-        </is>
-      </c>
-      <c r="D167" s="5" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E167" s="5" t="n"/>
-      <c r="F167" s="5" t="inlineStr">
-        <is>
-          <t>hasSeparator-hasMeasuredProperty-Area</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="4" t="inlineStr">
-        <is>
-          <t>Anolyte compartment width</t>
-        </is>
-      </c>
-      <c r="B168" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D168" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="n"/>
-      <c r="F168" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Width</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="5" t="inlineStr">
-        <is>
-          <t>Anolyte compartment volume</t>
-        </is>
-      </c>
-      <c r="B169" s="5" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="C169" s="5" t="inlineStr">
-        <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="D169" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E169" s="5" t="n"/>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Volume</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="4" t="inlineStr">
-        <is>
-          <t>Reference electrode in anolyte compartment</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>SilverChlorideElectrode</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="n"/>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="n"/>
-      <c r="F170" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentC-type|AnolyteCompartment-hasReferenceElectrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="5" t="inlineStr">
-        <is>
-          <t>Positive electrode geometric surface area</t>
-        </is>
-      </c>
-      <c r="B171" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C171" s="5" t="inlineStr">
-        <is>
-          <t>cm2</t>
-        </is>
-      </c>
-      <c r="D171" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E171" s="5" t="n"/>
-      <c r="F171" s="5" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrodeGeometricSurfaceArea</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="4" t="inlineStr">
-        <is>
-          <t>Positive electrode real surface area</t>
-        </is>
-      </c>
-      <c r="B172" s="4" t="n"/>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>cm2</t>
-        </is>
-      </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="n"/>
-      <c r="F172" s="4" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrodeRealSurfaceArea</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="5" t="inlineStr">
-        <is>
-          <t>Positive electrode electrochemically active surface area</t>
-        </is>
-      </c>
-      <c r="B173" s="5" t="n"/>
-      <c r="C173" s="5" t="inlineStr">
-        <is>
-          <t>cm2</t>
-        </is>
-      </c>
-      <c r="D173" s="5" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E173" s="5" t="n"/>
-      <c r="F173" s="5" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrochemicallyActiveSurfaceArea</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="4" t="inlineStr">
-        <is>
-          <t>Positive electrode to separator gap width</t>
-        </is>
-      </c>
-      <c r="B174" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C174" s="4" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D174" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E174" s="4" t="n"/>
-      <c r="F174" s="4" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrodeToSeparatorGapWidth</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="5" t="inlineStr">
-        <is>
-          <t>Positive electrode gas compartment</t>
-        </is>
-      </c>
-      <c r="B175" s="5" t="inlineStr">
-        <is>
-          <t>FlowField</t>
-        </is>
-      </c>
-      <c r="C175" s="5" t="n"/>
-      <c r="D175" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E175" s="5" t="inlineStr">
-        <is>
-          <t>FlowField or leave blank</t>
-        </is>
-      </c>
-      <c r="F175" s="5" t="inlineStr">
-        <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasComponent</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="4" t="inlineStr">
-        <is>
-          <t>Positive electrode gas compartment width</t>
-        </is>
-      </c>
-      <c r="B176" s="4" t="n"/>
-      <c r="C176" s="4" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D176" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E176" s="4" t="inlineStr">
-        <is>
-          <t>Leave blank if FlowField</t>
-        </is>
-      </c>
-      <c r="F176" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasMeasuredProperty-Width</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="5" t="inlineStr">
-        <is>
-          <t>Positive electrode gas compartment volume</t>
-        </is>
-      </c>
-      <c r="B177" s="5" t="n"/>
-      <c r="C177" s="5" t="inlineStr">
-        <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="D177" s="5" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E177" s="5" t="inlineStr">
-        <is>
-          <t>Leave blank if FlowField</t>
-        </is>
-      </c>
-      <c r="F177" s="5" t="inlineStr">
+      <c r="F180" s="5" t="inlineStr">
         <is>
           <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasMeasuredProperty-Volume</t>
         </is>
       </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="4" t="inlineStr">
-        <is>
-          <t>Catholyte tank volume</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E178" s="4" t="n"/>
-      <c r="F178" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentE-type|CatholyteTank-hasMeasuredProperty-Volume</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="5" t="inlineStr">
-        <is>
-          <t>Anolyte tank volume</t>
-        </is>
-      </c>
-      <c r="B179" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="C179" s="5" t="inlineStr">
-        <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="D179" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E179" s="5" t="n"/>
-      <c r="F179" s="5" t="inlineStr">
-        <is>
-          <t>hasComponentF-type|AnolyteTank-hasMeasuredProperty-Volume</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="18" t="inlineStr">
-        <is>
-          <t>Cell optional component supplier information</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="n"/>
-      <c r="C180" s="3" t="n"/>
-      <c r="D180" s="3" t="n"/>
-      <c r="E180" s="3" t="n"/>
-      <c r="F180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>Cell case manufacturer</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>Fuel Cell Store</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="n"/>
+          <t>Catholyte tank volume</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E181" s="4" t="n"/>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>hasCase-schema:manufacturer</t>
+          <t>hasComponentE-type|CatholyteTank-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>Cell case manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B182" s="5" t="inlineStr">
-        <is>
-          <t>Micro Flow Cell</t>
-        </is>
-      </c>
-      <c r="C182" s="5" t="n"/>
+          <t>Anolyte tank volume</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E182" s="5" t="n"/>
       <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>hasComponentF-type|AnolyteTank-hasMeasuredProperty-Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="18" t="inlineStr">
+        <is>
+          <t>Cell optional component manufacturer information</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="n"/>
+      <c r="C183" s="3" t="n"/>
+      <c r="D183" s="3" t="n"/>
+      <c r="E183" s="3" t="n"/>
+      <c r="F183" s="3" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>Cell case manufacturer</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>Redox.me</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="n"/>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="n"/>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>hasCase-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>Cell case manufacturer product ID A</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>C-A-MM_PEC_HC-2x15-1</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="n"/>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="n"/>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>hasCase-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>Cell case manufacturer product ID B</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>C-A-MM_FC_GDE_XRD_EC</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="n"/>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="n"/>
+      <c r="F186" s="4" t="inlineStr">
         <is>
           <t>hasCase-schema:productID</t>
         </is>
@@ -4898,7 +4870,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.22092428</t>
+          <t>https://doi.org/10.5281/zenodo.23761089</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4882,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>https://zenodo.org/api/records/22092428</t>
+          <t>https://zenodo.org/api/records/23761089</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4894,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Claudia Bissattini</t>
+          <t>Claudia Bissattini Alessi</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -5040,12 +5012,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Fig. 1a</t>
+          <t>Fig. 2a</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Fig. 2b</t>
+          <t>Fig. 3a</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5029,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Claudia Bissattini</t>
+          <t>Claudia Bissattini Alessi</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -5175,7 +5147,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>empa__ecid000001/empa__ecid000001.cdf.parquet</t>
+          <t>empa__ecid000251.cdf.parquet</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -5192,7 +5164,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>empa__ecid000001/empa__ecid000001.cdf.csv</t>
+          <t>empa__ecid000251.cdf.csv</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -5209,12 +5181,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>empa__ecid000001/empa__ecid000001_CA_C01.mpr</t>
+          <t>empa__ecid000251.raw.zip</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Raw electrochemical data, Biologic EC-Lab mpr binary format</t>
+          <t>Raw electrochemical data, GC data, and yadg settings.</t>
         </is>
       </c>
     </row>
@@ -5222,16 +5194,6 @@
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Input fileA</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>empa__ecid000001/empa__ecid000001.mps</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Measurement protocol, Biologic EC-Lab settings file</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Claudia Bissattini</t>
+          <t>Claudia Bissattini Alessi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6763,7 +6725,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://orcid.org/0000-0002-3971-0398</t>
+          <t>https://orcid.org/0009-0000-0662-4971</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6849,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q367032</t>
+          <t>http://www.wikidata.org/entity/Q720484</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6909,7 +6871,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q310172</t>
+          <t>http://www.wikidata.org/entity/Q309245</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6953,7 +6915,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q15829006</t>
+          <t>http://www.wikidata.org/entity/Q20630716</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6997,7 +6959,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q879878</t>
+          <t>http://www.wikidata.org/entity/Q15810492</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -7085,7 +7047,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q2361947</t>
+          <t>http://www.wikidata.org/entity/Q320207</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -7107,7 +7069,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q487209</t>
+          <t>http://www.wikidata.org/entity/Q706184</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -7151,7 +7113,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q306455</t>
+          <t>http://www.wikidata.org/entity/Q643674</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -7173,7 +7135,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q908461</t>
+          <t>http://www.wikidata.org/entity/Q168115</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">

--- a/test/data/electrolysis_excel_schema.xlsx
+++ b/test/data/electrolysis_excel_schema.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F172"/>
+  <dimension ref="A1:F186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="74" customWidth="1" min="1" max="1"/>
@@ -609,7 +609,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>empa__ecid_000001</t>
+          <t>empa__ecid000251</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>240616_bco_gr-NMC_01</t>
+          <t>20251118_S200-KHCO3-cont-puls-01</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="C6" s="5" t="n"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Corsin Battaglia</t>
+          <t>Claudia Bissattini Alessi</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -749,7 +749,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ETHB PREMISE/NCCR Catalysis</t>
+          <t>SFOE SWEET Refuel.ch/ETHB ORD PREMISE</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>manually</t>
+          <t>Manually</t>
         </is>
       </c>
       <c r="C10" s="5" t="n"/>
@@ -889,7 +889,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>CarbonPaper</t>
+          <t>ElectrospunMesh</t>
         </is>
       </c>
       <c r="C15" s="8" t="n"/>
@@ -913,7 +913,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Carbon</t>
+          <t>PolyvinylideneFluoride</t>
         </is>
       </c>
       <c r="C16" s="4" t="n"/>
@@ -935,11 +935,7 @@
           <t>Negative electrode substrate coating material</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Polytetrafluoroethylene</t>
-        </is>
-      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
       <c r="D17" s="8" t="inlineStr">
         <is>
@@ -960,7 +956,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>315</v>
+        <v>110</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
@@ -1011,7 +1007,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
@@ -1034,7 +1030,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
@@ -1060,7 +1056,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
@@ -1085,15 +1081,11 @@
           <t>Negative electrode coating binder type</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>IonomerCompound</t>
-        </is>
-      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E23" s="8" t="n"/>
@@ -1109,15 +1101,11 @@
           <t>Negative electrode coating binder material</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>PerfluorosulfonicAcid</t>
-        </is>
-      </c>
+      <c r="B24" s="4" t="n"/>
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E24" s="4" t="n"/>
@@ -1133,9 +1121,7 @@
           <t>Negative electrode coating binder mass fraction</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="inlineStr">
         <is>
           <t>%</t>
@@ -1182,7 +1168,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Negative electrode optional microstructral/physical parameters</t>
+          <t>Negative electrode optional microstructural/physical parameters</t>
         </is>
       </c>
       <c r="B27" s="7" t="n"/>
@@ -1197,9 +1183,7 @@
           <t>Negative electrode substrate porosity</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n">
-        <v>85</v>
-      </c>
+      <c r="B28" s="4" t="n"/>
       <c r="C28" s="4" t="inlineStr">
         <is>
           <t>%</t>
@@ -1220,11 +1204,11 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Negative electrode coating active material particle size (leave blank for films)</t>
+          <t>Negative electrode substrate mean pore size</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
@@ -1239,995 +1223,947 @@
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="inlineStr">
         <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-MeanPoreSize</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode coating active material median particle size (leave blank for films)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-D50ParticleSize</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Negative electrode optional component manufacturer information</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Negative electrode manufacturer</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Empa</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Negative electrode manufacturer product ID</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>15p_Cu</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Negative electrode substrate manufacturer</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>SGLCarbon</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Negative electrode substrate product ID</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>39BB</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Negative electrode substrate manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Negative electrode coating active material manufacturer</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Millipore Sigma</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Negative electrode coating active material product ID</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="n">
-        <v>774081</v>
-      </c>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Negative electrode coating active material manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Negative electrode coating binder manufacturer</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Chemours</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasBinder-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Negative electrode coating binder product ID</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>D521CS</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Negative electrode coating binder manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasBinder-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Positive electrode (counter electrode)</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Positive electrode type</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>ImmersionElectrode</t>
         </is>
       </c>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>Positive electrode substrate type</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>PerforatedFoil</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Positive electrode substrate material</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Titanium</t>
         </is>
       </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Positive electrode substrate thickness</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B44" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode coating active material type</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Electrocatalyst</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>Positive electrode coating active material A</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>IridiumOxideCompound</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="n"/>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasConstituentA</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode coating active material A mass fraction</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasConstituentA-hasMeasuredProperty-MassFraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Positive electrode coating active material B</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>TantalumOxideCompound</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n"/>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasConstituentB</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode coating active material B mass fraction</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasConstituentB-hasMeasuredProperty-MassFraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Positive electrode coating active material mass loading</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>mg/cm2</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Positive electrode coating active material type</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Electrocatalyst</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>Positive electrode coating active material</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>IridiumIIIOxide</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>Positive electrode coating active material mass loading</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>mg/cm2</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassLoading</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode coating active material mass fraction</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassLoading</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>Positive electrode coating active material mass fraction</t>
-        </is>
-      </c>
-      <c r="B47" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassFraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Positive electrode coating binder type</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="n"/>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n"/>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassFraction</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>Positive electrode coating binder type</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>IonomerCompound</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasBinder</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>Positive electrode coating binder material</t>
-        </is>
-      </c>
-      <c r="B49" s="12" t="inlineStr">
-        <is>
-          <t>PerfluorosulfonicAcid</t>
-        </is>
-      </c>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E49" s="12" t="n"/>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasCoating-hasBinder</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Positive electrode coating binder mass fraction</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasCoating-hasBinder-hasMeasuredProperty-MassFraction</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t>Positive electrode coating  thickness</t>
-        </is>
-      </c>
-      <c r="B51" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E51" s="12" t="n"/>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasCoating-hasMeasuredProperty-Thickness</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>Positive electrode optional microstructural/physical parameters</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="n"/>
-      <c r="C52" s="11" t="n"/>
-      <c r="D52" s="11" t="n"/>
-      <c r="E52" s="11" t="n"/>
-      <c r="F52" s="11" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode substrate porosity</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>Positive electrode coating binder material</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Porosity</t>
+          <t>hasPositiveElectrode-hasCoating-hasBinder</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material mean particle size (leave blank for films)</t>
-        </is>
-      </c>
-      <c r="B54" s="12" t="n">
-        <v>0.007</v>
-      </c>
+          <t>Positive electrode coating binder mass fraction</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="n"/>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E54" s="12" t="n"/>
       <c r="F54" s="12" t="inlineStr">
         <is>
+          <t>hasPositiveElectrode-hasCoating-hasBinder-hasMeasuredProperty-MassFraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode coating thickness</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-hasMeasuredProperty-Thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>Positive electrode optional microstructural/physical parameters</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n"/>
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="11" t="n"/>
+      <c r="F56" s="11" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode substrate porosity</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Positive electrode substrate mean pore size</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="n"/>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-MeanPoreSize</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode coating active material median particle size (leave blank for films)</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="n"/>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-D50ParticleSize</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="13" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>Positive electrode optional component manufacturer information</t>
         </is>
       </c>
-      <c r="B55" s="11" t="n"/>
-      <c r="C55" s="11" t="n"/>
-      <c r="D55" s="11" t="n"/>
-      <c r="E55" s="11" t="n"/>
-      <c r="F55" s="11" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="B60" s="11" t="n"/>
+      <c r="C60" s="11" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="11" t="n"/>
+      <c r="F60" s="11" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Positive electrode manufacturer</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Empa</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Baoji Qixin Titanium</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="12" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>Positive electrode manufacturer product ID</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>18x_Ti</t>
-        </is>
-      </c>
-      <c r="C57" s="12" t="n"/>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E57" s="12" t="n"/>
-      <c r="F57" s="12" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>Iridium Oxide Coated Titanium Anodes</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="n"/>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="n"/>
+      <c r="F62" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Positive electrode substrate manufacturer</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>Fuel Cell Store</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>Positive electrode substrate manufacturer product ID</t>
         </is>
       </c>
-      <c r="B59" s="12" t="n">
-        <v>40050001</v>
-      </c>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="12" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E59" s="12" t="n"/>
-      <c r="F59" s="12" t="inlineStr">
+      <c r="B64" s="12" t="n"/>
+      <c r="C64" s="12" t="n"/>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="n"/>
+      <c r="F64" s="12" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasSubstrate-schema:productID</t>
         </is>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>Positive electrode coating active material manufacturer</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Fuel Cell Store</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="n"/>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>Positive electrode coating active material manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B61" s="12" t="n">
-        <v>57080249</v>
-      </c>
-      <c r="C61" s="12" t="n"/>
-      <c r="D61" s="12" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E61" s="12" t="n"/>
-      <c r="F61" s="12" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-schema:productID</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>Positive electrode coating binder manufacturer</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>Chemours</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="n"/>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasCoating-hasBinder-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>Positive electrode coating binder manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B63" s="12" t="inlineStr">
-        <is>
-          <t>D521CS</t>
-        </is>
-      </c>
-      <c r="C63" s="12" t="n"/>
-      <c r="D63" s="12" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E63" s="12" t="n"/>
-      <c r="F63" s="12" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasCoating-hasBinder-schema:productID</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr">
-        <is>
-          <t>Negative electrode gas supply</t>
-        </is>
-      </c>
-      <c r="B64" s="15" t="n"/>
-      <c r="C64" s="15" t="n"/>
-      <c r="D64" s="15" t="n"/>
-      <c r="E64" s="15" t="n"/>
-      <c r="F64" s="15" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Negative electrode gas A</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>CarbonDioxide</t>
-        </is>
-      </c>
+          <t>Positive electrode coating active material manufacturer</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="n"/>
       <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E65" s="4" t="n"/>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-Gas</t>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="inlineStr">
-        <is>
-          <t>Negative electrode gas A volume fraction</t>
-        </is>
-      </c>
-      <c r="B66" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="C66" s="16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E66" s="16" t="n"/>
-      <c r="F66" s="16" t="inlineStr">
-        <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>Positive electrode coating active material manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="n"/>
+      <c r="C66" s="12" t="n"/>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="n"/>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Negative electrode gas B</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Argon</t>
-        </is>
-      </c>
+          <t>Positive electrode coating binder manufacturer</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n"/>
       <c r="C67" s="4" t="n"/>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-Gas</t>
+          <t>hasPositiveElectrode-hasCoating-hasBinder-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="inlineStr">
-        <is>
-          <t>Negative electrode gas B volume fraction</t>
-        </is>
-      </c>
-      <c r="B68" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" s="16" t="inlineStr">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>Positive electrode coating binder manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="n"/>
+      <c r="C68" s="12" t="n"/>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="n"/>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-hasBinder-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>Negative electrode gas supply</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="n"/>
+      <c r="C69" s="15" t="n"/>
+      <c r="D69" s="15" t="n"/>
+      <c r="E69" s="15" t="n"/>
+      <c r="F69" s="15" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode gas A</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>CarbonDioxide</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n"/>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="n"/>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-type|Gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>Negative electrode gas A volume fraction</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E68" s="16" t="n"/>
-      <c r="F68" s="16" t="inlineStr">
-        <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>Negative electrode gas flow rate</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>mL/min</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="16" t="inlineStr">
-        <is>
-          <t>Negative electrode gas pressure</t>
-        </is>
-      </c>
-      <c r="B70" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" s="16" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="D70" s="16" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E70" s="16" t="n"/>
-      <c r="F70" s="16" t="inlineStr">
-        <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-Pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="14" t="inlineStr">
-        <is>
-          <t>Catholyte</t>
-        </is>
-      </c>
-      <c r="B71" s="15" t="n"/>
-      <c r="C71" s="15" t="n"/>
-      <c r="D71" s="15" t="n"/>
-      <c r="E71" s="15" t="n"/>
-      <c r="F71" s="15" t="n"/>
+      <c r="E71" s="16" t="n"/>
+      <c r="F71" s="16" t="inlineStr">
+        <is>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Catholyte solvent A</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
+          <t>Negative electrode gas B</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n"/>
       <c r="C72" s="4" t="n"/>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E72" s="4" t="n"/>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA</t>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-type|Gas</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Catholyte solvent A volume fraction</t>
-        </is>
-      </c>
-      <c r="B73" s="16" t="n">
-        <v>100</v>
-      </c>
+          <t>Negative electrode gas B volume fraction</t>
+        </is>
+      </c>
+      <c r="B73" s="16" t="n"/>
       <c r="C73" s="16" t="inlineStr">
         <is>
           <t>%</t>
@@ -2235,352 +2171,350 @@
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E73" s="16" t="n"/>
       <c r="F73" s="16" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Catholyte solvent B</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="n"/>
-      <c r="C74" s="4" t="n"/>
+          <t>Negative electrode gas flow rate</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB</t>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>Catholyte solvent B volume fraction</t>
-        </is>
-      </c>
-      <c r="B75" s="16" t="n"/>
+          <t>Negative electrode gas pressure</t>
+        </is>
+      </c>
+      <c r="B75" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="C75" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E75" s="16" t="n"/>
       <c r="F75" s="16" t="inlineStr">
         <is>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-Pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>Catholyte</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="n"/>
+      <c r="C76" s="15" t="n"/>
+      <c r="D76" s="15" t="n"/>
+      <c r="E76" s="15" t="n"/>
+      <c r="F76" s="15" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Catholyte solvent A</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n"/>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>hasCatholyte-hasSolvent-hasConstituentA</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>Catholyte solvent A volume fraction</t>
+        </is>
+      </c>
+      <c r="B78" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C78" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E78" s="16" t="n"/>
+      <c r="F78" s="16" t="inlineStr">
+        <is>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Catholyte solvent B</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="n"/>
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="n"/>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>hasCatholyte-hasSolvent-hasConstituentB</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>Catholyte solvent B volume fraction</t>
+        </is>
+      </c>
+      <c r="B80" s="16" t="n"/>
+      <c r="C80" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D80" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="n"/>
+      <c r="F80" s="16" t="inlineStr">
+        <is>
           <t>hasCatholyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>Catholyte solute A</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>PotassiumCarbonate</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>PotassiumBicarbonate</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E76" s="4" t="n"/>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentA</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="16" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="16" t="inlineStr">
         <is>
           <t>Catholyte solute A molarity</t>
         </is>
       </c>
-      <c r="B77" s="16" t="n">
+      <c r="B82" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C77" s="16" t="inlineStr">
+      <c r="C82" s="16" t="inlineStr">
         <is>
           <t>mol/L</t>
         </is>
       </c>
-      <c r="D77" s="16" t="inlineStr">
+      <c r="D82" s="16" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E77" s="16" t="n"/>
-      <c r="F77" s="16" t="inlineStr">
+      <c r="E82" s="16" t="n"/>
+      <c r="F82" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>Catholyte solute B</t>
         </is>
       </c>
-      <c r="B78" s="4" t="n"/>
-      <c r="C78" s="4" t="n"/>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="n"/>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="B83" s="4" t="n"/>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentB</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="16" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
         <is>
           <t>Catholyte solute B molarity</t>
         </is>
       </c>
-      <c r="B79" s="16" t="n"/>
-      <c r="C79" s="16" t="inlineStr">
+      <c r="B84" s="16" t="n"/>
+      <c r="C84" s="16" t="inlineStr">
         <is>
           <t>mol/L</t>
         </is>
       </c>
-      <c r="D79" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E79" s="16" t="n"/>
-      <c r="F79" s="16" t="inlineStr">
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E84" s="16" t="n"/>
+      <c r="F84" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>Catholyte volume</t>
         </is>
       </c>
-      <c r="B80" s="4" t="n">
+      <c r="B85" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E80" s="4" t="n"/>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="16" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="16" t="inlineStr">
         <is>
           <t>Catholyte volume flow rate</t>
         </is>
       </c>
-      <c r="B81" s="16" t="n">
+      <c r="B86" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C81" s="16" t="inlineStr">
+      <c r="C86" s="16" t="inlineStr">
         <is>
           <t>mL/min</t>
         </is>
       </c>
-      <c r="D81" s="16" t="inlineStr">
+      <c r="D86" s="16" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E81" s="16" t="n"/>
-      <c r="F81" s="16" t="inlineStr">
+      <c r="E86" s="16" t="n"/>
+      <c r="F86" s="16" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>Catholyte pressure</t>
         </is>
       </c>
-      <c r="B82" s="4" t="n">
+      <c r="B87" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>bar</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="E87" s="4" t="n"/>
+      <c r="F87" s="4" t="inlineStr">
         <is>
           <t>hasCatholyte-hasMeasuredProperty-Pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="17" t="inlineStr">
-        <is>
-          <t>Catholyte optional physical parameters</t>
-        </is>
-      </c>
-      <c r="B83" s="15" t="n"/>
-      <c r="C83" s="15" t="n"/>
-      <c r="D83" s="15" t="n"/>
-      <c r="E83" s="15" t="n"/>
-      <c r="F83" s="15" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>Catholyte conductivity</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>mS/cm</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="n"/>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasMeasuredProperty-ElectrolyticConductivity</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="16" t="inlineStr">
-        <is>
-          <t>Catholyte pH</t>
-        </is>
-      </c>
-      <c r="B85" s="16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C85" s="16" t="inlineStr">
-        <is>
-          <t>unitless</t>
-        </is>
-      </c>
-      <c r="D85" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E85" s="16" t="n"/>
-      <c r="F85" s="16" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasMeasuredProperty-PH</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>Catholyte density</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>g/cm3</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="n"/>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasMeasuredProperty-Density</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="16" t="inlineStr">
-        <is>
-          <t>Catholyte temperature</t>
-        </is>
-      </c>
-      <c r="B87" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="C87" s="16" t="inlineStr">
-        <is>
-          <t>°C</t>
-        </is>
-      </c>
-      <c r="D87" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E87" s="16" t="n"/>
-      <c r="F87" s="16" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasMeasuredProperty-CelsiusTemperature</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t>Catholyte optional component manufacturer information</t>
+          <t>Catholyte optional physical parameters</t>
         </is>
       </c>
       <c r="B88" s="15" t="n"/>
@@ -2592,15 +2526,15 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Catholyte manufacturer</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Empa</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="n"/>
+          <t>Catholyte conductivity</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="n"/>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>mS/cm</t>
+        </is>
+      </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2609,22 +2543,24 @@
       <c r="E89" s="4" t="n"/>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-schema:manufacturer</t>
+          <t>hasCatholyte-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="16" t="inlineStr">
         <is>
-          <t>Catholyte manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B90" s="16" t="inlineStr">
-        <is>
-          <t>KCl_1M_catholyte</t>
-        </is>
-      </c>
-      <c r="C90" s="16" t="n"/>
+          <t>Catholyte pH</t>
+        </is>
+      </c>
+      <c r="B90" s="16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2633,18 +2569,24 @@
       <c r="E90" s="16" t="n"/>
       <c r="F90" s="16" t="inlineStr">
         <is>
-          <t>hasCatholyte-schema:productID</t>
+          <t>hasCatholyte-hasMeasuredProperty-PH</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Catholyte solvent A manufacturer</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="n"/>
+          <t>Catholyte density</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>g/cm3</t>
+        </is>
+      </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2653,18 +2595,24 @@
       <c r="E91" s="4" t="n"/>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolventA-schema:manufacturer</t>
+          <t>hasCatholyte-hasMeasuredProperty-Density</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="16" t="inlineStr">
         <is>
-          <t>Catholyte solvent A manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B92" s="16" t="n"/>
-      <c r="C92" s="16" t="n"/>
+          <t>Catholyte temperature</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2673,157 +2621,159 @@
       <c r="E92" s="16" t="n"/>
       <c r="F92" s="16" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolventA-schema:productID</t>
+          <t>hasCatholyte-hasMeasuredProperty-CelsiusTemperature</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="A93" s="17" t="inlineStr">
+        <is>
+          <t>Catholyte optional component manufacturer information</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="n"/>
+      <c r="C93" s="15" t="n"/>
+      <c r="D93" s="15" t="n"/>
+      <c r="E93" s="15" t="n"/>
+      <c r="F93" s="15" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Catholyte manufacturer</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>hasCatholyte-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Catholyte manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B95" s="16" t="inlineStr">
+        <is>
+          <t>KHCO3_1M_catholyte</t>
+        </is>
+      </c>
+      <c r="C95" s="16" t="n"/>
+      <c r="D95" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E95" s="16" t="n"/>
+      <c r="F95" s="16" t="inlineStr">
+        <is>
+          <t>hasCatholyte-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Catholyte solvent A manufacturer</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="n"/>
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="n"/>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Catholyte solvent A manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B97" s="16" t="n"/>
+      <c r="C97" s="16" t="n"/>
+      <c r="D97" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E97" s="16" t="n"/>
+      <c r="F97" s="16" t="inlineStr">
+        <is>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>Catholyte solvent B manufacturer</t>
         </is>
       </c>
-      <c r="B93" s="4" t="n"/>
-      <c r="C93" s="4" t="n"/>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="n"/>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasSolventB-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="16" t="inlineStr">
+      <c r="B98" s="4" t="n"/>
+      <c r="C98" s="4" t="n"/>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="n"/>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t>Catholyte solvent B manufacturer product ID</t>
         </is>
       </c>
-      <c r="B94" s="16" t="n"/>
-      <c r="C94" s="16" t="n"/>
-      <c r="D94" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E94" s="16" t="n"/>
-      <c r="F94" s="16" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasSolventB-schema:productID</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>Catholyte solute A manufacturer</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Thermo Fisher Scientific</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="n"/>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="n"/>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasSoluteA-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="16" t="inlineStr">
-        <is>
-          <t>Catholyte solute A manufacturer productD</t>
-        </is>
-      </c>
-      <c r="B96" s="16" t="n">
-        <v>424090010</v>
-      </c>
-      <c r="C96" s="16" t="n"/>
-      <c r="D96" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E96" s="16" t="n"/>
-      <c r="F96" s="16" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasSoluteA-schema:productID</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>Catholyte solute B manufacturer</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="n"/>
-      <c r="C97" s="4" t="n"/>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="n"/>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasSoluteB-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="16" t="inlineStr">
-        <is>
-          <t>Catholyte solute B manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B98" s="16" t="n"/>
-      <c r="C98" s="16" t="n"/>
-      <c r="D98" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E98" s="16" t="n"/>
-      <c r="F98" s="16" t="inlineStr">
-        <is>
-          <t>hasCatholyte-hasSoluteB-schema:productID</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="14" t="inlineStr">
-        <is>
-          <t>Positive electrode gas supply</t>
-        </is>
-      </c>
-      <c r="B99" s="15" t="n"/>
-      <c r="C99" s="15" t="n"/>
-      <c r="D99" s="15" t="n"/>
-      <c r="E99" s="15" t="n"/>
-      <c r="F99" s="15" t="n"/>
+      <c r="B99" s="16" t="n"/>
+      <c r="C99" s="16" t="n"/>
+      <c r="D99" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E99" s="16" t="n"/>
+      <c r="F99" s="16" t="inlineStr">
+        <is>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-schema:productID</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode gas A</t>
+          <t>Catholyte solute A manufacturer</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Nitrogen</t>
+          <t>Millipore Sigma</t>
         </is>
       </c>
       <c r="C100" s="4" t="n"/>
@@ -2835,24 +2785,20 @@
       <c r="E100" s="4" t="n"/>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-Gas</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="16" t="inlineStr">
         <is>
-          <t>Positive electrode gas A volume fraction</t>
+          <t>Catholyte solute A manufacturer product ID</t>
         </is>
       </c>
       <c r="B101" s="16" t="n">
-        <v>100</v>
-      </c>
-      <c r="C101" s="16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+        <v>237205</v>
+      </c>
+      <c r="C101" s="16" t="n"/>
       <c r="D101" s="16" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2861,14 +2807,14 @@
       <c r="E101" s="16" t="n"/>
       <c r="F101" s="16" t="inlineStr">
         <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode gas B</t>
+          <t>Catholyte solute B manufacturer</t>
         </is>
       </c>
       <c r="B102" s="4" t="n"/>
@@ -2881,22 +2827,18 @@
       <c r="E102" s="4" t="n"/>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-Gas</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="16" t="inlineStr">
         <is>
-          <t>Positive electrode gas B volume fraction</t>
+          <t>Catholyte solute B manufacturer product ID</t>
         </is>
       </c>
       <c r="B103" s="16" t="n"/>
-      <c r="C103" s="16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="C103" s="16" t="n"/>
       <c r="D103" s="16" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2905,107 +2847,93 @@
       <c r="E103" s="16" t="n"/>
       <c r="F103" s="16" t="inlineStr">
         <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>Positive electrode gas flow rate</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>mL/min</t>
-        </is>
-      </c>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="n"/>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
-        </is>
-      </c>
+      <c r="A104" s="14" t="inlineStr">
+        <is>
+          <t>Positive electrode gas supply</t>
+        </is>
+      </c>
+      <c r="B104" s="15" t="n"/>
+      <c r="C104" s="15" t="n"/>
+      <c r="D104" s="15" t="n"/>
+      <c r="E104" s="15" t="n"/>
+      <c r="F104" s="15" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="16" t="inlineStr">
-        <is>
-          <t>Positive electrode gas pressure</t>
-        </is>
-      </c>
-      <c r="B105" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C105" s="16" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="D105" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E105" s="16" t="n"/>
-      <c r="F105" s="16" t="inlineStr">
-        <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-Pressure</t>
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode gas A</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="n"/>
+      <c r="C105" s="4" t="n"/>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="n"/>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-type|Gas</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="14" t="inlineStr">
-        <is>
-          <t>Anolyte</t>
-        </is>
-      </c>
-      <c r="B106" s="15" t="n"/>
-      <c r="C106" s="15" t="n"/>
-      <c r="D106" s="15" t="n"/>
-      <c r="E106" s="15" t="n"/>
-      <c r="F106" s="15" t="n"/>
+      <c r="A106" s="16" t="inlineStr">
+        <is>
+          <t>Positive electrode gas A volume fraction</t>
+        </is>
+      </c>
+      <c r="B106" s="16" t="n"/>
+      <c r="C106" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D106" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E106" s="16" t="n"/>
+      <c r="F106" s="16" t="inlineStr">
+        <is>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Anolyte solvent A</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
+          <t>Positive electrode gas B</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="n"/>
       <c r="C107" s="4" t="n"/>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E107" s="4" t="n"/>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA</t>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-type|Gas</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="16" t="inlineStr">
         <is>
-          <t>Anolyte solvent A volume fraction</t>
-        </is>
-      </c>
-      <c r="B108" s="16" t="n">
-        <v>100</v>
-      </c>
+          <t>Positive electrode gas B volume fraction</t>
+        </is>
+      </c>
+      <c r="B108" s="16" t="n"/>
       <c r="C108" s="16" t="inlineStr">
         <is>
           <t>%</t>
@@ -3013,24 +2941,28 @@
       </c>
       <c r="D108" s="16" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E108" s="16" t="n"/>
       <c r="F108" s="16" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Anolyte solvent B</t>
+          <t>Positive electrode gas flow rate</t>
         </is>
       </c>
       <c r="B109" s="4" t="n"/>
-      <c r="C109" s="4" t="n"/>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3039,20 +2971,20 @@
       <c r="E109" s="4" t="n"/>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB</t>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="16" t="inlineStr">
         <is>
-          <t>Anolyte solvent B volume fraction</t>
+          <t>Positive electrode gas pressure</t>
         </is>
       </c>
       <c r="B110" s="16" t="n"/>
       <c r="C110" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="D110" s="16" t="inlineStr">
@@ -3063,302 +2995,292 @@
       <c r="E110" s="16" t="n"/>
       <c r="F110" s="16" t="inlineStr">
         <is>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasActiveMaterial-type|GasMixture-hasMeasuredProperty-Pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="14" t="inlineStr">
+        <is>
+          <t>Anolyte</t>
+        </is>
+      </c>
+      <c r="B111" s="15" t="n"/>
+      <c r="C111" s="15" t="n"/>
+      <c r="D111" s="15" t="n"/>
+      <c r="E111" s="15" t="n"/>
+      <c r="F111" s="15" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>Anolyte solvent A</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="n"/>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasSolvent-hasConstituentA</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="16" t="inlineStr">
+        <is>
+          <t>Anolyte solvent A volume fraction</t>
+        </is>
+      </c>
+      <c r="B113" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C113" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D113" s="16" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E113" s="16" t="n"/>
+      <c r="F113" s="16" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>Anolyte solvent B</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="n"/>
+      <c r="C114" s="4" t="n"/>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="n"/>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasSolvent-hasConstituentB</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="16" t="inlineStr">
+        <is>
+          <t>Anolyte solvent B volume fraction</t>
+        </is>
+      </c>
+      <c r="B115" s="16" t="n"/>
+      <c r="C115" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D115" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E115" s="16" t="n"/>
+      <c r="F115" s="16" t="inlineStr">
+        <is>
           <t>hasAnolyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
         <is>
           <t>Anolyte solute A</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B116" s="4" t="inlineStr">
         <is>
           <t>SulfuricAcid</t>
         </is>
       </c>
-      <c r="C111" s="4" t="n"/>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="C116" s="4" t="n"/>
+      <c r="D116" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E111" s="4" t="n"/>
-      <c r="F111" s="4" t="inlineStr">
+      <c r="E116" s="4" t="n"/>
+      <c r="F116" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentA</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="16" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="16" t="inlineStr">
         <is>
           <t>Anolyte solute A molarity</t>
         </is>
       </c>
-      <c r="B112" s="16" t="n">
+      <c r="B117" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C112" s="16" t="inlineStr">
+      <c r="C117" s="16" t="inlineStr">
         <is>
           <t>mol/L</t>
         </is>
       </c>
-      <c r="D112" s="16" t="inlineStr">
+      <c r="D117" s="16" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E112" s="16" t="n"/>
-      <c r="F112" s="16" t="inlineStr">
+      <c r="E117" s="16" t="n"/>
+      <c r="F117" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
         <is>
           <t>Anolyte solute B</t>
         </is>
       </c>
-      <c r="B113" s="4" t="n"/>
-      <c r="C113" s="4" t="n"/>
-      <c r="D113" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="n"/>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="B118" s="4" t="n"/>
+      <c r="C118" s="4" t="n"/>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="n"/>
+      <c r="F118" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentB</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="16" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="16" t="inlineStr">
         <is>
           <t>Anolyte solute B molarity</t>
         </is>
       </c>
-      <c r="B114" s="16" t="n"/>
-      <c r="C114" s="16" t="inlineStr">
+      <c r="B119" s="16" t="n"/>
+      <c r="C119" s="16" t="inlineStr">
         <is>
           <t>mol/L</t>
         </is>
       </c>
-      <c r="D114" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E114" s="16" t="n"/>
-      <c r="F114" s="16" t="inlineStr">
+      <c r="D119" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E119" s="16" t="n"/>
+      <c r="F119" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>Anolyte volume</t>
         </is>
       </c>
-      <c r="B115" s="4" t="n">
+      <c r="B120" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="D120" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E115" s="4" t="n"/>
-      <c r="F115" s="4" t="inlineStr">
+      <c r="E120" s="4" t="n"/>
+      <c r="F120" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="16" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="16" t="inlineStr">
         <is>
           <t>Anolyte volume flow rate</t>
         </is>
       </c>
-      <c r="B116" s="16" t="n">
+      <c r="B121" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C116" s="16" t="inlineStr">
+      <c r="C121" s="16" t="inlineStr">
         <is>
           <t>mL/min</t>
         </is>
       </c>
-      <c r="D116" s="16" t="inlineStr">
+      <c r="D121" s="16" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E116" s="16" t="n"/>
-      <c r="F116" s="16" t="inlineStr">
+      <c r="E121" s="16" t="n"/>
+      <c r="F121" s="16" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
         <is>
           <t>Anolyte pressure</t>
         </is>
       </c>
-      <c r="B117" s="4" t="n">
+      <c r="B122" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C122" s="4" t="inlineStr">
         <is>
           <t>bar</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D122" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E117" s="4" t="n"/>
-      <c r="F117" s="4" t="inlineStr">
+      <c r="E122" s="4" t="n"/>
+      <c r="F122" s="4" t="inlineStr">
         <is>
           <t>hasAnolyte-hasMeasuredProperty-Pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="17" t="inlineStr">
-        <is>
-          <t>Anolyte optional physical parameters</t>
-        </is>
-      </c>
-      <c r="B118" s="15" t="n"/>
-      <c r="C118" s="15" t="n"/>
-      <c r="D118" s="15" t="n"/>
-      <c r="E118" s="15" t="n"/>
-      <c r="F118" s="15" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>Anolyte conductivity</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="n">
-        <v>800</v>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>mS/cm</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="n"/>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasMeasuredProperty-ElectrolyticConductivity</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="16" t="inlineStr">
-        <is>
-          <t>Anolyte pH</t>
-        </is>
-      </c>
-      <c r="B120" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C120" s="16" t="inlineStr">
-        <is>
-          <t>unitless</t>
-        </is>
-      </c>
-      <c r="D120" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E120" s="16" t="n"/>
-      <c r="F120" s="16" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasMeasuredProperty-PH</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>Anolyte density</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>g/cm3</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="n"/>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasMeasuredProperty-Density</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="16" t="inlineStr">
-        <is>
-          <t>Anolyte temperature</t>
-        </is>
-      </c>
-      <c r="B122" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="C122" s="16" t="inlineStr">
-        <is>
-          <t>°C</t>
-        </is>
-      </c>
-      <c r="D122" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E122" s="16" t="n"/>
-      <c r="F122" s="16" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasMeasuredProperty-CelsiusTemperature</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="17" t="inlineStr">
         <is>
-          <t>Anolyte optional component manufacturer information</t>
+          <t>Anolyte optional physical parameters</t>
         </is>
       </c>
       <c r="B123" s="15" t="n"/>
@@ -3370,15 +3292,15 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>Anolyte manufacturer</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>Empa</t>
-        </is>
-      </c>
-      <c r="C124" s="4" t="n"/>
+          <t>Anolyte conductivity</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="n"/>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>mS/cm</t>
+        </is>
+      </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3387,22 +3309,24 @@
       <c r="E124" s="4" t="n"/>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-schema:manufacturer</t>
+          <t>hasAnolyte-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="16" t="inlineStr">
         <is>
-          <t>Anolyte manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B125" s="16" t="inlineStr">
-        <is>
-          <t>H2SO4_1M_anolyte</t>
-        </is>
-      </c>
-      <c r="C125" s="16" t="n"/>
+          <t>Anolyte pH</t>
+        </is>
+      </c>
+      <c r="B125" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="16" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
       <c r="D125" s="16" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3411,18 +3335,24 @@
       <c r="E125" s="16" t="n"/>
       <c r="F125" s="16" t="inlineStr">
         <is>
-          <t>hasAnolyte-schema:productID</t>
+          <t>hasAnolyte-hasMeasuredProperty-PH</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>Anolyte solvent A manufacturer</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="n"/>
-      <c r="C126" s="4" t="n"/>
+          <t>Anolyte density</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>g/cm3</t>
+        </is>
+      </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3431,18 +3361,24 @@
       <c r="E126" s="4" t="n"/>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-schema:manufacturer</t>
+          <t>hasAnolyte-hasMeasuredProperty-Density</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="16" t="inlineStr">
         <is>
-          <t>Anolyte solvent A manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B127" s="16" t="n"/>
-      <c r="C127" s="16" t="n"/>
+          <t>Anolyte temperature</t>
+        </is>
+      </c>
+      <c r="B127" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="C127" s="16" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
       <c r="D127" s="16" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3451,422 +3387,400 @@
       <c r="E127" s="16" t="n"/>
       <c r="F127" s="16" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-schema:productID</t>
+          <t>hasAnolyte-hasMeasuredProperty-CelsiusTemperature</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="4" t="inlineStr">
+      <c r="A128" s="17" t="inlineStr">
+        <is>
+          <t>Anolyte optional component manufacturer information</t>
+        </is>
+      </c>
+      <c r="B128" s="15" t="n"/>
+      <c r="C128" s="15" t="n"/>
+      <c r="D128" s="15" t="n"/>
+      <c r="E128" s="15" t="n"/>
+      <c r="F128" s="15" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>Anolyte manufacturer</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="n"/>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="n"/>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>hasAnolyte-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="16" t="inlineStr">
+        <is>
+          <t>Anolyte manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B130" s="16" t="inlineStr">
+        <is>
+          <t>H2SO4_1M_anolyte</t>
+        </is>
+      </c>
+      <c r="C130" s="16" t="n"/>
+      <c r="D130" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E130" s="16" t="n"/>
+      <c r="F130" s="16" t="inlineStr">
+        <is>
+          <t>hasAnolyte-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>Anolyte solvent A manufacturer</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="n"/>
+      <c r="C131" s="4" t="n"/>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="n"/>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="16" t="inlineStr">
+        <is>
+          <t>Anolyte solvent A manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B132" s="16" t="n"/>
+      <c r="C132" s="16" t="n"/>
+      <c r="D132" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E132" s="16" t="n"/>
+      <c r="F132" s="16" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
         <is>
           <t>Anolyte solvent B manufacturer</t>
         </is>
       </c>
-      <c r="B128" s="4" t="n"/>
-      <c r="C128" s="4" t="n"/>
-      <c r="D128" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="n"/>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasSolvent-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="16" t="inlineStr">
+      <c r="B133" s="4" t="n"/>
+      <c r="C133" s="4" t="n"/>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="n"/>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="16" t="inlineStr">
         <is>
           <t>Anolyte solvent B manufacturer product ID</t>
         </is>
       </c>
-      <c r="B129" s="16" t="n"/>
-      <c r="C129" s="16" t="n"/>
-      <c r="D129" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E129" s="16" t="n"/>
-      <c r="F129" s="16" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasSolvent-schema:productID</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>Anolyte solute A manufacturer</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>Millipore Sigma</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="n"/>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="n"/>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasSolute-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="16" t="inlineStr">
-        <is>
-          <t>Anolyte solute A manufacturer productD</t>
-        </is>
-      </c>
-      <c r="B131" s="16" t="n">
-        <v>258105</v>
-      </c>
-      <c r="C131" s="16" t="n"/>
-      <c r="D131" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E131" s="16" t="n"/>
-      <c r="F131" s="16" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasSolute-schema:productID</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="4" t="inlineStr">
-        <is>
-          <t>Anolyte solute B manufacturer</t>
-        </is>
-      </c>
-      <c r="B132" s="4" t="n"/>
-      <c r="C132" s="4" t="n"/>
-      <c r="D132" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="n"/>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasSolute-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="16" t="inlineStr">
-        <is>
-          <t>Anolyte solute B manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B133" s="16" t="n"/>
-      <c r="C133" s="16" t="n"/>
-      <c r="D133" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E133" s="16" t="n"/>
-      <c r="F133" s="16" t="inlineStr">
-        <is>
-          <t>hasAnolyte-hasSolute-schema:productID</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Membrane</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="n"/>
-      <c r="C134" s="3" t="n"/>
-      <c r="D134" s="3" t="n"/>
-      <c r="E134" s="3" t="n"/>
-      <c r="F134" s="3" t="n"/>
+      <c r="B134" s="16" t="n"/>
+      <c r="C134" s="16" t="n"/>
+      <c r="D134" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E134" s="16" t="n"/>
+      <c r="F134" s="16" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-schema:productID</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>Membrane type</t>
+          <t>Anolyte solute A manufacturer</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>IonExchangeMembrane</t>
+          <t>Millipore Sigma</t>
         </is>
       </c>
       <c r="C135" s="4" t="n"/>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E135" s="4" t="n"/>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>Membrane type  (BilayerMembrane or leave blank)</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>BilayerMembrane</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="n"/>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="n"/>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>hasSeparator</t>
+      <c r="A136" s="16" t="inlineStr">
+        <is>
+          <t>Anolyte solute A manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B136" s="16" t="n">
+        <v>258105</v>
+      </c>
+      <c r="C136" s="16" t="n"/>
+      <c r="D136" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E136" s="16" t="n"/>
+      <c r="F136" s="16" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasSolute-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>Membrane A type (facing catholyte)</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>AnionExchangeMembrane</t>
-        </is>
-      </c>
+          <t>Anolyte solute B manufacturer</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="n"/>
       <c r="C137" s="4" t="n"/>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E137" s="4" t="n"/>
       <c r="F137" s="4" t="inlineStr">
         <is>
+          <t>hasAnolyte-hasSolute-hasConstituentB-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="16" t="inlineStr">
+        <is>
+          <t>Anolyte solute B manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B138" s="16" t="n"/>
+      <c r="C138" s="16" t="n"/>
+      <c r="D138" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E138" s="16" t="n"/>
+      <c r="F138" s="16" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasSolute-hasConstituentB-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Membrane</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="n"/>
+      <c r="C139" s="3" t="n"/>
+      <c r="D139" s="3" t="n"/>
+      <c r="E139" s="3" t="n"/>
+      <c r="F139" s="3" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>Membrane type</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>IonExchangeMembrane</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="n"/>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="n"/>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>hasSeparator</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>Membrane type (BilayerMembrane or leave blank)</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="n"/>
+      <c r="C141" s="5" t="n"/>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n"/>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>hasSeparator</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>Membrane A type (facing catholyte)</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>CationExchangeMembrane</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="n"/>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="n"/>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
           <t>hasSeparator-hasElectrolyteA</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="5" t="inlineStr">
-        <is>
-          <t>Membrane A material A (facing catholyte)</t>
-        </is>
-      </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>PolyArylPiperidinium</t>
-        </is>
-      </c>
-      <c r="C138" s="5" t="n"/>
-      <c r="D138" s="5" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>Membrane A material (facing catholyte)</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>PerfluorosulfonicAcid</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="n"/>
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E138" s="5" t="n"/>
-      <c r="F138" s="5" t="inlineStr">
+      <c r="E143" s="5" t="n"/>
+      <c r="F143" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="4" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
         <is>
           <t>Membrane A thickness (facing catholyte)</t>
         </is>
       </c>
-      <c r="B139" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="B144" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
         <is>
           <t>um</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="D144" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E139" s="4" t="n"/>
-      <c r="F139" s="4" t="inlineStr">
+      <c r="E144" s="4" t="n"/>
+      <c r="F144" s="4" t="inlineStr">
         <is>
           <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="5" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>Membrane A ion exchange capacity (facing catholyte)</t>
         </is>
       </c>
-      <c r="B140" s="5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C140" s="5" t="inlineStr">
+      <c r="B145" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
         <is>
           <t>mEq/100g</t>
         </is>
       </c>
-      <c r="D140" s="5" t="inlineStr">
+      <c r="D145" s="5" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E140" s="5" t="n"/>
-      <c r="F140" s="5" t="inlineStr">
-        <is>
-          <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-AmountConcentration</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>Membrane B type (facing anolyte)</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>CationExchangeMembrane</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="n"/>
-      <c r="D141" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="n"/>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>hasSeparator-hasElectrolyteB</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t>Membrane B material A (facing anolyte)</t>
-        </is>
-      </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>PerfluorosulfonicAcid</t>
-        </is>
-      </c>
-      <c r="C142" s="5" t="n"/>
-      <c r="D142" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E142" s="5" t="n"/>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>hasSeparator-hasElectrolyteB</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>Membrane B thickness (facing anolyte)</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E143" s="4" t="n"/>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-Thickness</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>Membrane B ion exchange capacity (facing anolyte)</t>
-        </is>
-      </c>
-      <c r="B144" s="5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C144" s="5" t="inlineStr">
-        <is>
-          <t>mEq/100g</t>
-        </is>
-      </c>
-      <c r="D144" s="5" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E144" s="5" t="n"/>
-      <c r="F144" s="5" t="inlineStr">
-        <is>
-          <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-AmountConcentration</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Membrane optional physical parameters</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="n"/>
-      <c r="C145" s="3" t="n"/>
-      <c r="D145" s="3" t="n"/>
-      <c r="E145" s="3" t="n"/>
-      <c r="F145" s="3" t="n"/>
+      <c r="E145" s="5" t="n"/>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-IonExchangeCapacity</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>Membrane A area specific conductivity</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>mS/cm</t>
-        </is>
-      </c>
+          <t>Membrane B type (facing anolyte)</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="n"/>
+      <c r="C146" s="4" t="n"/>
       <c r="D146" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3875,24 +3789,18 @@
       <c r="E146" s="4" t="n"/>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-ElectrolyticConductivity</t>
+          <t>hasSeparator-hasElectrolyteB</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Membrane B area specific conductivity</t>
-        </is>
-      </c>
-      <c r="B147" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C147" s="5" t="inlineStr">
-        <is>
-          <t>mS/cm</t>
-        </is>
-      </c>
+          <t>Membrane B material (facing anolyte)</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="n"/>
+      <c r="C147" s="5" t="n"/>
       <c r="D147" s="5" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3901,80 +3809,82 @@
       <c r="E147" s="5" t="n"/>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-ElectrolyticConductivity</t>
+          <t>hasSeparator-hasElectrolyteB</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Membrane optional component manufacturer information</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="n"/>
-      <c r="C148" s="3" t="n"/>
-      <c r="D148" s="3" t="n"/>
-      <c r="E148" s="3" t="n"/>
-      <c r="F148" s="3" t="n"/>
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>Membrane B thickness (facing anolyte)</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="n"/>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="n"/>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-Thickness</t>
+        </is>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>Membrane A manufacturer</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>Fuel Cell Store</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="n"/>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E149" s="4" t="n"/>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>hasSeparator-hasElectrolyteA-schema:manufacturer</t>
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>Membrane B ion exchange capacity (facing anolyte)</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="n"/>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>mEq/100g</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n"/>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-IonExchangeCapacity</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>Membrane A manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B150" s="5" t="n">
-        <v>72010015</v>
-      </c>
-      <c r="C150" s="5" t="n"/>
-      <c r="D150" s="5" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E150" s="5" t="n"/>
-      <c r="F150" s="5" t="inlineStr">
-        <is>
-          <t>hasSeparator-hasElectrolyteA-schema:productID</t>
-        </is>
-      </c>
+      <c r="A150" s="18" t="inlineStr">
+        <is>
+          <t>Membrane optional physical parameters</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n"/>
+      <c r="C150" s="3" t="n"/>
+      <c r="D150" s="3" t="n"/>
+      <c r="E150" s="3" t="n"/>
+      <c r="F150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>Membrane B manufacturer</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>Chemours</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="n"/>
+          <t>Membrane A conductivity</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="n"/>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>mS/cm</t>
+        </is>
+      </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3983,22 +3893,22 @@
       <c r="E151" s="4" t="n"/>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasElectrolyteB-schema:manufacturer</t>
+          <t>hasSeparator-hasElectrolyteA-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Membrane B manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B152" s="5" t="inlineStr">
-        <is>
-          <t>N117</t>
-        </is>
-      </c>
-      <c r="C152" s="5" t="n"/>
+          <t>Membrane B conductivity</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="n"/>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>mS/cm</t>
+        </is>
+      </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4007,14 +3917,14 @@
       <c r="E152" s="5" t="n"/>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>hasSeparator-hasElectrolyteB-schema:productID</t>
+          <t>hasSeparator-hasElectrolyteB-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>Cell assembly</t>
+      <c r="A153" s="18" t="inlineStr">
+        <is>
+          <t>Membrane optional component manufacturer information</t>
         </is>
       </c>
       <c r="B153" s="3" t="n"/>
@@ -4026,464 +3936,794 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Cell case type (FlowCell or leave blank)</t>
+          <t>Membrane A manufacturer</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>FlowCell</t>
+          <t>Fuel Cell Store</t>
         </is>
       </c>
       <c r="C154" s="4" t="n"/>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E154" s="4" t="n"/>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>hasCase</t>
+          <t>hasSeparator-hasElectrolyteA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Negative electrode gas compartment (FlowField or leave blank)</t>
-        </is>
-      </c>
-      <c r="B155" s="5" t="inlineStr">
-        <is>
-          <t>FlowField</t>
-        </is>
+          <t>Membrane A manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="n">
+        <v>87010020</v>
       </c>
       <c r="C155" s="5" t="n"/>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E155" s="5" t="n"/>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasComponent</t>
+          <t>hasSeparator-hasElectrolyteA-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>Negative electrode gas compartment width</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
+          <t>Membrane B manufacturer</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="n"/>
+      <c r="C156" s="4" t="n"/>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E156" s="4" t="n"/>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasMeasuredProperty-Width</t>
+          <t>hasSeparator-hasElectrolyteB-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Negative electrode projected area</t>
-        </is>
-      </c>
-      <c r="B157" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C157" s="5" t="inlineStr">
-        <is>
-          <t>cm2</t>
-        </is>
-      </c>
+          <t>Membrane B manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="n"/>
+      <c r="C157" s="5" t="n"/>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E157" s="5" t="n"/>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode-hasMeasuredProperty-Area</t>
+          <t>hasSeparator-hasElectrolyteB-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>Negative electrode to membrane gap/catholyte compartment width</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C158" s="4" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Cell assembly</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="n"/>
+      <c r="C158" s="3" t="n"/>
+      <c r="D158" s="3" t="n"/>
+      <c r="E158" s="3" t="n"/>
+      <c r="F158" s="3" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>Cell case type</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>FlowCell</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="n"/>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>FlowCell or leave blank</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>hasCase</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>Negative electrode gas compartment</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="n"/>
+      <c r="C160" s="5" t="n"/>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>FlowField or leave blank</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasComponent</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode gas compartment width</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="n"/>
+      <c r="C161" s="4" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D158" s="4" t="inlineStr">
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>Leave blank if FlowField</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasMeasuredProperty-Width</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Negative electrode gas compartment volume</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="n"/>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>Leave blank if FlowField</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>hasComponentA-type|NegativeElectrodeGasCompartment-hasMeasuredProperty-Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode geometric surface area</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E158" s="4" t="n"/>
-      <c r="F158" s="4" t="inlineStr">
+      <c r="E163" s="4" t="n"/>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrodeGeometricSurfaceArea</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>Negative electrode real surface area</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="n"/>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="n"/>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrodeRealSurfaceArea</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode electrochemically active surface area</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="n"/>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="n"/>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrochemicallyActiveSurfaceArea</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>Negative electrode to separator gap width</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="n"/>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasMeasuredProperty-ElectrodeToSeparatorGapWidth</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>Catholyte compartment width</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="n"/>
+      <c r="F167" s="4" t="inlineStr">
         <is>
           <t>hasComponentB-type|CatholyteCompartment-hasMeasuredProperty-Width</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="5" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
         <is>
           <t>Catholyte compartment volume</t>
         </is>
       </c>
-      <c r="B159" s="5" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="C159" s="5" t="inlineStr">
+      <c r="B168" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="D168" s="5" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E159" s="5" t="n"/>
-      <c r="F159" s="5" t="inlineStr">
+      <c r="E168" s="5" t="n"/>
+      <c r="F168" s="5" t="inlineStr">
         <is>
           <t>hasComponentB-type|CatholyteCompartment-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="4" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
         <is>
           <t>Reference electrode in catholyte compartment</t>
         </is>
       </c>
-      <c r="B160" s="4" t="inlineStr">
+      <c r="B169" s="4" t="inlineStr">
         <is>
           <t>SilverChlorideElectrode</t>
         </is>
       </c>
-      <c r="C160" s="4" t="n"/>
-      <c r="D160" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="n"/>
-      <c r="F160" s="4" t="inlineStr">
+      <c r="C169" s="4" t="n"/>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="n"/>
+      <c r="F169" s="4" t="inlineStr">
         <is>
           <t>hasComponentB-type|CatholyteCompartment-hasReferenceElectrode</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
         <is>
           <t>Membrane projected area</t>
         </is>
       </c>
-      <c r="B161" s="5" t="n">
+      <c r="B170" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C161" s="5" t="inlineStr">
+      <c r="C170" s="5" t="inlineStr">
         <is>
           <t>cm2</t>
         </is>
       </c>
-      <c r="D161" s="5" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="n"/>
-      <c r="F161" s="5" t="inlineStr">
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="n"/>
+      <c r="F170" s="5" t="inlineStr">
         <is>
           <t>hasSeparator-hasMeasuredProperty-Area</t>
         </is>
       </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="4" t="inlineStr">
-        <is>
-          <t>Anolyte compartment volume</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="C162" s="4" t="inlineStr">
-        <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="D162" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E162" s="4" t="n"/>
-      <c r="F162" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Volume</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="5" t="inlineStr">
-        <is>
-          <t>Positive electrode to membrane gap/anolyte compartment width</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C163" s="5" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D163" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="n"/>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Width</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="4" t="inlineStr">
-        <is>
-          <t>Reference electrode in anolyte compartment</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>SilverChlorideElectrode</t>
-        </is>
-      </c>
-      <c r="C164" s="4" t="n"/>
-      <c r="D164" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="n"/>
-      <c r="F164" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentC-type|AnolyteCompartment-hasReferenceElectrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="5" t="inlineStr">
-        <is>
-          <t>Positive electrode projected area</t>
-        </is>
-      </c>
-      <c r="B165" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C165" s="5" t="inlineStr">
-        <is>
-          <t>cm2</t>
-        </is>
-      </c>
-      <c r="D165" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E165" s="5" t="n"/>
-      <c r="F165" s="5" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode-hasMeasuredProperty-Area</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="4" t="inlineStr">
-        <is>
-          <t>Positive electrode gas compartment width</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="n"/>
-      <c r="F166" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasMeasuredProperty-Width</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t>Positive electrode gas compartment (FlowField or leave blank)</t>
-        </is>
-      </c>
-      <c r="B167" s="5" t="inlineStr">
-        <is>
-          <t>FlowField</t>
-        </is>
-      </c>
-      <c r="C167" s="5" t="n"/>
-      <c r="D167" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E167" s="5" t="n"/>
-      <c r="F167" s="5" t="inlineStr">
-        <is>
-          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasComponent</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="4" t="inlineStr">
-        <is>
-          <t>Catholyte tank volume</t>
-        </is>
-      </c>
-      <c r="B168" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="D168" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="n"/>
-      <c r="F168" s="4" t="inlineStr">
-        <is>
-          <t>hasComponentE-type|CatholyteTank-hasMeasuredProperty-Volume</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="5" t="inlineStr">
-        <is>
-          <t>Anolyte tank volume</t>
-        </is>
-      </c>
-      <c r="B169" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="C169" s="5" t="inlineStr">
-        <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="D169" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E169" s="5" t="n"/>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>hasComponentF-type|AnolyteTank-hasMeasuredProperty-Volume</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="18" t="inlineStr">
-        <is>
-          <t>Cell optional component supplier information</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="n"/>
-      <c r="C170" s="3" t="n"/>
-      <c r="D170" s="3" t="n"/>
-      <c r="E170" s="3" t="n"/>
-      <c r="F170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>Cell case manufacturer</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>Fuel Cell Store</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="n"/>
+          <t>Anolyte compartment width</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E171" s="4" t="n"/>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>hasCase-schema:manufacturer</t>
+          <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Width</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>Cell case manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B172" s="5" t="inlineStr">
-        <is>
-          <t>Micro Flow Cell</t>
-        </is>
-      </c>
-      <c r="C172" s="5" t="n"/>
+          <t>Anolyte compartment volume</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E172" s="5" t="n"/>
       <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>hasComponentC-type|AnolyteCompartment-hasMeasuredProperty-Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>Reference electrode in anolyte compartment</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="n"/>
+      <c r="C173" s="4" t="n"/>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="n"/>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentC-type|AnolyteCompartment-hasReferenceElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>Positive electrode geometric surface area</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="n"/>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrodeGeometricSurfaceArea</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode real surface area</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="n"/>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="n"/>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrodeRealSurfaceArea</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>Positive electrode electrochemically active surface area</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="n"/>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="n"/>
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrochemicallyActiveSurfaceArea</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode to separator gap width</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="n"/>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasMeasuredProperty-ElectrodeToSeparatorGapWidth</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>Positive electrode gas compartment</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="n"/>
+      <c r="C178" s="5" t="n"/>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>FlowField or leave blank</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasComponent</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrode gas compartment width</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="n"/>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>Leave blank if FlowField</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasMeasuredProperty-Width</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>Positive electrode gas compartment volume</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="n"/>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="inlineStr">
+        <is>
+          <t>Leave blank if FlowField</t>
+        </is>
+      </c>
+      <c r="F180" s="5" t="inlineStr">
+        <is>
+          <t>hasComponentD-type|PositiveElectrodeGasCompartment-hasMeasuredProperty-Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>Catholyte tank volume</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="n"/>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>hasComponentE-type|CatholyteTank-hasMeasuredProperty-Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>Anolyte tank volume</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="n"/>
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>hasComponentF-type|AnolyteTank-hasMeasuredProperty-Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="18" t="inlineStr">
+        <is>
+          <t>Cell optional component manufacturer information</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="n"/>
+      <c r="C183" s="3" t="n"/>
+      <c r="D183" s="3" t="n"/>
+      <c r="E183" s="3" t="n"/>
+      <c r="F183" s="3" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>Cell case manufacturer</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>Redox.me</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="n"/>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="n"/>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>hasCase-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>Cell case manufacturer product ID A</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>C-A-MM_PEC_HC-2x15-1</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="n"/>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="n"/>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>hasCase-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>Cell case manufacturer product ID B</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>C-A-MM_FC_GDE_XRD_EC</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="n"/>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="n"/>
+      <c r="F186" s="4" t="inlineStr">
         <is>
           <t>hasCase-schema:productID</t>
         </is>
@@ -4630,7 +4870,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5281/zenodo.22092428</t>
+          <t>https://doi.org/10.5281/zenodo.23761089</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4882,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>https://zenodo.org/api/records/22092428</t>
+          <t>https://zenodo.org/api/records/23761089</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4894,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Claudia Bissattini</t>
+          <t>Claudia Bissattini Alessi</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -4772,12 +5012,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Fig. 1a</t>
+          <t>Fig. 2a</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Fig. 2b</t>
+          <t>Fig. 3a</t>
         </is>
       </c>
     </row>
@@ -4789,7 +5029,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Claudia Bissattini</t>
+          <t>Claudia Bissattini Alessi</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -4907,7 +5147,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>empa__ecid000001/empa__ecid000001.cdf.parquet</t>
+          <t>empa__ecid000251.cdf.parquet</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -4924,7 +5164,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>empa__ecid000001/empa__ecid000001.cdf.csv</t>
+          <t>empa__ecid000251.cdf.csv</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -4941,12 +5181,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>empa__ecid000001/empa__ecid000001_CA_C01.mpr</t>
+          <t>empa__ecid000251.raw.zip</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Raw electrochemical data, Biologic EC-Lab mpr binary format</t>
+          <t>Raw electrochemical data, GC data, and yadg settings.</t>
         </is>
       </c>
     </row>
@@ -4954,16 +5194,6 @@
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Input fileA</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>empa__ecid000001/empa__ecid000001.mps</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Measurement protocol, Biologic EC-Lab settings file</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6485,7 +6715,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Claudia Bissattini</t>
+          <t>Claudia Bissattini Alessi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6495,7 +6725,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://orcid.org/0000-0002-3971-0398</t>
+          <t>https://orcid.org/0009-0000-0662-4971</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6849,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q367032</t>
+          <t>http://www.wikidata.org/entity/Q720484</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6641,7 +6871,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q310172</t>
+          <t>http://www.wikidata.org/entity/Q309245</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6685,7 +6915,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q15829006</t>
+          <t>http://www.wikidata.org/entity/Q20630716</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6729,7 +6959,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q879878</t>
+          <t>http://www.wikidata.org/entity/Q15810492</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -6817,7 +7047,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q2361947</t>
+          <t>http://www.wikidata.org/entity/Q320207</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6839,7 +7069,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q487209</t>
+          <t>http://www.wikidata.org/entity/Q706184</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -6883,7 +7113,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q306455</t>
+          <t>http://www.wikidata.org/entity/Q643674</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -6905,7 +7135,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q908461</t>
+          <t>http://www.wikidata.org/entity/Q168115</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -7091,6 +7321,30 @@
       <c r="D36" t="inlineStr">
         <is>
           <t>Versogen Inc.; manufacturer of PiperION AEM series based on poly(aryl piperidinium) backbone for CO2 electrolysis and fuel cells. https://www.versogen.com. to be requested</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Baoji Qixin Titanium</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Redox.me</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
         </is>
       </c>
     </row>
